--- a/Excel/StockQuotation (4).xlsx
+++ b/Excel/StockQuotation (4).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>03/02/23 12:58:31</v>
+        <v>07/02/23 23:29:58</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1068.11</v>
+        <v>1064</v>
       </c>
       <c r="B7" t="str">
-        <v>2.59 (0.243%)</v>
+        <v>-0.43 (-0.0403%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>1070.05</v>
+        <v>1069.54</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>1063.03</v>
+        <v>1060.96</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>1044249730</v>
+        <v>1843006951</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>22192209753.63</v>
+        <v>38880805074.99</v>
       </c>
     </row>
     <row r="9">
@@ -514,46 +514,46 @@
         <v>-</v>
       </c>
       <c r="C10">
-        <v>3.06</v>
+        <v>3.08</v>
       </c>
       <c r="D10">
         <v>-0.02</v>
       </c>
       <c r="E10">
-        <v>-0.6493506493506493</v>
+        <v>-0.6451612903225806</v>
       </c>
       <c r="F10">
+        <v>3.1</v>
+      </c>
+      <c r="G10">
+        <v>3.12</v>
+      </c>
+      <c r="H10">
+        <v>3.06</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>47860704</v>
+      </c>
+      <c r="L10">
+        <v>148095.61584</v>
+      </c>
+      <c r="M10">
+        <v>10938600</v>
+      </c>
+      <c r="N10">
+        <v>3.06</v>
+      </c>
+      <c r="O10">
         <v>3.08</v>
       </c>
-      <c r="G10">
-        <v>3.08</v>
-      </c>
-      <c r="H10">
-        <v>3.04</v>
-      </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>32807300</v>
-      </c>
-      <c r="L10">
-        <v>100509.9188</v>
-      </c>
-      <c r="M10">
-        <v>17097600</v>
-      </c>
-      <c r="N10">
-        <v>3.04</v>
-      </c>
-      <c r="O10">
-        <v>3.06</v>
-      </c>
       <c r="P10">
-        <v>1037400</v>
+        <v>307300</v>
       </c>
     </row>
     <row r="11">
@@ -579,31 +579,31 @@
         <v>2.58</v>
       </c>
       <c r="H11">
+        <v>2.54</v>
+      </c>
+      <c r="I11">
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <v>23915176</v>
+      </c>
+      <c r="L11">
+        <v>61242.8576</v>
+      </c>
+      <c r="M11">
+        <v>4541200</v>
+      </c>
+      <c r="N11">
+        <v>2.54</v>
+      </c>
+      <c r="O11">
         <v>2.56</v>
       </c>
-      <c r="I11">
-        <v>0</v>
-      </c>
-      <c r="J11">
-        <v>0</v>
-      </c>
-      <c r="K11">
-        <v>5287232</v>
-      </c>
-      <c r="L11">
-        <v>13538.515800000001</v>
-      </c>
-      <c r="M11">
-        <v>1072200</v>
-      </c>
-      <c r="N11">
-        <v>2.56</v>
-      </c>
-      <c r="O11">
-        <v>2.58</v>
-      </c>
       <c r="P11">
-        <v>1953600</v>
+        <v>456300</v>
       </c>
     </row>
     <row r="12">
@@ -614,22 +614,22 @@
         <v>-</v>
       </c>
       <c r="C12">
+        <v>196.5</v>
+      </c>
+      <c r="D12">
+        <v>-0.5</v>
+      </c>
+      <c r="E12">
+        <v>-0.25380710659898476</v>
+      </c>
+      <c r="F12">
+        <v>197</v>
+      </c>
+      <c r="G12">
         <v>198</v>
       </c>
-      <c r="D12">
-        <v>0.5</v>
-      </c>
-      <c r="E12">
-        <v>0.25316455696202533</v>
-      </c>
-      <c r="F12">
-        <v>197.5</v>
-      </c>
-      <c r="G12">
-        <v>198.5</v>
-      </c>
       <c r="H12">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -638,22 +638,22 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>926679</v>
+        <v>3223977</v>
       </c>
       <c r="L12">
-        <v>183244.338</v>
+        <v>633905.6665</v>
       </c>
       <c r="M12">
-        <v>127900</v>
+        <v>581100</v>
       </c>
       <c r="N12">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="O12">
-        <v>198.5</v>
+        <v>196.5</v>
       </c>
       <c r="P12">
-        <v>132800</v>
+        <v>51200</v>
       </c>
     </row>
     <row r="13">
@@ -664,46 +664,46 @@
         <v>-</v>
       </c>
       <c r="C13">
-        <v>32.25</v>
+        <v>32.75</v>
       </c>
       <c r="D13">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E13">
-        <v>-1.5267175572519085</v>
+        <v>-0.7575757575757576</v>
       </c>
       <c r="F13">
+        <v>33</v>
+      </c>
+      <c r="G13">
+        <v>33.25</v>
+      </c>
+      <c r="H13">
+        <v>32.5</v>
+      </c>
+      <c r="I13">
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <v>1688685</v>
+      </c>
+      <c r="L13">
+        <v>55467.10525</v>
+      </c>
+      <c r="M13">
+        <v>5000</v>
+      </c>
+      <c r="N13">
         <v>32.75</v>
       </c>
-      <c r="G13">
-        <v>32.75</v>
-      </c>
-      <c r="H13">
-        <v>32</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <v>1366962</v>
-      </c>
-      <c r="L13">
-        <v>44180.37375</v>
-      </c>
-      <c r="M13">
-        <v>147200</v>
-      </c>
-      <c r="N13">
-        <v>32</v>
-      </c>
       <c r="O13">
-        <v>32.25</v>
+        <v>33</v>
       </c>
       <c r="P13">
-        <v>66200</v>
+        <v>328000</v>
       </c>
     </row>
     <row r="14">
@@ -717,16 +717,16 @@
         <v>12.9</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E14">
-        <v>0</v>
+        <v>-0.7692307692307693</v>
       </c>
       <c r="F14">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="G14">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="H14">
         <v>12.8</v>
@@ -738,22 +738,22 @@
         <v>0</v>
       </c>
       <c r="K14">
-        <v>83924</v>
+        <v>296417</v>
       </c>
       <c r="L14">
-        <v>1082.9692</v>
+        <v>3835.5916</v>
       </c>
       <c r="M14">
-        <v>46400</v>
+        <v>86000</v>
       </c>
       <c r="N14">
+        <v>12.8</v>
+      </c>
+      <c r="O14">
         <v>12.9</v>
       </c>
-      <c r="O14">
-        <v>13</v>
-      </c>
       <c r="P14">
-        <v>64300</v>
+        <v>27100</v>
       </c>
     </row>
     <row r="15">
@@ -764,22 +764,22 @@
         <v>-</v>
       </c>
       <c r="C15">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="D15">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E15">
-        <v>0.49019607843137253</v>
+        <v>0</v>
       </c>
       <c r="F15">
-        <v>20.5</v>
+        <v>20.2</v>
       </c>
       <c r="G15">
-        <v>20.6</v>
+        <v>20.3</v>
       </c>
       <c r="H15">
-        <v>20.4</v>
+        <v>19.9</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -788,22 +788,22 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>2882659</v>
+        <v>6175226</v>
       </c>
       <c r="L15">
-        <v>59060.9257</v>
+        <v>124102.2675</v>
       </c>
       <c r="M15">
-        <v>357200</v>
+        <v>171800</v>
       </c>
       <c r="N15">
-        <v>20.5</v>
+        <v>20.1</v>
       </c>
       <c r="O15">
-        <v>20.6</v>
+        <v>20.2</v>
       </c>
       <c r="P15">
-        <v>1158000</v>
+        <v>143600</v>
       </c>
     </row>
     <row r="16">
@@ -814,46 +814,46 @@
         <v>-</v>
       </c>
       <c r="C16">
+        <v>73.5</v>
+      </c>
+      <c r="D16">
+        <v>-0.25</v>
+      </c>
+      <c r="E16">
+        <v>-0.3389830508474576</v>
+      </c>
+      <c r="F16">
+        <v>73.5</v>
+      </c>
+      <c r="G16">
+        <v>74</v>
+      </c>
+      <c r="H16">
+        <v>73.25</v>
+      </c>
+      <c r="I16">
+        <v>0</v>
+      </c>
+      <c r="J16">
+        <v>0</v>
+      </c>
+      <c r="K16">
+        <v>19882884</v>
+      </c>
+      <c r="L16">
+        <v>1462189.4985</v>
+      </c>
+      <c r="M16">
+        <v>5942900</v>
+      </c>
+      <c r="N16">
+        <v>73.5</v>
+      </c>
+      <c r="O16">
         <v>73.75</v>
       </c>
-      <c r="D16">
-        <v>-0.75</v>
-      </c>
-      <c r="E16">
-        <v>-1.0067114093959733</v>
-      </c>
-      <c r="F16">
-        <v>74</v>
-      </c>
-      <c r="G16">
-        <v>74.25</v>
-      </c>
-      <c r="H16">
-        <v>73.75</v>
-      </c>
-      <c r="I16">
-        <v>0</v>
-      </c>
-      <c r="J16">
-        <v>0</v>
-      </c>
-      <c r="K16">
-        <v>15849880</v>
-      </c>
-      <c r="L16">
-        <v>1172900.6285</v>
-      </c>
-      <c r="M16">
-        <v>3667400</v>
-      </c>
-      <c r="N16">
-        <v>73.75</v>
-      </c>
-      <c r="O16">
-        <v>74</v>
-      </c>
       <c r="P16">
-        <v>1404700</v>
+        <v>439300</v>
       </c>
     </row>
     <row r="17">
@@ -864,46 +864,46 @@
         <v>-</v>
       </c>
       <c r="C17">
-        <v>12</v>
+        <v>11.9</v>
       </c>
       <c r="D17">
-        <v>-0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E17">
-        <v>-1.639344262295082</v>
+        <v>0.847457627118644</v>
       </c>
       <c r="F17">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="G17">
-        <v>12.2</v>
+        <v>11.9</v>
       </c>
       <c r="H17">
+        <v>11.7</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>16341272</v>
+      </c>
+      <c r="L17">
+        <v>193278.3275</v>
+      </c>
+      <c r="M17">
+        <v>2417300</v>
+      </c>
+      <c r="N17">
         <v>11.8</v>
       </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>18412971</v>
-      </c>
-      <c r="L17">
-        <v>220380.516</v>
-      </c>
-      <c r="M17">
-        <v>287400</v>
-      </c>
-      <c r="N17">
-        <v>12</v>
-      </c>
       <c r="O17">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="P17">
-        <v>1609600</v>
+        <v>754800</v>
       </c>
     </row>
     <row r="18">
@@ -914,23 +914,23 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="D18">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E18">
-        <v>0</v>
+        <v>0.7246376811594203</v>
       </c>
       <c r="F18">
-        <v>13.7</v>
+        <v>13.9</v>
       </c>
       <c r="G18">
+        <v>14</v>
+      </c>
+      <c r="H18">
         <v>13.8</v>
       </c>
-      <c r="H18">
-        <v>13.6</v>
-      </c>
       <c r="I18">
         <v>0</v>
       </c>
@@ -938,22 +938,22 @@
         <v>0</v>
       </c>
       <c r="K18">
-        <v>246028</v>
+        <v>740963</v>
       </c>
       <c r="L18">
-        <v>3372.5074</v>
+        <v>10289.0565</v>
       </c>
       <c r="M18">
-        <v>81400</v>
+        <v>281600</v>
       </c>
       <c r="N18">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="O18">
-        <v>13.8</v>
+        <v>13.9</v>
       </c>
       <c r="P18">
-        <v>129000</v>
+        <v>133600</v>
       </c>
     </row>
     <row r="19">
@@ -964,46 +964,46 @@
         <v>-</v>
       </c>
       <c r="C19">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="D19">
-        <v>0.25</v>
+        <v>-0.15</v>
       </c>
       <c r="E19">
-        <v>2.9940119760479043</v>
+        <v>-1.7341040462427746</v>
       </c>
       <c r="F19">
         <v>8.65</v>
       </c>
       <c r="G19">
-        <v>8.75</v>
+        <v>8.65</v>
       </c>
       <c r="H19">
+        <v>8.5</v>
+      </c>
+      <c r="I19">
+        <v>0</v>
+      </c>
+      <c r="J19">
+        <v>0</v>
+      </c>
+      <c r="K19">
+        <v>925083</v>
+      </c>
+      <c r="L19">
+        <v>7915.8463</v>
+      </c>
+      <c r="M19">
+        <v>199800</v>
+      </c>
+      <c r="N19">
+        <v>8.5</v>
+      </c>
+      <c r="O19">
         <v>8.55</v>
       </c>
-      <c r="I19">
-        <v>0</v>
-      </c>
-      <c r="J19">
-        <v>0</v>
-      </c>
-      <c r="K19">
-        <v>8392365</v>
-      </c>
-      <c r="L19">
-        <v>72569.17629999999</v>
-      </c>
-      <c r="M19">
-        <v>323100</v>
-      </c>
-      <c r="N19">
-        <v>8.55</v>
-      </c>
-      <c r="O19">
-        <v>8.6</v>
-      </c>
       <c r="P19">
-        <v>35500</v>
+        <v>31500</v>
       </c>
     </row>
     <row r="20">
@@ -1014,46 +1014,46 @@
         <v>-</v>
       </c>
       <c r="C20">
+        <v>5.85</v>
+      </c>
+      <c r="D20">
+        <v>0</v>
+      </c>
+      <c r="E20">
+        <v>0</v>
+      </c>
+      <c r="F20">
+        <v>5.85</v>
+      </c>
+      <c r="G20">
+        <v>5.9</v>
+      </c>
+      <c r="H20">
         <v>5.8</v>
       </c>
-      <c r="D20">
-        <v>0</v>
-      </c>
-      <c r="E20">
-        <v>0</v>
-      </c>
-      <c r="F20">
-        <v>5.8</v>
-      </c>
-      <c r="G20">
+      <c r="I20">
+        <v>0</v>
+      </c>
+      <c r="J20">
+        <v>0</v>
+      </c>
+      <c r="K20">
+        <v>19377717</v>
+      </c>
+      <c r="L20">
+        <v>113441.1258</v>
+      </c>
+      <c r="M20">
+        <v>12201600</v>
+      </c>
+      <c r="N20">
         <v>5.85</v>
       </c>
-      <c r="H20">
-        <v>5.75</v>
-      </c>
-      <c r="I20">
-        <v>0</v>
-      </c>
-      <c r="J20">
-        <v>0</v>
-      </c>
-      <c r="K20">
-        <v>18788287</v>
-      </c>
-      <c r="L20">
-        <v>109044.90335</v>
-      </c>
-      <c r="M20">
-        <v>5532400</v>
-      </c>
-      <c r="N20">
-        <v>5.8</v>
-      </c>
       <c r="O20">
-        <v>5.85</v>
+        <v>5.9</v>
       </c>
       <c r="P20">
-        <v>4710500</v>
+        <v>7559300</v>
       </c>
     </row>
     <row r="21">
@@ -1064,23 +1064,23 @@
         <v>-</v>
       </c>
       <c r="C21">
-        <v>33.75</v>
+        <v>34.25</v>
       </c>
       <c r="D21">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="E21">
-        <v>0.746268656716418</v>
+        <v>-0.7246376811594203</v>
       </c>
       <c r="F21">
-        <v>33.25</v>
+        <v>34.5</v>
       </c>
       <c r="G21">
+        <v>34.5</v>
+      </c>
+      <c r="H21">
         <v>34</v>
       </c>
-      <c r="H21">
-        <v>33</v>
-      </c>
       <c r="I21">
         <v>0</v>
       </c>
@@ -1088,22 +1088,22 @@
         <v>0</v>
       </c>
       <c r="K21">
-        <v>687770</v>
+        <v>773584</v>
       </c>
       <c r="L21">
-        <v>23117.48875</v>
+        <v>26529.6145</v>
       </c>
       <c r="M21">
-        <v>237500</v>
+        <v>45900</v>
       </c>
       <c r="N21">
-        <v>33.5</v>
+        <v>34.25</v>
       </c>
       <c r="O21">
-        <v>34</v>
+        <v>34.5</v>
       </c>
       <c r="P21">
-        <v>631000</v>
+        <v>320400</v>
       </c>
     </row>
     <row r="22">
@@ -1114,22 +1114,22 @@
         <v>-</v>
       </c>
       <c r="C22">
-        <v>16.2</v>
+        <v>15.8</v>
       </c>
       <c r="D22">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E22">
-        <v>-0.6134969325153374</v>
+        <v>-1.25</v>
       </c>
       <c r="F22">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="G22">
-        <v>16.4</v>
+        <v>16.1</v>
       </c>
       <c r="H22">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -1138,22 +1138,22 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>15647974</v>
+        <v>20470183</v>
       </c>
       <c r="L22">
-        <v>253643.8293</v>
+        <v>325444.6618</v>
       </c>
       <c r="M22">
-        <v>2173200</v>
+        <v>3687500</v>
       </c>
       <c r="N22">
-        <v>16.1</v>
+        <v>15.8</v>
       </c>
       <c r="O22">
-        <v>16.2</v>
+        <v>15.9</v>
       </c>
       <c r="P22">
-        <v>2739100</v>
+        <v>706100</v>
       </c>
     </row>
     <row r="23">
@@ -1164,46 +1164,46 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="D23">
         <v>-0.1</v>
       </c>
       <c r="E23">
-        <v>-0.8620689655172413</v>
+        <v>-0.8849557522123894</v>
       </c>
       <c r="F23">
-        <v>11.6</v>
+        <v>11.3</v>
       </c>
       <c r="G23">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="H23">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>100000</v>
       </c>
       <c r="J23">
-        <v>0</v>
+        <v>1134</v>
       </c>
       <c r="K23">
-        <v>54645283</v>
+        <v>161516144</v>
       </c>
       <c r="L23">
-        <v>624838.5507</v>
+        <v>1831534.3802</v>
       </c>
       <c r="M23">
-        <v>10262400</v>
+        <v>23883600</v>
       </c>
       <c r="N23">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="O23">
-        <v>11.5</v>
+        <v>11.3</v>
       </c>
       <c r="P23">
-        <v>6065600</v>
+        <v>772100</v>
       </c>
     </row>
     <row r="24">
@@ -1214,22 +1214,22 @@
         <v>-</v>
       </c>
       <c r="C24">
-        <v>161.5</v>
+        <v>160.5</v>
       </c>
       <c r="D24">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E24">
-        <v>0</v>
+        <v>-0.3105590062111801</v>
       </c>
       <c r="F24">
         <v>161.5</v>
       </c>
       <c r="G24">
-        <v>162</v>
+        <v>161.5</v>
       </c>
       <c r="H24">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="I24">
         <v>0</v>
@@ -1238,22 +1238,22 @@
         <v>0</v>
       </c>
       <c r="K24">
-        <v>2211193</v>
+        <v>3101777</v>
       </c>
       <c r="L24">
-        <v>356945.837</v>
+        <v>497468.5115</v>
       </c>
       <c r="M24">
-        <v>328100</v>
+        <v>756800</v>
       </c>
       <c r="N24">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="O24">
-        <v>161.5</v>
+        <v>160.5</v>
       </c>
       <c r="P24">
-        <v>159400</v>
+        <v>235000</v>
       </c>
     </row>
     <row r="25">
@@ -1264,22 +1264,22 @@
         <v>-</v>
       </c>
       <c r="C25">
+        <v>35.5</v>
+      </c>
+      <c r="D25">
+        <v>-0.5</v>
+      </c>
+      <c r="E25">
+        <v>-1.3888888888888888</v>
+      </c>
+      <c r="F25">
         <v>36</v>
       </c>
-      <c r="D25">
-        <v>-0.75</v>
-      </c>
-      <c r="E25">
-        <v>-2.0408163265306123</v>
-      </c>
-      <c r="F25">
-        <v>36.75</v>
-      </c>
       <c r="G25">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="H25">
-        <v>36</v>
+        <v>35.25</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1288,22 +1288,22 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>4948626</v>
+        <v>5801589</v>
       </c>
       <c r="L25">
-        <v>178959.632</v>
+        <v>206626.30275</v>
       </c>
       <c r="M25">
-        <v>915200</v>
+        <v>767100</v>
       </c>
       <c r="N25">
-        <v>36</v>
+        <v>35.25</v>
       </c>
       <c r="O25">
-        <v>36.25</v>
+        <v>35.5</v>
       </c>
       <c r="P25">
-        <v>343900</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="26">
@@ -1317,10 +1317,10 @@
         <v>10</v>
       </c>
       <c r="D26">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E26">
-        <v>-0.9900990099009901</v>
+        <v>0</v>
       </c>
       <c r="F26">
         <v>10.1</v>
@@ -1329,7 +1329,7 @@
         <v>10.1</v>
       </c>
       <c r="H26">
-        <v>9.95</v>
+        <v>10</v>
       </c>
       <c r="I26">
         <v>0</v>
@@ -1338,22 +1338,22 @@
         <v>0</v>
       </c>
       <c r="K26">
-        <v>1716422</v>
+        <v>1404493</v>
       </c>
       <c r="L26">
-        <v>17156.9141</v>
+        <v>14074.1795</v>
       </c>
       <c r="M26">
-        <v>679000</v>
+        <v>640200</v>
       </c>
       <c r="N26">
-        <v>9.95</v>
+        <v>10</v>
       </c>
       <c r="O26">
-        <v>10</v>
+        <v>10.1</v>
       </c>
       <c r="P26">
-        <v>413600</v>
+        <v>895700</v>
       </c>
     </row>
     <row r="27">
@@ -1364,46 +1364,46 @@
         <v>-</v>
       </c>
       <c r="C27">
-        <v>29.75</v>
+        <v>29.5</v>
       </c>
       <c r="D27">
         <v>-0.25</v>
       </c>
       <c r="E27">
-        <v>-0.8333333333333334</v>
+        <v>-0.8403361344537815</v>
       </c>
       <c r="F27">
-        <v>29.75</v>
+        <v>30</v>
       </c>
       <c r="G27">
         <v>30</v>
       </c>
       <c r="H27">
+        <v>29.5</v>
+      </c>
+      <c r="I27">
+        <v>0</v>
+      </c>
+      <c r="J27">
+        <v>0</v>
+      </c>
+      <c r="K27">
+        <v>21781654</v>
+      </c>
+      <c r="L27">
+        <v>646621.64125</v>
+      </c>
+      <c r="M27">
+        <v>9700400</v>
+      </c>
+      <c r="N27">
+        <v>29.5</v>
+      </c>
+      <c r="O27">
         <v>29.75</v>
       </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>10127799</v>
-      </c>
-      <c r="L27">
-        <v>301787.20025</v>
-      </c>
-      <c r="M27">
-        <v>3463300</v>
-      </c>
-      <c r="N27">
-        <v>29.75</v>
-      </c>
-      <c r="O27">
-        <v>30</v>
-      </c>
       <c r="P27">
-        <v>3613300</v>
+        <v>1863000</v>
       </c>
     </row>
     <row r="28">
@@ -1414,13 +1414,13 @@
         <v>-</v>
       </c>
       <c r="C28">
-        <v>9.75</v>
+        <v>9.6</v>
       </c>
       <c r="D28">
-        <v>0</v>
+        <v>-0.15</v>
       </c>
       <c r="E28">
-        <v>0</v>
+        <v>-1.5384615384615385</v>
       </c>
       <c r="F28">
         <v>9.7</v>
@@ -1429,31 +1429,31 @@
         <v>9.75</v>
       </c>
       <c r="H28">
+        <v>9.55</v>
+      </c>
+      <c r="I28">
+        <v>0</v>
+      </c>
+      <c r="J28">
+        <v>0</v>
+      </c>
+      <c r="K28">
+        <v>58793587</v>
+      </c>
+      <c r="L28">
+        <v>565334.3098500001</v>
+      </c>
+      <c r="M28">
+        <v>1211000</v>
+      </c>
+      <c r="N28">
+        <v>9.6</v>
+      </c>
+      <c r="O28">
         <v>9.65</v>
       </c>
-      <c r="I28">
-        <v>0</v>
-      </c>
-      <c r="J28">
-        <v>0</v>
-      </c>
-      <c r="K28">
-        <v>8532159</v>
-      </c>
-      <c r="L28">
-        <v>82777.6208</v>
-      </c>
-      <c r="M28">
-        <v>4542200</v>
-      </c>
-      <c r="N28">
-        <v>9.7</v>
-      </c>
-      <c r="O28">
-        <v>9.75</v>
-      </c>
       <c r="P28">
-        <v>3210100</v>
+        <v>3215400</v>
       </c>
     </row>
     <row r="29">
@@ -1464,23 +1464,23 @@
         <v>-</v>
       </c>
       <c r="C29">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="D29">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E29">
-        <v>0.9900990099009901</v>
+        <v>0</v>
       </c>
       <c r="F29">
         <v>10.2</v>
       </c>
       <c r="G29">
+        <v>10.4</v>
+      </c>
+      <c r="H29">
         <v>10.2</v>
       </c>
-      <c r="H29">
-        <v>10.1</v>
-      </c>
       <c r="I29">
         <v>0</v>
       </c>
@@ -1488,22 +1488,22 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>56400</v>
+        <v>321738</v>
       </c>
       <c r="L29">
-        <v>570.92</v>
+        <v>3312.4498</v>
       </c>
       <c r="M29">
-        <v>216900</v>
+        <v>918600</v>
       </c>
       <c r="N29">
-        <v>10.1</v>
+        <v>10.2</v>
       </c>
       <c r="O29">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="P29">
-        <v>340400</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="30">
@@ -1514,22 +1514,22 @@
         <v>-</v>
       </c>
       <c r="C30">
-        <v>40.5</v>
+        <v>40.75</v>
       </c>
       <c r="D30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E30">
-        <v>0</v>
+        <v>2.5157232704402515</v>
       </c>
       <c r="F30">
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="G30">
-        <v>41</v>
+        <v>40.75</v>
       </c>
       <c r="H30">
-        <v>40.5</v>
+        <v>39.75</v>
       </c>
       <c r="I30">
         <v>0</v>
@@ -1538,13 +1538,13 @@
         <v>0</v>
       </c>
       <c r="K30">
-        <v>5143625</v>
+        <v>9101197</v>
       </c>
       <c r="L30">
-        <v>209587.5735</v>
+        <v>365517.13</v>
       </c>
       <c r="M30">
-        <v>477300</v>
+        <v>464700</v>
       </c>
       <c r="N30">
         <v>40.5</v>
@@ -1553,7 +1553,7 @@
         <v>40.75</v>
       </c>
       <c r="P30">
-        <v>390000</v>
+        <v>724300</v>
       </c>
     </row>
     <row r="31">
@@ -1564,46 +1564,46 @@
         <v>-</v>
       </c>
       <c r="C31">
+        <v>38.5</v>
+      </c>
+      <c r="D31">
+        <v>0.5</v>
+      </c>
+      <c r="E31">
+        <v>1.3157894736842106</v>
+      </c>
+      <c r="F31">
         <v>38.25</v>
       </c>
-      <c r="D31">
-        <v>0.25</v>
-      </c>
-      <c r="E31">
-        <v>0.6578947368421053</v>
-      </c>
-      <c r="F31">
+      <c r="G31">
+        <v>38.75</v>
+      </c>
+      <c r="H31">
+        <v>37.5</v>
+      </c>
+      <c r="I31">
+        <v>0</v>
+      </c>
+      <c r="J31">
+        <v>0</v>
+      </c>
+      <c r="K31">
+        <v>4774943</v>
+      </c>
+      <c r="L31">
+        <v>182526.64975</v>
+      </c>
+      <c r="M31">
+        <v>374200</v>
+      </c>
+      <c r="N31">
         <v>38.5</v>
       </c>
-      <c r="G31">
-        <v>38.5</v>
-      </c>
-      <c r="H31">
-        <v>38</v>
-      </c>
-      <c r="I31">
-        <v>0</v>
-      </c>
-      <c r="J31">
-        <v>0</v>
-      </c>
-      <c r="K31">
-        <v>1713313</v>
-      </c>
-      <c r="L31">
-        <v>65550.448</v>
-      </c>
-      <c r="M31">
-        <v>146800</v>
-      </c>
-      <c r="N31">
-        <v>38.25</v>
-      </c>
       <c r="O31">
-        <v>38.5</v>
+        <v>38.75</v>
       </c>
       <c r="P31">
-        <v>651000</v>
+        <v>403100</v>
       </c>
     </row>
     <row r="32">
@@ -1614,46 +1614,46 @@
         <v>-</v>
       </c>
       <c r="C32">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D32">
         <v>-1</v>
       </c>
       <c r="E32">
-        <v>-0.3412969283276451</v>
+        <v>-0.3424657534246575</v>
       </c>
       <c r="F32">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="G32">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="H32">
+        <v>290</v>
+      </c>
+      <c r="I32">
+        <v>0</v>
+      </c>
+      <c r="J32">
+        <v>0</v>
+      </c>
+      <c r="K32">
+        <v>21207</v>
+      </c>
+      <c r="L32">
+        <v>6181.244</v>
+      </c>
+      <c r="M32">
+        <v>5100</v>
+      </c>
+      <c r="N32">
+        <v>291</v>
+      </c>
+      <c r="O32">
         <v>292</v>
       </c>
-      <c r="I32">
-        <v>0</v>
-      </c>
-      <c r="J32">
-        <v>0</v>
-      </c>
-      <c r="K32">
-        <v>12842</v>
-      </c>
-      <c r="L32">
-        <v>3760.942</v>
-      </c>
-      <c r="M32">
-        <v>500</v>
-      </c>
-      <c r="N32">
-        <v>292</v>
-      </c>
-      <c r="O32">
-        <v>293</v>
-      </c>
       <c r="P32">
-        <v>1800</v>
+        <v>4600</v>
       </c>
     </row>
     <row r="33">
@@ -1664,46 +1664,46 @@
         <v>-</v>
       </c>
       <c r="C33">
-        <v>28.75</v>
+        <v>30</v>
       </c>
       <c r="D33">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E33">
-        <v>-1.7094017094017093</v>
+        <v>-0.8264462809917356</v>
       </c>
       <c r="F33">
-        <v>29.25</v>
+        <v>30.25</v>
       </c>
       <c r="G33">
-        <v>29.25</v>
+        <v>30.5</v>
       </c>
       <c r="H33">
-        <v>28.5</v>
+        <v>29.75</v>
       </c>
       <c r="I33">
-        <v>0</v>
+        <v>107200</v>
       </c>
       <c r="J33">
-        <v>0</v>
+        <v>3216</v>
       </c>
       <c r="K33">
-        <v>2088022</v>
+        <v>5138658</v>
       </c>
       <c r="L33">
-        <v>60174.2905</v>
+        <v>154918.59375</v>
       </c>
       <c r="M33">
-        <v>900900</v>
+        <v>200400</v>
       </c>
       <c r="N33">
-        <v>28.5</v>
+        <v>30</v>
       </c>
       <c r="O33">
-        <v>28.75</v>
+        <v>30.25</v>
       </c>
       <c r="P33">
-        <v>294800</v>
+        <v>928600</v>
       </c>
     </row>
     <row r="34">
@@ -1714,22 +1714,22 @@
         <v>-</v>
       </c>
       <c r="C34">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="D34">
-        <v>-0.4</v>
+        <v>0.1</v>
       </c>
       <c r="E34">
-        <v>-2.3255813953488373</v>
+        <v>0.5882352941176471</v>
       </c>
       <c r="F34">
         <v>17.1</v>
       </c>
       <c r="G34">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="H34">
-        <v>16.5</v>
+        <v>16.8</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1738,22 +1738,22 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>2975210</v>
+        <v>551835</v>
       </c>
       <c r="L34">
-        <v>50004.5643</v>
+        <v>9361.9499</v>
       </c>
       <c r="M34">
-        <v>158600</v>
+        <v>17000</v>
       </c>
       <c r="N34">
-        <v>16.7</v>
+        <v>17</v>
       </c>
       <c r="O34">
-        <v>16.8</v>
+        <v>17.1</v>
       </c>
       <c r="P34">
-        <v>73900</v>
+        <v>228900</v>
       </c>
     </row>
     <row r="35">
@@ -1764,22 +1764,22 @@
         <v>-</v>
       </c>
       <c r="C35">
-        <v>8.4</v>
+        <v>8.25</v>
       </c>
       <c r="D35">
         <v>-0.05</v>
       </c>
       <c r="E35">
-        <v>-0.591715976331361</v>
+        <v>-0.6024096385542169</v>
       </c>
       <c r="F35">
+        <v>8.3</v>
+      </c>
+      <c r="G35">
         <v>8.4</v>
       </c>
-      <c r="G35">
-        <v>8.45</v>
-      </c>
       <c r="H35">
-        <v>8.4</v>
+        <v>8.2</v>
       </c>
       <c r="I35">
         <v>0</v>
@@ -1788,22 +1788,22 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>6616794</v>
+        <v>52782066</v>
       </c>
       <c r="L35">
-        <v>55847.0761</v>
+        <v>436595.46095</v>
       </c>
       <c r="M35">
-        <v>5078500</v>
+        <v>267700</v>
       </c>
       <c r="N35">
-        <v>8.4</v>
+        <v>8.25</v>
       </c>
       <c r="O35">
-        <v>8.45</v>
+        <v>8.3</v>
       </c>
       <c r="P35">
-        <v>1630800</v>
+        <v>1769900</v>
       </c>
     </row>
     <row r="36">
@@ -1814,22 +1814,22 @@
         <v>-</v>
       </c>
       <c r="C36">
-        <v>103.5</v>
+        <v>102</v>
       </c>
       <c r="D36">
-        <v>0.5</v>
+        <v>-1</v>
       </c>
       <c r="E36">
-        <v>0.4854368932038835</v>
+        <v>-0.970873786407767</v>
       </c>
       <c r="F36">
-        <v>103.5</v>
+        <v>103</v>
       </c>
       <c r="G36">
         <v>103.5</v>
       </c>
       <c r="H36">
-        <v>102.5</v>
+        <v>101.5</v>
       </c>
       <c r="I36">
         <v>0</v>
@@ -1838,22 +1838,22 @@
         <v>0</v>
       </c>
       <c r="K36">
-        <v>596127</v>
+        <v>1768116</v>
       </c>
       <c r="L36">
-        <v>61450.2335</v>
+        <v>180572.946</v>
       </c>
       <c r="M36">
-        <v>137100</v>
+        <v>151600</v>
       </c>
       <c r="N36">
-        <v>103</v>
+        <v>101.5</v>
       </c>
       <c r="O36">
-        <v>103.5</v>
+        <v>102</v>
       </c>
       <c r="P36">
-        <v>282300</v>
+        <v>63900</v>
       </c>
     </row>
     <row r="37">
@@ -1864,23 +1864,23 @@
         <v>-</v>
       </c>
       <c r="C37">
+        <v>54</v>
+      </c>
+      <c r="D37">
+        <v>0</v>
+      </c>
+      <c r="E37">
+        <v>0</v>
+      </c>
+      <c r="F37">
+        <v>53.75</v>
+      </c>
+      <c r="G37">
+        <v>54.25</v>
+      </c>
+      <c r="H37">
         <v>53.25</v>
       </c>
-      <c r="D37">
-        <v>0.75</v>
-      </c>
-      <c r="E37">
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="F37">
-        <v>52.5</v>
-      </c>
-      <c r="G37">
-        <v>53.5</v>
-      </c>
-      <c r="H37">
-        <v>52.25</v>
-      </c>
       <c r="I37">
         <v>0</v>
       </c>
@@ -1888,22 +1888,22 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>2880115</v>
+        <v>2843307</v>
       </c>
       <c r="L37">
-        <v>152595.1425</v>
+        <v>153187.50425</v>
       </c>
       <c r="M37">
-        <v>124300</v>
+        <v>105900</v>
       </c>
       <c r="N37">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="O37">
-        <v>53.25</v>
+        <v>54.25</v>
       </c>
       <c r="P37">
-        <v>119500</v>
+        <v>66500</v>
       </c>
     </row>
     <row r="38">
@@ -1914,22 +1914,22 @@
         <v>-</v>
       </c>
       <c r="C38">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="D38">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="E38">
-        <v>0.8810572687224669</v>
+        <v>1.7391304347826086</v>
       </c>
       <c r="F38">
-        <v>4.54</v>
+        <v>4.64</v>
       </c>
       <c r="G38">
-        <v>4.58</v>
+        <v>4.72</v>
       </c>
       <c r="H38">
-        <v>4.54</v>
+        <v>4.6</v>
       </c>
       <c r="I38">
         <v>0</v>
@@ -1938,22 +1938,22 @@
         <v>0</v>
       </c>
       <c r="K38">
-        <v>1178350</v>
+        <v>24336619</v>
       </c>
       <c r="L38">
-        <v>5383.643</v>
+        <v>113698.60182</v>
       </c>
       <c r="M38">
-        <v>857200</v>
+        <v>1189900</v>
       </c>
       <c r="N38">
-        <v>4.56</v>
+        <v>4.66</v>
       </c>
       <c r="O38">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="P38">
-        <v>1046500</v>
+        <v>359000</v>
       </c>
     </row>
     <row r="39">
@@ -1964,46 +1964,46 @@
         <v>-</v>
       </c>
       <c r="C39">
-        <v>32.5</v>
+        <v>31.75</v>
       </c>
       <c r="D39">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E39">
-        <v>0</v>
+        <v>-1.550387596899225</v>
       </c>
       <c r="F39">
-        <v>32.5</v>
+        <v>32</v>
       </c>
       <c r="G39">
-        <v>32.75</v>
+        <v>32.25</v>
       </c>
       <c r="H39">
+        <v>31.25</v>
+      </c>
+      <c r="I39">
+        <v>7133000</v>
+      </c>
+      <c r="J39">
+        <v>228106</v>
+      </c>
+      <c r="K39">
+        <v>15549744</v>
+      </c>
+      <c r="L39">
+        <v>495102.87975</v>
+      </c>
+      <c r="M39">
+        <v>265700</v>
+      </c>
+      <c r="N39">
+        <v>31.75</v>
+      </c>
+      <c r="O39">
         <v>32</v>
       </c>
-      <c r="I39">
-        <v>0</v>
-      </c>
-      <c r="J39">
-        <v>0</v>
-      </c>
-      <c r="K39">
-        <v>7897929</v>
-      </c>
-      <c r="L39">
-        <v>253918.7285</v>
-      </c>
-      <c r="M39">
-        <v>167600</v>
-      </c>
-      <c r="N39">
-        <v>32.25</v>
-      </c>
-      <c r="O39">
-        <v>32.5</v>
-      </c>
       <c r="P39">
-        <v>1216400</v>
+        <v>667600</v>
       </c>
     </row>
     <row r="40">
@@ -2014,19 +2014,19 @@
         <v>-</v>
       </c>
       <c r="C40">
-        <v>67.5</v>
+        <v>66.75</v>
       </c>
       <c r="D40">
-        <v>0.75</v>
+        <v>0</v>
       </c>
       <c r="E40">
-        <v>1.1235955056179776</v>
+        <v>0</v>
       </c>
       <c r="F40">
-        <v>66.75</v>
+        <v>66.5</v>
       </c>
       <c r="G40">
-        <v>67.5</v>
+        <v>67</v>
       </c>
       <c r="H40">
         <v>66.5</v>
@@ -2038,22 +2038,22 @@
         <v>0</v>
       </c>
       <c r="K40">
-        <v>5993135</v>
+        <v>17353807</v>
       </c>
       <c r="L40">
-        <v>401516.93475</v>
+        <v>1158120.88375</v>
       </c>
       <c r="M40">
-        <v>848500</v>
+        <v>2792200</v>
       </c>
       <c r="N40">
-        <v>67.25</v>
+        <v>66.75</v>
       </c>
       <c r="O40">
-        <v>67.5</v>
+        <v>67</v>
       </c>
       <c r="P40">
-        <v>928200</v>
+        <v>1848100</v>
       </c>
     </row>
     <row r="41">
@@ -2064,7 +2064,7 @@
         <v>-</v>
       </c>
       <c r="C41">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="D41">
         <v>0</v>
@@ -2073,13 +2073,13 @@
         <v>0</v>
       </c>
       <c r="F41">
-        <v>23.8</v>
+        <v>23.6</v>
       </c>
       <c r="G41">
-        <v>24</v>
+        <v>23.7</v>
       </c>
       <c r="H41">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="I41">
         <v>0</v>
@@ -2088,22 +2088,22 @@
         <v>0</v>
       </c>
       <c r="K41">
-        <v>9578760</v>
+        <v>17028962</v>
       </c>
       <c r="L41">
-        <v>228593.6587</v>
+        <v>401183.07739999995</v>
       </c>
       <c r="M41">
-        <v>1523800</v>
+        <v>2056100</v>
       </c>
       <c r="N41">
-        <v>23.8</v>
+        <v>23.5</v>
       </c>
       <c r="O41">
-        <v>23.9</v>
+        <v>23.6</v>
       </c>
       <c r="P41">
-        <v>474400</v>
+        <v>347500</v>
       </c>
     </row>
     <row r="42">
@@ -2114,46 +2114,46 @@
         <v>-</v>
       </c>
       <c r="C42">
-        <v>74.75</v>
+        <v>73</v>
       </c>
       <c r="D42">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="E42">
-        <v>3.8194444444444446</v>
+        <v>0</v>
       </c>
       <c r="F42">
+        <v>73.25</v>
+      </c>
+      <c r="G42">
+        <v>73.25</v>
+      </c>
+      <c r="H42">
+        <v>72.5</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>6999054</v>
+      </c>
+      <c r="L42">
+        <v>510636.73125</v>
+      </c>
+      <c r="M42">
+        <v>21700</v>
+      </c>
+      <c r="N42">
         <v>73</v>
       </c>
-      <c r="G42">
-        <v>75.5</v>
-      </c>
-      <c r="H42">
-        <v>73</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>8292812</v>
-      </c>
-      <c r="L42">
-        <v>617454.42875</v>
-      </c>
-      <c r="M42">
-        <v>263600</v>
-      </c>
-      <c r="N42">
-        <v>74.5</v>
-      </c>
       <c r="O42">
-        <v>74.75</v>
+        <v>73.25</v>
       </c>
       <c r="P42">
-        <v>464700</v>
+        <v>371800</v>
       </c>
     </row>
     <row r="43">
@@ -2164,19 +2164,19 @@
         <v>-</v>
       </c>
       <c r="C43">
+        <v>44.25</v>
+      </c>
+      <c r="D43">
+        <v>-0.25</v>
+      </c>
+      <c r="E43">
+        <v>-0.5617977528089888</v>
+      </c>
+      <c r="F43">
         <v>44.5</v>
       </c>
-      <c r="D43">
-        <v>0.25</v>
-      </c>
-      <c r="E43">
-        <v>0.5649717514124294</v>
-      </c>
-      <c r="F43">
-        <v>44</v>
-      </c>
       <c r="G43">
-        <v>44.75</v>
+        <v>44.5</v>
       </c>
       <c r="H43">
         <v>43.75</v>
@@ -2188,22 +2188,22 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>5789252</v>
+        <v>10167453</v>
       </c>
       <c r="L43">
-        <v>255629.49225</v>
+        <v>448185.82275</v>
       </c>
       <c r="M43">
-        <v>1007200</v>
+        <v>667100</v>
       </c>
       <c r="N43">
-        <v>44.5</v>
+        <v>44</v>
       </c>
       <c r="O43">
-        <v>44.75</v>
+        <v>44.25</v>
       </c>
       <c r="P43">
-        <v>888400</v>
+        <v>1198400</v>
       </c>
     </row>
     <row r="44">
@@ -2214,22 +2214,22 @@
         <v>-</v>
       </c>
       <c r="C44">
-        <v>934</v>
+        <v>970</v>
       </c>
       <c r="D44">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="E44">
-        <v>1.965065502183406</v>
+        <v>2.1052631578947367</v>
       </c>
       <c r="F44">
-        <v>922</v>
+        <v>966</v>
       </c>
       <c r="G44">
-        <v>942</v>
+        <v>996</v>
       </c>
       <c r="H44">
-        <v>916</v>
+        <v>962</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2238,22 +2238,22 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>2335098</v>
+        <v>4132116</v>
       </c>
       <c r="L44">
-        <v>2167990.978</v>
+        <v>4034300.206</v>
       </c>
       <c r="M44">
-        <v>4900</v>
+        <v>29800</v>
       </c>
       <c r="N44">
-        <v>932</v>
+        <v>970</v>
       </c>
       <c r="O44">
-        <v>934</v>
+        <v>972</v>
       </c>
       <c r="P44">
-        <v>12100</v>
+        <v>66800</v>
       </c>
     </row>
     <row r="45">
@@ -2264,46 +2264,46 @@
         <v>-</v>
       </c>
       <c r="C45">
+        <v>13</v>
+      </c>
+      <c r="D45">
+        <v>0</v>
+      </c>
+      <c r="E45">
+        <v>0</v>
+      </c>
+      <c r="F45">
+        <v>13</v>
+      </c>
+      <c r="G45">
         <v>13.1</v>
       </c>
-      <c r="D45">
-        <v>0</v>
-      </c>
-      <c r="E45">
-        <v>0</v>
-      </c>
-      <c r="F45">
-        <v>13.2</v>
-      </c>
-      <c r="G45">
-        <v>13.2</v>
-      </c>
       <c r="H45">
+        <v>12.8</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>1248511</v>
+      </c>
+      <c r="L45">
+        <v>16126.752</v>
+      </c>
+      <c r="M45">
+        <v>60000</v>
+      </c>
+      <c r="N45">
+        <v>12.9</v>
+      </c>
+      <c r="O45">
         <v>13</v>
       </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>444546</v>
-      </c>
-      <c r="L45">
-        <v>5831.7126</v>
-      </c>
-      <c r="M45">
-        <v>168400</v>
-      </c>
-      <c r="N45">
-        <v>13</v>
-      </c>
-      <c r="O45">
-        <v>13.1</v>
-      </c>
       <c r="P45">
-        <v>234600</v>
+        <v>6900</v>
       </c>
     </row>
     <row r="46">
@@ -2314,46 +2314,46 @@
         <v>-</v>
       </c>
       <c r="C46">
-        <v>8.35</v>
+        <v>8.25</v>
       </c>
       <c r="D46">
-        <v>0.05</v>
+        <v>-0.05</v>
       </c>
       <c r="E46">
-        <v>0.6024096385542169</v>
+        <v>-0.6024096385542169</v>
       </c>
       <c r="F46">
+        <v>8.25</v>
+      </c>
+      <c r="G46">
         <v>8.3</v>
       </c>
-      <c r="G46">
-        <v>8.35</v>
-      </c>
       <c r="H46">
+        <v>8.25</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>137355</v>
+      </c>
+      <c r="L46">
+        <v>1134.4045</v>
+      </c>
+      <c r="M46">
+        <v>11800</v>
+      </c>
+      <c r="N46">
+        <v>8.25</v>
+      </c>
+      <c r="O46">
         <v>8.3</v>
       </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>5287</v>
-      </c>
-      <c r="L46">
-        <v>44.0471</v>
-      </c>
-      <c r="M46">
-        <v>15500</v>
-      </c>
-      <c r="N46">
-        <v>8.3</v>
-      </c>
-      <c r="O46">
-        <v>8.35</v>
-      </c>
       <c r="P46">
-        <v>46600</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="47">
@@ -2364,46 +2364,46 @@
         <v>-</v>
       </c>
       <c r="C47">
-        <v>50</v>
+        <v>49.75</v>
       </c>
       <c r="D47">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E47">
-        <v>0.5025125628140703</v>
+        <v>0</v>
       </c>
       <c r="F47">
-        <v>50</v>
+        <v>49.75</v>
       </c>
       <c r="G47">
         <v>50</v>
       </c>
       <c r="H47">
+        <v>49.25</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>3615781</v>
+      </c>
+      <c r="L47">
+        <v>179304.867</v>
+      </c>
+      <c r="M47">
+        <v>419300</v>
+      </c>
+      <c r="N47">
+        <v>49.5</v>
+      </c>
+      <c r="O47">
         <v>49.75</v>
       </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>1996532</v>
-      </c>
-      <c r="L47">
-        <v>99501.42075</v>
-      </c>
-      <c r="M47">
-        <v>244600</v>
-      </c>
-      <c r="N47">
-        <v>49.75</v>
-      </c>
-      <c r="O47">
-        <v>50</v>
-      </c>
       <c r="P47">
-        <v>715600</v>
+        <v>54800</v>
       </c>
     </row>
     <row r="48">
@@ -2414,46 +2414,46 @@
         <v>-</v>
       </c>
       <c r="C48">
+        <v>90.5</v>
+      </c>
+      <c r="D48">
+        <v>1.75</v>
+      </c>
+      <c r="E48">
+        <v>1.971830985915493</v>
+      </c>
+      <c r="F48">
         <v>89.25</v>
       </c>
-      <c r="D48">
-        <v>2.75</v>
-      </c>
-      <c r="E48">
-        <v>3.179190751445087</v>
-      </c>
-      <c r="F48">
-        <v>87.5</v>
-      </c>
       <c r="G48">
-        <v>90.25</v>
+        <v>91.25</v>
       </c>
       <c r="H48">
-        <v>87.5</v>
+        <v>89</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>300000</v>
       </c>
       <c r="J48">
-        <v>0</v>
+        <v>27150</v>
       </c>
       <c r="K48">
-        <v>15996698</v>
+        <v>20532822</v>
       </c>
       <c r="L48">
-        <v>1429505.722</v>
+        <v>1857934.2095</v>
       </c>
       <c r="M48">
-        <v>1007400</v>
+        <v>129000</v>
       </c>
       <c r="N48">
-        <v>89</v>
+        <v>90.5</v>
       </c>
       <c r="O48">
-        <v>89.25</v>
+        <v>90.75</v>
       </c>
       <c r="P48">
-        <v>287100</v>
+        <v>395700</v>
       </c>
     </row>
     <row r="49">
@@ -2464,46 +2464,46 @@
         <v>-</v>
       </c>
       <c r="C49">
-        <v>5.35</v>
+        <v>5.45</v>
       </c>
       <c r="D49">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E49">
-        <v>0</v>
+        <v>1.8691588785046729</v>
       </c>
       <c r="F49">
-        <v>5.35</v>
+        <v>5.3</v>
       </c>
       <c r="G49">
+        <v>5.5</v>
+      </c>
+      <c r="H49">
+        <v>5.25</v>
+      </c>
+      <c r="I49">
+        <v>0</v>
+      </c>
+      <c r="J49">
+        <v>0</v>
+      </c>
+      <c r="K49">
+        <v>1512018</v>
+      </c>
+      <c r="L49">
+        <v>8110.20285</v>
+      </c>
+      <c r="M49">
+        <v>48300</v>
+      </c>
+      <c r="N49">
         <v>5.4</v>
       </c>
-      <c r="H49">
-        <v>5.3</v>
-      </c>
-      <c r="I49">
-        <v>0</v>
-      </c>
-      <c r="J49">
-        <v>0</v>
-      </c>
-      <c r="K49">
-        <v>807364</v>
-      </c>
-      <c r="L49">
-        <v>4314.47025</v>
-      </c>
-      <c r="M49">
-        <v>9700</v>
-      </c>
-      <c r="N49">
-        <v>5.35</v>
-      </c>
       <c r="O49">
-        <v>5.4</v>
+        <v>5.45</v>
       </c>
       <c r="P49">
-        <v>152700</v>
+        <v>79900</v>
       </c>
     </row>
     <row r="50">
@@ -2514,22 +2514,22 @@
         <v>-</v>
       </c>
       <c r="C50">
-        <v>173.5</v>
+        <v>172</v>
       </c>
       <c r="D50">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="E50">
-        <v>-0.5730659025787965</v>
+        <v>-0.2898550724637681</v>
       </c>
       <c r="F50">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G50">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H50">
-        <v>173.5</v>
+        <v>171</v>
       </c>
       <c r="I50">
         <v>0</v>
@@ -2538,22 +2538,22 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>254316</v>
+        <v>944769</v>
       </c>
       <c r="L50">
-        <v>44194.1755</v>
+        <v>162568.3245</v>
       </c>
       <c r="M50">
-        <v>52200</v>
+        <v>100</v>
       </c>
       <c r="N50">
-        <v>173.5</v>
+        <v>172</v>
       </c>
       <c r="O50">
-        <v>174</v>
+        <v>172.5</v>
       </c>
       <c r="P50">
-        <v>58700</v>
+        <v>23000</v>
       </c>
     </row>
     <row r="51">
@@ -2564,7 +2564,7 @@
         <v>-</v>
       </c>
       <c r="C51">
-        <v>8.75</v>
+        <v>8.7</v>
       </c>
       <c r="D51">
         <v>0</v>
@@ -2573,7 +2573,7 @@
         <v>0</v>
       </c>
       <c r="F51">
-        <v>8.75</v>
+        <v>8.65</v>
       </c>
       <c r="G51">
         <v>8.75</v>
@@ -2588,22 +2588,22 @@
         <v>0</v>
       </c>
       <c r="K51">
-        <v>679204</v>
+        <v>1349939</v>
       </c>
       <c r="L51">
-        <v>5909.6748</v>
+        <v>11741.280050000001</v>
       </c>
       <c r="M51">
-        <v>363000</v>
+        <v>471000</v>
       </c>
       <c r="N51">
+        <v>8.65</v>
+      </c>
+      <c r="O51">
         <v>8.7</v>
       </c>
-      <c r="O51">
-        <v>8.75</v>
-      </c>
       <c r="P51">
-        <v>142700</v>
+        <v>124800</v>
       </c>
     </row>
     <row r="52">
@@ -2614,46 +2614,46 @@
         <v>-</v>
       </c>
       <c r="C52">
-        <v>4.42</v>
+        <v>4.6</v>
       </c>
       <c r="D52">
-        <v>0.02</v>
+        <v>0.16</v>
       </c>
       <c r="E52">
-        <v>0.45454545454545453</v>
+        <v>3.6036036036036037</v>
       </c>
       <c r="F52">
-        <v>4.4</v>
+        <v>4.46</v>
       </c>
       <c r="G52">
+        <v>4.62</v>
+      </c>
+      <c r="H52">
         <v>4.46</v>
       </c>
-      <c r="H52">
-        <v>4.32</v>
-      </c>
       <c r="I52">
-        <v>9000000</v>
+        <v>0</v>
       </c>
       <c r="J52">
-        <v>37800</v>
+        <v>0</v>
       </c>
       <c r="K52">
-        <v>20712202</v>
+        <v>27268940</v>
       </c>
       <c r="L52">
-        <v>89338.69873999999</v>
+        <v>123563.55742</v>
       </c>
       <c r="M52">
-        <v>230800</v>
+        <v>67000</v>
       </c>
       <c r="N52">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="O52">
-        <v>4.42</v>
+        <v>4.62</v>
       </c>
       <c r="P52">
-        <v>328600</v>
+        <v>256800</v>
       </c>
     </row>
     <row r="53">
@@ -2664,22 +2664,22 @@
         <v>-</v>
       </c>
       <c r="C53">
-        <v>13.3</v>
+        <v>12.6</v>
       </c>
       <c r="D53">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="E53">
-        <v>1.5267175572519085</v>
+        <v>-4.545454545454546</v>
       </c>
       <c r="F53">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="G53">
         <v>13.3</v>
       </c>
       <c r="H53">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2688,22 +2688,22 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>1913071</v>
+        <v>13964192</v>
       </c>
       <c r="L53">
-        <v>25169.519399999997</v>
+        <v>178375.5901</v>
       </c>
       <c r="M53">
-        <v>212400</v>
+        <v>950600</v>
       </c>
       <c r="N53">
-        <v>13.2</v>
+        <v>12.6</v>
       </c>
       <c r="O53">
-        <v>13.3</v>
+        <v>12.7</v>
       </c>
       <c r="P53">
-        <v>380100</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="54">
@@ -2714,19 +2714,19 @@
         <v>-</v>
       </c>
       <c r="C54">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="D54">
-        <v>0.4</v>
+        <v>0</v>
       </c>
       <c r="E54">
-        <v>1.932367149758454</v>
+        <v>0</v>
       </c>
       <c r="F54">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="G54">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="H54">
         <v>20.7</v>
@@ -2738,22 +2738,22 @@
         <v>0</v>
       </c>
       <c r="K54">
-        <v>7827538</v>
+        <v>11074770</v>
       </c>
       <c r="L54">
-        <v>164164.5855</v>
+        <v>230826.29940000002</v>
       </c>
       <c r="M54">
-        <v>366800</v>
+        <v>9800</v>
       </c>
       <c r="N54">
-        <v>21.1</v>
+        <v>20.9</v>
       </c>
       <c r="O54">
-        <v>21.2</v>
+        <v>21</v>
       </c>
       <c r="P54">
-        <v>1111100</v>
+        <v>851900</v>
       </c>
     </row>
     <row r="55">
@@ -2767,43 +2767,43 @@
         <v>69.5</v>
       </c>
       <c r="D55">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E55">
-        <v>0.36101083032490977</v>
+        <v>0.7246376811594203</v>
       </c>
       <c r="F55">
+        <v>69</v>
+      </c>
+      <c r="G55">
+        <v>69.75</v>
+      </c>
+      <c r="H55">
+        <v>69</v>
+      </c>
+      <c r="I55">
+        <v>0</v>
+      </c>
+      <c r="J55">
+        <v>0</v>
+      </c>
+      <c r="K55">
+        <v>3829162</v>
+      </c>
+      <c r="L55">
+        <v>265731.12725</v>
+      </c>
+      <c r="M55">
+        <v>160600</v>
+      </c>
+      <c r="N55">
+        <v>69.25</v>
+      </c>
+      <c r="O55">
         <v>69.5</v>
       </c>
-      <c r="G55">
-        <v>70</v>
-      </c>
-      <c r="H55">
-        <v>69.25</v>
-      </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>3217833</v>
-      </c>
-      <c r="L55">
-        <v>224379.00775</v>
-      </c>
-      <c r="M55">
-        <v>255900</v>
-      </c>
-      <c r="N55">
-        <v>69.5</v>
-      </c>
-      <c r="O55">
-        <v>69.75</v>
-      </c>
       <c r="P55">
-        <v>171900</v>
+        <v>41000</v>
       </c>
     </row>
     <row r="56">
@@ -2826,10 +2826,10 @@
         <v>53.75</v>
       </c>
       <c r="G56">
-        <v>54</v>
+        <v>54.25</v>
       </c>
       <c r="H56">
-        <v>53.5</v>
+        <v>53.75</v>
       </c>
       <c r="I56">
         <v>0</v>
@@ -2838,13 +2838,13 @@
         <v>0</v>
       </c>
       <c r="K56">
-        <v>4045359</v>
+        <v>11502957</v>
       </c>
       <c r="L56">
-        <v>217544.964</v>
+        <v>620947.3135</v>
       </c>
       <c r="M56">
-        <v>474400</v>
+        <v>3345400</v>
       </c>
       <c r="N56">
         <v>53.75</v>
@@ -2853,7 +2853,7 @@
         <v>54</v>
       </c>
       <c r="P56">
-        <v>887700</v>
+        <v>190800</v>
       </c>
     </row>
     <row r="57">
@@ -2864,46 +2864,46 @@
         <v>-</v>
       </c>
       <c r="C57">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="D57">
-        <v>-0.02</v>
+        <v>-0.04</v>
       </c>
       <c r="E57">
-        <v>-0.4</v>
+        <v>-0.8032128514056225</v>
       </c>
       <c r="F57">
         <v>5</v>
       </c>
       <c r="G57">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="H57">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="I57">
-        <v>0</v>
+        <v>580000</v>
       </c>
       <c r="J57">
-        <v>0</v>
+        <v>2865.2</v>
       </c>
       <c r="K57">
-        <v>3485277</v>
+        <v>52248036</v>
       </c>
       <c r="L57">
-        <v>17380.11324</v>
+        <v>259856.6892</v>
       </c>
       <c r="M57">
-        <v>4818900</v>
+        <v>7270900</v>
       </c>
       <c r="N57">
-        <v>4.98</v>
+        <v>4.94</v>
       </c>
       <c r="O57">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="P57">
-        <v>3493200</v>
+        <v>43100</v>
       </c>
     </row>
     <row r="58">
@@ -2917,34 +2917,34 @@
         <v>64</v>
       </c>
       <c r="D58">
-        <v>-1</v>
+        <v>0.75</v>
       </c>
       <c r="E58">
-        <v>-1.5384615384615385</v>
+        <v>1.1857707509881423</v>
       </c>
       <c r="F58">
-        <v>64.5</v>
+        <v>63</v>
       </c>
       <c r="G58">
         <v>65</v>
       </c>
       <c r="H58">
-        <v>63.75</v>
+        <v>63</v>
       </c>
       <c r="I58">
-        <v>154800</v>
+        <v>0</v>
       </c>
       <c r="J58">
-        <v>10017.94392</v>
+        <v>0</v>
       </c>
       <c r="K58">
-        <v>8214450</v>
+        <v>14815331</v>
       </c>
       <c r="L58">
-        <v>528159.57017</v>
+        <v>949666.43975</v>
       </c>
       <c r="M58">
-        <v>125100</v>
+        <v>274800</v>
       </c>
       <c r="N58">
         <v>64</v>
@@ -2953,7 +2953,7 @@
         <v>64.25</v>
       </c>
       <c r="P58">
-        <v>90600</v>
+        <v>258800</v>
       </c>
     </row>
     <row r="59">
@@ -2964,22 +2964,22 @@
         <v>-</v>
       </c>
       <c r="C59">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="D59">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="E59">
-        <v>3.4722222222222223</v>
+        <v>0</v>
       </c>
       <c r="F59">
-        <v>14.5</v>
+        <v>14.7</v>
       </c>
       <c r="G59">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="H59">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="I59">
         <v>0</v>
@@ -2988,22 +2988,22 @@
         <v>0</v>
       </c>
       <c r="K59">
-        <v>17087624</v>
+        <v>11804881</v>
       </c>
       <c r="L59">
-        <v>251533.164</v>
+        <v>173815.2965</v>
       </c>
       <c r="M59">
-        <v>2459500</v>
+        <v>2315500</v>
       </c>
       <c r="N59">
+        <v>14.7</v>
+      </c>
+      <c r="O59">
         <v>14.8</v>
       </c>
-      <c r="O59">
-        <v>14.9</v>
-      </c>
       <c r="P59">
-        <v>2476200</v>
+        <v>1376800</v>
       </c>
     </row>
     <row r="60">
@@ -3014,22 +3014,22 @@
         <v>-</v>
       </c>
       <c r="C60">
-        <v>30.75</v>
+        <v>31.5</v>
       </c>
       <c r="D60">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E60">
-        <v>0.819672131147541</v>
+        <v>1.6129032258064515</v>
       </c>
       <c r="F60">
-        <v>30.5</v>
+        <v>31.5</v>
       </c>
       <c r="G60">
-        <v>30.75</v>
+        <v>32.25</v>
       </c>
       <c r="H60">
-        <v>30.5</v>
+        <v>31.5</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -3038,22 +3038,22 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>45207</v>
+        <v>521964</v>
       </c>
       <c r="L60">
-        <v>1387.0495</v>
+        <v>16558.09075</v>
       </c>
       <c r="M60">
-        <v>39500</v>
+        <v>17800</v>
       </c>
       <c r="N60">
-        <v>30.5</v>
+        <v>31.25</v>
       </c>
       <c r="O60">
-        <v>30.75</v>
+        <v>31.5</v>
       </c>
       <c r="P60">
-        <v>42100</v>
+        <v>6700</v>
       </c>
     </row>
     <row r="61">
@@ -3064,23 +3064,23 @@
         <v>-</v>
       </c>
       <c r="C61">
-        <v>12.5</v>
+        <v>12.4</v>
       </c>
       <c r="D61">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E61">
-        <v>0</v>
+        <v>-0.8</v>
       </c>
       <c r="F61">
+        <v>12.6</v>
+      </c>
+      <c r="G61">
+        <v>12.7</v>
+      </c>
+      <c r="H61">
         <v>12.4</v>
       </c>
-      <c r="G61">
-        <v>12.5</v>
-      </c>
-      <c r="H61">
-        <v>12.3</v>
-      </c>
       <c r="I61">
         <v>0</v>
       </c>
@@ -3088,13 +3088,13 @@
         <v>0</v>
       </c>
       <c r="K61">
-        <v>2221074</v>
+        <v>3613668</v>
       </c>
       <c r="L61">
-        <v>27533.5165</v>
+        <v>45327.817299999995</v>
       </c>
       <c r="M61">
-        <v>140300</v>
+        <v>656600</v>
       </c>
       <c r="N61">
         <v>12.4</v>
@@ -3103,7 +3103,7 @@
         <v>12.5</v>
       </c>
       <c r="P61">
-        <v>413200</v>
+        <v>15000</v>
       </c>
     </row>
     <row r="62">
@@ -3114,46 +3114,46 @@
         <v>-</v>
       </c>
       <c r="C62">
-        <v>73.5</v>
+        <v>72.5</v>
       </c>
       <c r="D62">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E62">
-        <v>0.684931506849315</v>
+        <v>-0.3436426116838488</v>
       </c>
       <c r="F62">
         <v>72.75</v>
       </c>
       <c r="G62">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="H62">
+        <v>72.25</v>
+      </c>
+      <c r="I62">
+        <v>0</v>
+      </c>
+      <c r="J62">
+        <v>0</v>
+      </c>
+      <c r="K62">
+        <v>1572591</v>
+      </c>
+      <c r="L62">
+        <v>114134.26675</v>
+      </c>
+      <c r="M62">
+        <v>25400</v>
+      </c>
+      <c r="N62">
+        <v>72.5</v>
+      </c>
+      <c r="O62">
         <v>72.75</v>
       </c>
-      <c r="I62">
-        <v>0</v>
-      </c>
-      <c r="J62">
-        <v>0</v>
-      </c>
-      <c r="K62">
-        <v>802203</v>
-      </c>
-      <c r="L62">
-        <v>58812.5405</v>
-      </c>
-      <c r="M62">
-        <v>85100</v>
-      </c>
-      <c r="N62">
-        <v>73.25</v>
-      </c>
-      <c r="O62">
-        <v>73.5</v>
-      </c>
       <c r="P62">
-        <v>37400</v>
+        <v>154600</v>
       </c>
     </row>
     <row r="63">
@@ -3164,22 +3164,22 @@
         <v>-</v>
       </c>
       <c r="C63">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="D63">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="E63">
-        <v>-1.3071895424836601</v>
+        <v>-0.6535947712418301</v>
       </c>
       <c r="F63">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="G63">
         <v>3.08</v>
       </c>
       <c r="H63">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="I63">
         <v>0</v>
@@ -3188,22 +3188,22 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>45863127</v>
+        <v>19508263</v>
       </c>
       <c r="L63">
-        <v>139544.70306</v>
+        <v>59583.11662</v>
       </c>
       <c r="M63">
-        <v>14972900</v>
+        <v>10848100</v>
       </c>
       <c r="N63">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="O63">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="P63">
-        <v>6129300</v>
+        <v>1410300</v>
       </c>
     </row>
     <row r="64">
@@ -3214,22 +3214,22 @@
         <v>-</v>
       </c>
       <c r="C64">
-        <v>3.76</v>
+        <v>4.12</v>
       </c>
       <c r="D64">
         <v>-0.02</v>
       </c>
       <c r="E64">
-        <v>-0.5291005291005291</v>
+        <v>-0.4830917874396135</v>
       </c>
       <c r="F64">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="G64">
-        <v>3.82</v>
+        <v>4.22</v>
       </c>
       <c r="H64">
-        <v>3.76</v>
+        <v>4.06</v>
       </c>
       <c r="I64">
         <v>0</v>
@@ -3238,22 +3238,22 @@
         <v>0</v>
       </c>
       <c r="K64">
-        <v>2472647</v>
+        <v>26726143</v>
       </c>
       <c r="L64">
-        <v>9354.12644</v>
+        <v>110904.4647</v>
       </c>
       <c r="M64">
-        <v>914200</v>
+        <v>186900</v>
       </c>
       <c r="N64">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="O64">
-        <v>3.78</v>
+        <v>4.12</v>
       </c>
       <c r="P64">
-        <v>158900</v>
+        <v>146000</v>
       </c>
     </row>
     <row r="65">
@@ -3264,16 +3264,16 @@
         <v>-</v>
       </c>
       <c r="C65">
+        <v>40.5</v>
+      </c>
+      <c r="D65">
+        <v>-0.5</v>
+      </c>
+      <c r="E65">
+        <v>-1.2195121951219512</v>
+      </c>
+      <c r="F65">
         <v>40.75</v>
-      </c>
-      <c r="D65">
-        <v>0</v>
-      </c>
-      <c r="E65">
-        <v>0</v>
-      </c>
-      <c r="F65">
-        <v>40.5</v>
       </c>
       <c r="G65">
         <v>41</v>
@@ -3282,19 +3282,19 @@
         <v>40.25</v>
       </c>
       <c r="I65">
-        <v>0</v>
+        <v>69700</v>
       </c>
       <c r="J65">
-        <v>0</v>
+        <v>2822.85</v>
       </c>
       <c r="K65">
-        <v>5699163</v>
+        <v>11842657</v>
       </c>
       <c r="L65">
-        <v>231249.6615</v>
+        <v>481125.65975</v>
       </c>
       <c r="M65">
-        <v>849800</v>
+        <v>181400</v>
       </c>
       <c r="N65">
         <v>40.5</v>
@@ -3303,7 +3303,7 @@
         <v>40.75</v>
       </c>
       <c r="P65">
-        <v>512500</v>
+        <v>641100</v>
       </c>
     </row>
     <row r="66">
@@ -3314,22 +3314,22 @@
         <v>-</v>
       </c>
       <c r="C66">
-        <v>21.3</v>
+        <v>20.7</v>
       </c>
       <c r="D66">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E66">
-        <v>0.4716981132075472</v>
+        <v>-0.9569377990430622</v>
       </c>
       <c r="F66">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
       <c r="G66">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="H66">
-        <v>21.2</v>
+        <v>20.5</v>
       </c>
       <c r="I66">
         <v>0</v>
@@ -3338,22 +3338,22 @@
         <v>0</v>
       </c>
       <c r="K66">
-        <v>1299710</v>
+        <v>5033514</v>
       </c>
       <c r="L66">
-        <v>27678.966</v>
+        <v>104421.0835</v>
       </c>
       <c r="M66">
-        <v>134500</v>
+        <v>167300</v>
       </c>
       <c r="N66">
-        <v>21.3</v>
+        <v>20.6</v>
       </c>
       <c r="O66">
-        <v>21.4</v>
+        <v>20.7</v>
       </c>
       <c r="P66">
-        <v>109800</v>
+        <v>10300</v>
       </c>
     </row>
     <row r="67">
@@ -3364,37 +3364,37 @@
         <v>-</v>
       </c>
       <c r="C67">
+        <v>143.5</v>
+      </c>
+      <c r="D67">
+        <v>-0.5</v>
+      </c>
+      <c r="E67">
+        <v>-0.3472222222222222</v>
+      </c>
+      <c r="F67">
         <v>144</v>
       </c>
-      <c r="D67">
-        <v>0</v>
-      </c>
-      <c r="E67">
-        <v>0</v>
-      </c>
-      <c r="F67">
+      <c r="G67">
         <v>144.5</v>
-      </c>
-      <c r="G67">
-        <v>145</v>
       </c>
       <c r="H67">
         <v>143.5</v>
       </c>
       <c r="I67">
-        <v>0</v>
+        <v>500000</v>
       </c>
       <c r="J67">
-        <v>0</v>
+        <v>72000</v>
       </c>
       <c r="K67">
-        <v>5620646</v>
+        <v>7124224</v>
       </c>
       <c r="L67">
-        <v>810120.921</v>
+        <v>1025018.0965</v>
       </c>
       <c r="M67">
-        <v>1805600</v>
+        <v>1601200</v>
       </c>
       <c r="N67">
         <v>143.5</v>
@@ -3403,7 +3403,7 @@
         <v>144</v>
       </c>
       <c r="P67">
-        <v>305800</v>
+        <v>163200</v>
       </c>
     </row>
     <row r="68">
@@ -3414,22 +3414,22 @@
         <v>-</v>
       </c>
       <c r="C68">
+        <v>18.3</v>
+      </c>
+      <c r="D68">
+        <v>-0.3</v>
+      </c>
+      <c r="E68">
+        <v>-1.6129032258064515</v>
+      </c>
+      <c r="F68">
+        <v>18.6</v>
+      </c>
+      <c r="G68">
         <v>18.7</v>
       </c>
-      <c r="D68">
-        <v>0.1</v>
-      </c>
-      <c r="E68">
-        <v>0.5376344086021505</v>
-      </c>
-      <c r="F68">
-        <v>18.9</v>
-      </c>
-      <c r="G68">
-        <v>19</v>
-      </c>
       <c r="H68">
-        <v>18.5</v>
+        <v>18.2</v>
       </c>
       <c r="I68">
         <v>0</v>
@@ -3438,22 +3438,22 @@
         <v>0</v>
       </c>
       <c r="K68">
-        <v>976661</v>
+        <v>2231293</v>
       </c>
       <c r="L68">
-        <v>18309.578</v>
+        <v>40973.5248</v>
       </c>
       <c r="M68">
-        <v>144400</v>
+        <v>130400</v>
       </c>
       <c r="N68">
-        <v>18.6</v>
+        <v>18.3</v>
       </c>
       <c r="O68">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="P68">
-        <v>84300</v>
+        <v>30900</v>
       </c>
     </row>
     <row r="69">
@@ -3464,46 +3464,46 @@
         <v>-</v>
       </c>
       <c r="C69">
-        <v>68</v>
+        <v>67.5</v>
       </c>
       <c r="D69">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="E69">
-        <v>-0.7299270072992701</v>
+        <v>-1.4598540145985401</v>
       </c>
       <c r="F69">
-        <v>68.75</v>
+        <v>68.5</v>
       </c>
       <c r="G69">
-        <v>68.75</v>
+        <v>68.5</v>
       </c>
       <c r="H69">
-        <v>68</v>
+        <v>67.25</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>600000</v>
       </c>
       <c r="J69">
-        <v>0</v>
+        <v>40500</v>
       </c>
       <c r="K69">
-        <v>3221568</v>
+        <v>9986259</v>
       </c>
       <c r="L69">
-        <v>220126.521</v>
+        <v>675593.27775</v>
       </c>
       <c r="M69">
-        <v>1284000</v>
+        <v>688400</v>
       </c>
       <c r="N69">
-        <v>68</v>
+        <v>67.25</v>
       </c>
       <c r="O69">
-        <v>68.25</v>
+        <v>67.5</v>
       </c>
       <c r="P69">
-        <v>311600</v>
+        <v>110400</v>
       </c>
     </row>
     <row r="70">
@@ -3514,22 +3514,22 @@
         <v>-</v>
       </c>
       <c r="C70">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="D70">
         <v>-0.2</v>
       </c>
       <c r="E70">
-        <v>-1.1299435028248588</v>
+        <v>-1.1494252873563218</v>
       </c>
       <c r="F70">
-        <v>17.7</v>
+        <v>17.3</v>
       </c>
       <c r="G70">
-        <v>17.7</v>
+        <v>17.4</v>
       </c>
       <c r="H70">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3538,22 +3538,22 @@
         <v>0</v>
       </c>
       <c r="K70">
-        <v>8304490</v>
+        <v>37917040</v>
       </c>
       <c r="L70">
-        <v>146039.773</v>
+        <v>654660.8281</v>
       </c>
       <c r="M70">
-        <v>9742600</v>
+        <v>6309000</v>
       </c>
       <c r="N70">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="O70">
-        <v>17.6</v>
+        <v>17.3</v>
       </c>
       <c r="P70">
-        <v>1840600</v>
+        <v>3186300</v>
       </c>
     </row>
     <row r="71">
@@ -3564,46 +3564,46 @@
         <v>-</v>
       </c>
       <c r="C71">
-        <v>59.25</v>
+        <v>58</v>
       </c>
       <c r="D71">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="E71">
-        <v>0</v>
+        <v>-1.2765957446808511</v>
       </c>
       <c r="F71">
+        <v>58.75</v>
+      </c>
+      <c r="G71">
         <v>59</v>
       </c>
-      <c r="G71">
-        <v>59.25</v>
-      </c>
       <c r="H71">
-        <v>58.25</v>
+        <v>57.5</v>
       </c>
       <c r="I71">
-        <v>0</v>
+        <v>4000000</v>
       </c>
       <c r="J71">
-        <v>0</v>
+        <v>222500</v>
       </c>
       <c r="K71">
-        <v>1378885</v>
+        <v>13144003</v>
       </c>
       <c r="L71">
-        <v>81098.2005</v>
+        <v>751904.0455</v>
       </c>
       <c r="M71">
-        <v>905800</v>
+        <v>1194900</v>
       </c>
       <c r="N71">
-        <v>59</v>
+        <v>57.75</v>
       </c>
       <c r="O71">
-        <v>59.25</v>
+        <v>58</v>
       </c>
       <c r="P71">
-        <v>173400</v>
+        <v>78100</v>
       </c>
     </row>
     <row r="72">
@@ -3614,13 +3614,13 @@
         <v>-</v>
       </c>
       <c r="C72">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="D72">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="E72">
-        <v>0</v>
+        <v>-1.0638297872340425</v>
       </c>
       <c r="F72">
         <v>18.7</v>
@@ -3629,7 +3629,7 @@
         <v>18.8</v>
       </c>
       <c r="H72">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="I72">
         <v>0</v>
@@ -3638,22 +3638,22 @@
         <v>0</v>
       </c>
       <c r="K72">
-        <v>756276</v>
+        <v>1235687</v>
       </c>
       <c r="L72">
-        <v>14094.438300000002</v>
+        <v>23003.4544</v>
       </c>
       <c r="M72">
-        <v>93000</v>
+        <v>122700</v>
       </c>
       <c r="N72">
+        <v>18.6</v>
+      </c>
+      <c r="O72">
         <v>18.7</v>
       </c>
-      <c r="O72">
-        <v>18.8</v>
-      </c>
       <c r="P72">
-        <v>101500</v>
+        <v>20100</v>
       </c>
     </row>
     <row r="73">
@@ -3667,19 +3667,19 @@
         <v>51.5</v>
       </c>
       <c r="D73">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E73">
-        <v>-0.9615384615384616</v>
+        <v>-0.4830917874396135</v>
       </c>
       <c r="F73">
-        <v>52</v>
+        <v>51.75</v>
       </c>
       <c r="G73">
         <v>52</v>
       </c>
       <c r="H73">
-        <v>51.25</v>
+        <v>50.5</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3688,22 +3688,22 @@
         <v>0</v>
       </c>
       <c r="K73">
-        <v>837619</v>
+        <v>2419856</v>
       </c>
       <c r="L73">
-        <v>43140.9105</v>
+        <v>124190.05275</v>
       </c>
       <c r="M73">
-        <v>221800</v>
+        <v>307500</v>
       </c>
       <c r="N73">
-        <v>51.25</v>
+        <v>51.5</v>
       </c>
       <c r="O73">
-        <v>51.5</v>
+        <v>51.75</v>
       </c>
       <c r="P73">
-        <v>67600</v>
+        <v>22200</v>
       </c>
     </row>
     <row r="74">
@@ -3714,46 +3714,46 @@
         <v>-</v>
       </c>
       <c r="C74">
+        <v>33.25</v>
+      </c>
+      <c r="D74">
+        <v>-0.25</v>
+      </c>
+      <c r="E74">
+        <v>-0.746268656716418</v>
+      </c>
+      <c r="F74">
+        <v>33.5</v>
+      </c>
+      <c r="G74">
         <v>33.75</v>
       </c>
-      <c r="D74">
-        <v>0.25</v>
-      </c>
-      <c r="E74">
-        <v>0.746268656716418</v>
-      </c>
-      <c r="F74">
-        <v>33.75</v>
-      </c>
-      <c r="G74">
-        <v>34</v>
-      </c>
       <c r="H74">
+        <v>33</v>
+      </c>
+      <c r="I74">
+        <v>374700</v>
+      </c>
+      <c r="J74">
+        <v>12458.775</v>
+      </c>
+      <c r="K74">
+        <v>26462523</v>
+      </c>
+      <c r="L74">
+        <v>882109.52025</v>
+      </c>
+      <c r="M74">
+        <v>3142800</v>
+      </c>
+      <c r="N74">
         <v>33.25</v>
       </c>
-      <c r="I74">
-        <v>0</v>
-      </c>
-      <c r="J74">
-        <v>0</v>
-      </c>
-      <c r="K74">
-        <v>7461410</v>
-      </c>
-      <c r="L74">
-        <v>252144.407</v>
-      </c>
-      <c r="M74">
-        <v>1659400</v>
-      </c>
-      <c r="N74">
-        <v>33.75</v>
-      </c>
       <c r="O74">
-        <v>34</v>
+        <v>33.5</v>
       </c>
       <c r="P74">
-        <v>1891500</v>
+        <v>2900500</v>
       </c>
     </row>
     <row r="75">
@@ -3764,46 +3764,46 @@
         <v>-</v>
       </c>
       <c r="C75">
-        <v>39.75</v>
+        <v>37</v>
       </c>
       <c r="D75">
-        <v>0.5</v>
+        <v>-1.75</v>
       </c>
       <c r="E75">
-        <v>1.2738853503184713</v>
+        <v>-4.516129032258065</v>
       </c>
       <c r="F75">
-        <v>39.25</v>
+        <v>38.75</v>
       </c>
       <c r="G75">
-        <v>39.75</v>
+        <v>39</v>
       </c>
       <c r="H75">
-        <v>39.25</v>
+        <v>36.75</v>
       </c>
       <c r="I75">
-        <v>0</v>
+        <v>519800</v>
       </c>
       <c r="J75">
-        <v>0</v>
+        <v>19232.6</v>
       </c>
       <c r="K75">
-        <v>6228305</v>
+        <v>35140049</v>
       </c>
       <c r="L75">
-        <v>245694.68325</v>
+        <v>1317204.382</v>
       </c>
       <c r="M75">
-        <v>569100</v>
+        <v>1845900</v>
       </c>
       <c r="N75">
-        <v>39.5</v>
+        <v>36.75</v>
       </c>
       <c r="O75">
-        <v>39.75</v>
+        <v>37</v>
       </c>
       <c r="P75">
-        <v>1071900</v>
+        <v>58000</v>
       </c>
     </row>
     <row r="76">
@@ -3814,46 +3814,46 @@
         <v>-</v>
       </c>
       <c r="C76">
+        <v>6.45</v>
+      </c>
+      <c r="D76">
+        <v>-0.05</v>
+      </c>
+      <c r="E76">
+        <v>-0.7692307692307693</v>
+      </c>
+      <c r="F76">
+        <v>6.5</v>
+      </c>
+      <c r="G76">
+        <v>6.5</v>
+      </c>
+      <c r="H76">
         <v>6.4</v>
       </c>
-      <c r="D76">
-        <v>0</v>
-      </c>
-      <c r="E76">
-        <v>0</v>
-      </c>
-      <c r="F76">
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>5084039</v>
+      </c>
+      <c r="L76">
+        <v>32840.1161</v>
+      </c>
+      <c r="M76">
+        <v>1176800</v>
+      </c>
+      <c r="N76">
         <v>6.4</v>
       </c>
-      <c r="G76">
-        <v>6.4</v>
-      </c>
-      <c r="H76">
-        <v>6.3</v>
-      </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76">
-        <v>4133384</v>
-      </c>
-      <c r="L76">
-        <v>26300.593699999998</v>
-      </c>
-      <c r="M76">
-        <v>1034300</v>
-      </c>
-      <c r="N76">
-        <v>6.35</v>
-      </c>
       <c r="O76">
-        <v>6.4</v>
+        <v>6.45</v>
       </c>
       <c r="P76">
-        <v>723800</v>
+        <v>136400</v>
       </c>
     </row>
     <row r="77">
@@ -3864,19 +3864,19 @@
         <v>-</v>
       </c>
       <c r="C77">
-        <v>5.7</v>
+        <v>5.65</v>
       </c>
       <c r="D77">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E77">
-        <v>0</v>
+        <v>-0.8771929824561403</v>
       </c>
       <c r="F77">
-        <v>5.65</v>
+        <v>5.75</v>
       </c>
       <c r="G77">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="H77">
         <v>5.65</v>
@@ -3888,13 +3888,13 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>624747</v>
+        <v>4374247</v>
       </c>
       <c r="L77">
-        <v>3543.2245</v>
+        <v>24894.49825</v>
       </c>
       <c r="M77">
-        <v>286400</v>
+        <v>322000</v>
       </c>
       <c r="N77">
         <v>5.65</v>
@@ -3903,7 +3903,7 @@
         <v>5.7</v>
       </c>
       <c r="P77">
-        <v>229700</v>
+        <v>10500</v>
       </c>
     </row>
     <row r="78">
@@ -3914,19 +3914,19 @@
         <v>-</v>
       </c>
       <c r="C78">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="D78">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="E78">
-        <v>-2.459016393442623</v>
+        <v>0</v>
       </c>
       <c r="F78">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="G78">
-        <v>6.15</v>
+        <v>6.05</v>
       </c>
       <c r="H78">
         <v>5.95</v>
@@ -3938,22 +3938,22 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>1959825</v>
+        <v>1057658</v>
       </c>
       <c r="L78">
-        <v>11793.761</v>
+        <v>6319.468</v>
       </c>
       <c r="M78">
-        <v>537200</v>
+        <v>25100</v>
       </c>
       <c r="N78">
-        <v>5.95</v>
+        <v>6</v>
       </c>
       <c r="O78">
-        <v>6</v>
+        <v>6.05</v>
       </c>
       <c r="P78">
-        <v>118100</v>
+        <v>430700</v>
       </c>
     </row>
     <row r="79">
@@ -3964,46 +3964,46 @@
         <v>-</v>
       </c>
       <c r="C79">
+        <v>22.3</v>
+      </c>
+      <c r="D79">
+        <v>-0.2</v>
+      </c>
+      <c r="E79">
+        <v>-0.8888888888888888</v>
+      </c>
+      <c r="F79">
         <v>22.5</v>
       </c>
-      <c r="D79">
-        <v>0.1</v>
-      </c>
-      <c r="E79">
-        <v>0.44642857142857145</v>
-      </c>
-      <c r="F79">
+      <c r="G79">
+        <v>22.5</v>
+      </c>
+      <c r="H79">
+        <v>22.3</v>
+      </c>
+      <c r="I79">
+        <v>87500</v>
+      </c>
+      <c r="J79">
+        <v>1951.25</v>
+      </c>
+      <c r="K79">
+        <v>10067522</v>
+      </c>
+      <c r="L79">
+        <v>225402.4148</v>
+      </c>
+      <c r="M79">
+        <v>2745000</v>
+      </c>
+      <c r="N79">
+        <v>22.3</v>
+      </c>
+      <c r="O79">
         <v>22.4</v>
       </c>
-      <c r="G79">
-        <v>22.7</v>
-      </c>
-      <c r="H79">
-        <v>22.4</v>
-      </c>
-      <c r="I79">
-        <v>0</v>
-      </c>
-      <c r="J79">
-        <v>0</v>
-      </c>
-      <c r="K79">
-        <v>5808000</v>
-      </c>
-      <c r="L79">
-        <v>131181.3141</v>
-      </c>
-      <c r="M79">
-        <v>1419600</v>
-      </c>
-      <c r="N79">
-        <v>22.5</v>
-      </c>
-      <c r="O79">
-        <v>22.6</v>
-      </c>
       <c r="P79">
-        <v>333500</v>
+        <v>658200</v>
       </c>
     </row>
     <row r="80">
@@ -4014,22 +4014,22 @@
         <v>-</v>
       </c>
       <c r="C80">
-        <v>12.1</v>
+        <v>11.7</v>
       </c>
       <c r="D80">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E80">
-        <v>0.8333333333333334</v>
+        <v>0</v>
       </c>
       <c r="F80">
-        <v>12</v>
+        <v>11.8</v>
       </c>
       <c r="G80">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="H80">
-        <v>11.9</v>
+        <v>11.5</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -4038,22 +4038,22 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>2285421</v>
+        <v>8430180</v>
       </c>
       <c r="L80">
-        <v>27429.3772</v>
+        <v>98138.46029999999</v>
       </c>
       <c r="M80">
-        <v>358100</v>
+        <v>115300</v>
       </c>
       <c r="N80">
-        <v>12</v>
+        <v>11.7</v>
       </c>
       <c r="O80">
-        <v>12.1</v>
+        <v>11.8</v>
       </c>
       <c r="P80">
-        <v>1005200</v>
+        <v>439100</v>
       </c>
     </row>
     <row r="81">
@@ -4064,13 +4064,13 @@
         <v>-</v>
       </c>
       <c r="C81">
-        <v>28.25</v>
+        <v>28.5</v>
       </c>
       <c r="D81">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="E81">
-        <v>-0.8771929824561403</v>
+        <v>0.8849557522123894</v>
       </c>
       <c r="F81">
         <v>28.25</v>
@@ -4079,7 +4079,7 @@
         <v>28.5</v>
       </c>
       <c r="H81">
-        <v>28.25</v>
+        <v>28</v>
       </c>
       <c r="I81">
         <v>0</v>
@@ -4088,13 +4088,13 @@
         <v>0</v>
       </c>
       <c r="K81">
-        <v>1108746</v>
+        <v>5471542</v>
       </c>
       <c r="L81">
-        <v>31330.526</v>
+        <v>154774.204</v>
       </c>
       <c r="M81">
-        <v>639800</v>
+        <v>760700</v>
       </c>
       <c r="N81">
         <v>28.25</v>
@@ -4103,7 +4103,7 @@
         <v>28.5</v>
       </c>
       <c r="P81">
-        <v>1398300</v>
+        <v>714100</v>
       </c>
     </row>
     <row r="82">
@@ -4117,43 +4117,43 @@
         <v>8.9</v>
       </c>
       <c r="D82">
-        <v>0.05</v>
+        <v>-0.1</v>
       </c>
       <c r="E82">
-        <v>0.5649717514124294</v>
+        <v>-1.1111111111111112</v>
       </c>
       <c r="F82">
-        <v>8.85</v>
+        <v>8.9</v>
       </c>
       <c r="G82">
+        <v>9</v>
+      </c>
+      <c r="H82">
+        <v>8.7</v>
+      </c>
+      <c r="I82">
+        <v>0</v>
+      </c>
+      <c r="J82">
+        <v>0</v>
+      </c>
+      <c r="K82">
+        <v>32374692</v>
+      </c>
+      <c r="L82">
+        <v>286589.20310000004</v>
+      </c>
+      <c r="M82">
+        <v>9800</v>
+      </c>
+      <c r="N82">
         <v>8.9</v>
       </c>
-      <c r="H82">
-        <v>8.75</v>
-      </c>
-      <c r="I82">
-        <v>0</v>
-      </c>
-      <c r="J82">
-        <v>0</v>
-      </c>
-      <c r="K82">
-        <v>2808284</v>
-      </c>
-      <c r="L82">
-        <v>24802.80455</v>
-      </c>
-      <c r="M82">
-        <v>984500</v>
-      </c>
-      <c r="N82">
-        <v>8.85</v>
-      </c>
       <c r="O82">
-        <v>8.9</v>
+        <v>8.95</v>
       </c>
       <c r="P82">
-        <v>497700</v>
+        <v>1105600</v>
       </c>
     </row>
     <row r="83">
@@ -4164,22 +4164,22 @@
         <v>-</v>
       </c>
       <c r="C83">
-        <v>9.6</v>
+        <v>9.65</v>
       </c>
       <c r="D83">
-        <v>-0.1</v>
+        <v>0.05</v>
       </c>
       <c r="E83">
-        <v>-1.0309278350515463</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="F83">
-        <v>9.7</v>
+        <v>9.55</v>
       </c>
       <c r="G83">
         <v>9.7</v>
       </c>
       <c r="H83">
-        <v>9.6</v>
+        <v>9.55</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -4188,13 +4188,13 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>17605</v>
+        <v>24233</v>
       </c>
       <c r="L83">
-        <v>169.8885</v>
+        <v>232.7922</v>
       </c>
       <c r="M83">
-        <v>58700</v>
+        <v>20600</v>
       </c>
       <c r="N83">
         <v>9.6</v>
@@ -4203,7 +4203,7 @@
         <v>9.65</v>
       </c>
       <c r="P83">
-        <v>3300</v>
+        <v>11700</v>
       </c>
     </row>
     <row r="84">
@@ -4217,19 +4217,19 @@
         <v>20</v>
       </c>
       <c r="D84">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E84">
-        <v>-0.4975124378109453</v>
+        <v>0.5025125628140703</v>
       </c>
       <c r="F84">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="G84">
         <v>20.1</v>
       </c>
       <c r="H84">
-        <v>19.8</v>
+        <v>19.7</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -4238,22 +4238,22 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>362861</v>
+        <v>1248209</v>
       </c>
       <c r="L84">
-        <v>7246.95</v>
+        <v>24861.0687</v>
       </c>
       <c r="M84">
-        <v>98700</v>
+        <v>73000</v>
       </c>
       <c r="N84">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="O84">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="P84">
-        <v>11900</v>
+        <v>126800</v>
       </c>
     </row>
     <row r="85">
@@ -4267,20 +4267,20 @@
         <v>13.4</v>
       </c>
       <c r="D85">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="E85">
-        <v>1.5151515151515151</v>
+        <v>0.7518796992481203</v>
       </c>
       <c r="F85">
+        <v>13.3</v>
+      </c>
+      <c r="G85">
+        <v>13.4</v>
+      </c>
+      <c r="H85">
         <v>13.2</v>
       </c>
-      <c r="G85">
-        <v>13.5</v>
-      </c>
-      <c r="H85">
-        <v>13.1</v>
-      </c>
       <c r="I85">
         <v>0</v>
       </c>
@@ -4288,22 +4288,22 @@
         <v>0</v>
       </c>
       <c r="K85">
-        <v>931217</v>
+        <v>381025</v>
       </c>
       <c r="L85">
-        <v>12421.3886</v>
+        <v>5083.5905</v>
       </c>
       <c r="M85">
-        <v>61800</v>
+        <v>100100</v>
       </c>
       <c r="N85">
+        <v>13.3</v>
+      </c>
+      <c r="O85">
         <v>13.4</v>
       </c>
-      <c r="O85">
-        <v>13.5</v>
-      </c>
       <c r="P85">
-        <v>854500</v>
+        <v>15200</v>
       </c>
     </row>
     <row r="86">
@@ -4314,46 +4314,46 @@
         <v>-</v>
       </c>
       <c r="C86">
-        <v>16.3</v>
+        <v>16.1</v>
       </c>
       <c r="D86">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E86">
-        <v>0</v>
+        <v>-0.6172839506172839</v>
       </c>
       <c r="F86">
-        <v>16.3</v>
+        <v>16.2</v>
       </c>
       <c r="G86">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="H86">
+        <v>16</v>
+      </c>
+      <c r="I86">
+        <v>0</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>4381392</v>
+      </c>
+      <c r="L86">
+        <v>70741.9954</v>
+      </c>
+      <c r="M86">
+        <v>580600</v>
+      </c>
+      <c r="N86">
+        <v>16.1</v>
+      </c>
+      <c r="O86">
         <v>16.2</v>
       </c>
-      <c r="I86">
-        <v>0</v>
-      </c>
-      <c r="J86">
-        <v>0</v>
-      </c>
-      <c r="K86">
-        <v>1943974</v>
-      </c>
-      <c r="L86">
-        <v>31713.3482</v>
-      </c>
-      <c r="M86">
-        <v>727500</v>
-      </c>
-      <c r="N86">
-        <v>16.2</v>
-      </c>
-      <c r="O86">
-        <v>16.3</v>
-      </c>
       <c r="P86">
-        <v>310000</v>
+        <v>807600</v>
       </c>
     </row>
     <row r="87">
@@ -4364,13 +4364,13 @@
         <v>-</v>
       </c>
       <c r="C87">
-        <v>13.6</v>
+        <v>13.3</v>
       </c>
       <c r="D87">
-        <v>0.2</v>
+        <v>-0.2</v>
       </c>
       <c r="E87">
-        <v>1.492537313432836</v>
+        <v>-1.4814814814814814</v>
       </c>
       <c r="F87">
         <v>13.5</v>
@@ -4379,31 +4379,31 @@
         <v>13.6</v>
       </c>
       <c r="H87">
+        <v>13.3</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>5654769</v>
+      </c>
+      <c r="L87">
+        <v>75620.2913</v>
+      </c>
+      <c r="M87">
+        <v>2709100</v>
+      </c>
+      <c r="N87">
+        <v>13.3</v>
+      </c>
+      <c r="O87">
         <v>13.4</v>
       </c>
-      <c r="I87">
-        <v>0</v>
-      </c>
-      <c r="J87">
-        <v>0</v>
-      </c>
-      <c r="K87">
-        <v>1951340</v>
-      </c>
-      <c r="L87">
-        <v>26309.8622</v>
-      </c>
-      <c r="M87">
-        <v>608000</v>
-      </c>
-      <c r="N87">
-        <v>13.5</v>
-      </c>
-      <c r="O87">
-        <v>13.6</v>
-      </c>
       <c r="P87">
-        <v>1330000</v>
+        <v>528200</v>
       </c>
     </row>
     <row r="88">
@@ -4414,16 +4414,16 @@
         <v>-</v>
       </c>
       <c r="C88">
-        <v>33</v>
+        <v>32.5</v>
       </c>
       <c r="D88">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E88">
-        <v>0</v>
+        <v>-0.7633587786259542</v>
       </c>
       <c r="F88">
-        <v>33</v>
+        <v>32.75</v>
       </c>
       <c r="G88">
         <v>33</v>
@@ -4438,22 +4438,22 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>37092275</v>
+        <v>33729036</v>
       </c>
       <c r="L88">
-        <v>1217492.49675</v>
+        <v>1100507.0125</v>
       </c>
       <c r="M88">
-        <v>13678200</v>
+        <v>13937300</v>
       </c>
       <c r="N88">
+        <v>32.5</v>
+      </c>
+      <c r="O88">
         <v>32.75</v>
       </c>
-      <c r="O88">
-        <v>33</v>
-      </c>
       <c r="P88">
-        <v>10779800</v>
+        <v>1785800</v>
       </c>
     </row>
     <row r="89">
@@ -4464,46 +4464,46 @@
         <v>-</v>
       </c>
       <c r="C89">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D89">
-        <v>-4</v>
+        <v>1</v>
       </c>
       <c r="E89">
-        <v>-2.3529411764705883</v>
+        <v>0.6097560975609756</v>
       </c>
       <c r="F89">
-        <v>169.5</v>
+        <v>164</v>
       </c>
       <c r="G89">
-        <v>169.5</v>
+        <v>165.5</v>
       </c>
       <c r="H89">
+        <v>164</v>
+      </c>
+      <c r="I89">
+        <v>160000</v>
+      </c>
+      <c r="J89">
+        <v>26240</v>
+      </c>
+      <c r="K89">
+        <v>15544249</v>
+      </c>
+      <c r="L89">
+        <v>2560725.5295</v>
+      </c>
+      <c r="M89">
+        <v>810500</v>
+      </c>
+      <c r="N89">
         <v>164.5</v>
       </c>
-      <c r="I89">
-        <v>0</v>
-      </c>
-      <c r="J89">
-        <v>0</v>
-      </c>
-      <c r="K89">
-        <v>20392736</v>
-      </c>
-      <c r="L89">
-        <v>3387949.05</v>
-      </c>
-      <c r="M89">
-        <v>773000</v>
-      </c>
-      <c r="N89">
-        <v>166</v>
-      </c>
       <c r="O89">
-        <v>166.5</v>
+        <v>165</v>
       </c>
       <c r="P89">
-        <v>252600</v>
+        <v>30300</v>
       </c>
     </row>
     <row r="90">
@@ -4514,16 +4514,16 @@
         <v>-</v>
       </c>
       <c r="C90">
-        <v>49.5</v>
+        <v>49.75</v>
       </c>
       <c r="D90">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="E90">
-        <v>-0.5025125628140703</v>
+        <v>0.5050505050505051</v>
       </c>
       <c r="F90">
-        <v>50</v>
+        <v>49.25</v>
       </c>
       <c r="G90">
         <v>50</v>
@@ -4538,13 +4538,13 @@
         <v>0</v>
       </c>
       <c r="K90">
-        <v>3436893</v>
+        <v>9366275</v>
       </c>
       <c r="L90">
-        <v>170335.43975</v>
+        <v>464101.732</v>
       </c>
       <c r="M90">
-        <v>618200</v>
+        <v>1252000</v>
       </c>
       <c r="N90">
         <v>49.5</v>
@@ -4553,7 +4553,7 @@
         <v>49.75</v>
       </c>
       <c r="P90">
-        <v>275200</v>
+        <v>526900</v>
       </c>
     </row>
     <row r="91">
@@ -4564,46 +4564,46 @@
         <v>-</v>
       </c>
       <c r="C91">
-        <v>43.25</v>
+        <v>42.5</v>
       </c>
       <c r="D91">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="E91">
-        <v>0.5813953488372093</v>
+        <v>-0.5847953216374269</v>
       </c>
       <c r="F91">
+        <v>42.5</v>
+      </c>
+      <c r="G91">
         <v>42.75</v>
       </c>
-      <c r="G91">
-        <v>43.25</v>
-      </c>
       <c r="H91">
+        <v>42.25</v>
+      </c>
+      <c r="I91">
+        <v>0</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>2231778</v>
+      </c>
+      <c r="L91">
+        <v>94917.6095</v>
+      </c>
+      <c r="M91">
+        <v>242100</v>
+      </c>
+      <c r="N91">
+        <v>42.5</v>
+      </c>
+      <c r="O91">
         <v>42.75</v>
       </c>
-      <c r="I91">
-        <v>0</v>
-      </c>
-      <c r="J91">
-        <v>0</v>
-      </c>
-      <c r="K91">
-        <v>1069275</v>
-      </c>
-      <c r="L91">
-        <v>45962.1565</v>
-      </c>
-      <c r="M91">
-        <v>169400</v>
-      </c>
-      <c r="N91">
-        <v>43</v>
-      </c>
-      <c r="O91">
-        <v>43.25</v>
-      </c>
       <c r="P91">
-        <v>433700</v>
+        <v>159700</v>
       </c>
     </row>
     <row r="92">
@@ -4617,19 +4617,19 @@
         <v>17.3</v>
       </c>
       <c r="D92">
-        <v>0.5</v>
+        <v>-0.2</v>
       </c>
       <c r="E92">
-        <v>2.9761904761904763</v>
+        <v>-1.1428571428571428</v>
       </c>
       <c r="F92">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="G92">
-        <v>17.3</v>
+        <v>17.6</v>
       </c>
       <c r="H92">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -4638,13 +4638,13 @@
         <v>0</v>
       </c>
       <c r="K92">
-        <v>10289980</v>
+        <v>4053447</v>
       </c>
       <c r="L92">
-        <v>176632.6249</v>
+        <v>70573.511</v>
       </c>
       <c r="M92">
-        <v>82900</v>
+        <v>339300</v>
       </c>
       <c r="N92">
         <v>17.3</v>
@@ -4653,7 +4653,7 @@
         <v>17.4</v>
       </c>
       <c r="P92">
-        <v>1169500</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="93">
@@ -4664,46 +4664,46 @@
         <v>-</v>
       </c>
       <c r="C93">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="D93">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="E93">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F93">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="G93">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="H93">
+        <v>2</v>
+      </c>
+      <c r="I93">
+        <v>0</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>7185045</v>
+      </c>
+      <c r="L93">
+        <v>14467.114300000001</v>
+      </c>
+      <c r="M93">
+        <v>903500</v>
+      </c>
+      <c r="N93">
+        <v>2</v>
+      </c>
+      <c r="O93">
         <v>2.04</v>
       </c>
-      <c r="I93">
-        <v>0</v>
-      </c>
-      <c r="J93">
-        <v>0</v>
-      </c>
-      <c r="K93">
-        <v>23570693</v>
-      </c>
-      <c r="L93">
-        <v>48552.15958</v>
-      </c>
-      <c r="M93">
-        <v>1000</v>
-      </c>
-      <c r="N93">
-        <v>2.06</v>
-      </c>
-      <c r="O93">
-        <v>2.08</v>
-      </c>
       <c r="P93">
-        <v>1344400</v>
+        <v>531000</v>
       </c>
     </row>
     <row r="94">
@@ -4714,46 +4714,46 @@
         <v>-</v>
       </c>
       <c r="C94">
-        <v>26.25</v>
+        <v>25.75</v>
       </c>
       <c r="D94">
-        <v>0.25</v>
+        <v>-0.25</v>
       </c>
       <c r="E94">
-        <v>0.9615384615384616</v>
+        <v>-0.9615384615384616</v>
       </c>
       <c r="F94">
-        <v>26.25</v>
+        <v>26</v>
       </c>
       <c r="G94">
         <v>26.25</v>
       </c>
       <c r="H94">
+        <v>25.5</v>
+      </c>
+      <c r="I94">
+        <v>0</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>681003</v>
+      </c>
+      <c r="L94">
+        <v>17658.303</v>
+      </c>
+      <c r="M94">
+        <v>43900</v>
+      </c>
+      <c r="N94">
         <v>25.75</v>
       </c>
-      <c r="I94">
-        <v>0</v>
-      </c>
-      <c r="J94">
-        <v>0</v>
-      </c>
-      <c r="K94">
-        <v>576701</v>
-      </c>
-      <c r="L94">
-        <v>14949.726</v>
-      </c>
-      <c r="M94">
-        <v>45500</v>
-      </c>
-      <c r="N94">
+      <c r="O94">
         <v>26</v>
       </c>
-      <c r="O94">
-        <v>26.25</v>
-      </c>
       <c r="P94">
-        <v>91200</v>
+        <v>35500</v>
       </c>
     </row>
     <row r="95">
@@ -4764,46 +4764,46 @@
         <v>-</v>
       </c>
       <c r="C95">
+        <v>7.05</v>
+      </c>
+      <c r="D95">
+        <v>-0.2</v>
+      </c>
+      <c r="E95">
+        <v>-2.7586206896551726</v>
+      </c>
+      <c r="F95">
+        <v>7.3</v>
+      </c>
+      <c r="G95">
+        <v>7.3</v>
+      </c>
+      <c r="H95">
+        <v>7</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>2719032</v>
+      </c>
+      <c r="L95">
+        <v>19312.0583</v>
+      </c>
+      <c r="M95">
+        <v>160900</v>
+      </c>
+      <c r="N95">
+        <v>7.05</v>
+      </c>
+      <c r="O95">
         <v>7.1</v>
       </c>
-      <c r="D95">
-        <v>0.1</v>
-      </c>
-      <c r="E95">
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="F95">
-        <v>6.95</v>
-      </c>
-      <c r="G95">
-        <v>7.15</v>
-      </c>
-      <c r="H95">
-        <v>6.95</v>
-      </c>
-      <c r="I95">
-        <v>0</v>
-      </c>
-      <c r="J95">
-        <v>0</v>
-      </c>
-      <c r="K95">
-        <v>3897052</v>
-      </c>
-      <c r="L95">
-        <v>27407.597850000002</v>
-      </c>
-      <c r="M95">
-        <v>31700</v>
-      </c>
-      <c r="N95">
-        <v>7.1</v>
-      </c>
-      <c r="O95">
-        <v>7.15</v>
-      </c>
       <c r="P95">
-        <v>223700</v>
+        <v>91000</v>
       </c>
     </row>
     <row r="96">
@@ -4814,22 +4814,22 @@
         <v>-</v>
       </c>
       <c r="C96">
-        <v>47</v>
+        <v>52.5</v>
       </c>
       <c r="D96">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E96">
-        <v>0</v>
+        <v>6.0606060606060606</v>
       </c>
       <c r="F96">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="G96">
-        <v>47.25</v>
+        <v>52.5</v>
       </c>
       <c r="H96">
-        <v>46.5</v>
+        <v>50</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -4838,22 +4838,22 @@
         <v>0</v>
       </c>
       <c r="K96">
-        <v>175409</v>
+        <v>2552941</v>
       </c>
       <c r="L96">
-        <v>8221.47525</v>
+        <v>131784.8835</v>
       </c>
       <c r="M96">
-        <v>37000</v>
+        <v>33900</v>
       </c>
       <c r="N96">
-        <v>46.75</v>
+        <v>51.75</v>
       </c>
       <c r="O96">
-        <v>47</v>
+        <v>52.5</v>
       </c>
       <c r="P96">
-        <v>17600</v>
+        <v>9300</v>
       </c>
     </row>
     <row r="97">
@@ -4864,46 +4864,46 @@
         <v>-</v>
       </c>
       <c r="C97">
+        <v>21.5</v>
+      </c>
+      <c r="D97">
+        <v>-0.1</v>
+      </c>
+      <c r="E97">
+        <v>-0.46296296296296297</v>
+      </c>
+      <c r="F97">
+        <v>21.6</v>
+      </c>
+      <c r="G97">
+        <v>21.7</v>
+      </c>
+      <c r="H97">
+        <v>21.3</v>
+      </c>
+      <c r="I97">
+        <v>0</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>438245</v>
+      </c>
+      <c r="L97">
+        <v>9425.7183</v>
+      </c>
+      <c r="M97">
+        <v>129000</v>
+      </c>
+      <c r="N97">
         <v>21.4</v>
       </c>
-      <c r="D97">
-        <v>0</v>
-      </c>
-      <c r="E97">
-        <v>0</v>
-      </c>
-      <c r="F97">
+      <c r="O97">
         <v>21.5</v>
       </c>
-      <c r="G97">
-        <v>21.5</v>
-      </c>
-      <c r="H97">
-        <v>21.2</v>
-      </c>
-      <c r="I97">
-        <v>0</v>
-      </c>
-      <c r="J97">
-        <v>0</v>
-      </c>
-      <c r="K97">
-        <v>380833</v>
-      </c>
-      <c r="L97">
-        <v>8121.3893</v>
-      </c>
-      <c r="M97">
-        <v>37800</v>
-      </c>
-      <c r="N97">
-        <v>21.3</v>
-      </c>
-      <c r="O97">
-        <v>21.4</v>
-      </c>
       <c r="P97">
-        <v>23800</v>
+        <v>400</v>
       </c>
     </row>
     <row r="98">
@@ -4914,22 +4914,22 @@
         <v>-</v>
       </c>
       <c r="C98">
-        <v>57.75</v>
+        <v>55.5</v>
       </c>
       <c r="D98">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="E98">
-        <v>0</v>
+        <v>-1.7699115044247788</v>
       </c>
       <c r="F98">
-        <v>57.75</v>
+        <v>56</v>
       </c>
       <c r="G98">
-        <v>58</v>
+        <v>56.5</v>
       </c>
       <c r="H98">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="I98">
         <v>0</v>
@@ -4938,22 +4938,22 @@
         <v>0</v>
       </c>
       <c r="K98">
-        <v>3911064</v>
+        <v>10005330</v>
       </c>
       <c r="L98">
-        <v>224982.16525</v>
+        <v>555531.02575</v>
       </c>
       <c r="M98">
-        <v>329900</v>
+        <v>289500</v>
       </c>
       <c r="N98">
-        <v>57.5</v>
+        <v>55.25</v>
       </c>
       <c r="O98">
-        <v>57.75</v>
+        <v>55.5</v>
       </c>
       <c r="P98">
-        <v>218900</v>
+        <v>33800</v>
       </c>
     </row>
     <row r="99">
@@ -4964,19 +4964,19 @@
         <v>-</v>
       </c>
       <c r="C99">
+        <v>4.64</v>
+      </c>
+      <c r="D99">
+        <v>0.04</v>
+      </c>
+      <c r="E99">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="F99">
+        <v>4.62</v>
+      </c>
+      <c r="G99">
         <v>4.7</v>
-      </c>
-      <c r="D99">
-        <v>0.02</v>
-      </c>
-      <c r="E99">
-        <v>0.42735042735042733</v>
-      </c>
-      <c r="F99">
-        <v>4.72</v>
-      </c>
-      <c r="G99">
-        <v>4.72</v>
       </c>
       <c r="H99">
         <v>4.62</v>
@@ -4988,22 +4988,22 @@
         <v>0</v>
       </c>
       <c r="K99">
-        <v>4342886</v>
+        <v>6508767</v>
       </c>
       <c r="L99">
-        <v>20281.8805</v>
+        <v>30310.22646</v>
       </c>
       <c r="M99">
-        <v>206600</v>
+        <v>228200</v>
       </c>
       <c r="N99">
-        <v>4.68</v>
+        <v>4.64</v>
       </c>
       <c r="O99">
-        <v>4.7</v>
+        <v>4.66</v>
       </c>
       <c r="P99">
-        <v>353900</v>
+        <v>13200</v>
       </c>
     </row>
     <row r="100">
@@ -5014,46 +5014,46 @@
         <v>-</v>
       </c>
       <c r="C100">
-        <v>104.5</v>
+        <v>103.5</v>
       </c>
       <c r="D100">
         <v>-0.5</v>
       </c>
       <c r="E100">
-        <v>-0.47619047619047616</v>
+        <v>-0.4807692307692308</v>
       </c>
       <c r="F100">
-        <v>105</v>
+        <v>103.5</v>
       </c>
       <c r="G100">
-        <v>105.5</v>
+        <v>104</v>
       </c>
       <c r="H100">
-        <v>104.5</v>
+        <v>102.5</v>
       </c>
       <c r="I100">
-        <v>0</v>
+        <v>30400</v>
       </c>
       <c r="J100">
-        <v>0</v>
+        <v>3146.4</v>
       </c>
       <c r="K100">
-        <v>684901</v>
+        <v>7684973</v>
       </c>
       <c r="L100">
-        <v>71852.403</v>
+        <v>791786.1195</v>
       </c>
       <c r="M100">
-        <v>1115600</v>
+        <v>639400</v>
       </c>
       <c r="N100">
-        <v>104.5</v>
+        <v>103</v>
       </c>
       <c r="O100">
-        <v>105</v>
+        <v>103.5</v>
       </c>
       <c r="P100">
-        <v>1364400</v>
+        <v>169900</v>
       </c>
     </row>
     <row r="101">
@@ -5064,46 +5064,46 @@
         <v>-</v>
       </c>
       <c r="C101">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D101">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101">
-        <v>0.2958579881656805</v>
+        <v>0.5952380952380952</v>
       </c>
       <c r="F101">
         <v>337</v>
       </c>
       <c r="G101">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H101">
+        <v>336</v>
+      </c>
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>2304687</v>
+      </c>
+      <c r="L101">
+        <v>778502.554</v>
+      </c>
+      <c r="M101">
+        <v>487000</v>
+      </c>
+      <c r="N101">
         <v>337</v>
       </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>1875224</v>
-      </c>
-      <c r="L101">
-        <v>634175.786</v>
-      </c>
-      <c r="M101">
-        <v>111400</v>
-      </c>
-      <c r="N101">
+      <c r="O101">
         <v>338</v>
       </c>
-      <c r="O101">
-        <v>339</v>
-      </c>
       <c r="P101">
-        <v>98600</v>
+        <v>211800</v>
       </c>
     </row>
     <row r="102">
@@ -5114,22 +5114,22 @@
         <v>-</v>
       </c>
       <c r="C102">
-        <v>159</v>
+        <v>157.5</v>
       </c>
       <c r="D102">
-        <v>-0.5</v>
+        <v>-1</v>
       </c>
       <c r="E102">
-        <v>-0.31347962382445144</v>
+        <v>-0.6309148264984227</v>
       </c>
       <c r="F102">
-        <v>160.5</v>
+        <v>158.5</v>
       </c>
       <c r="G102">
-        <v>160.5</v>
+        <v>158.5</v>
       </c>
       <c r="H102">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="I102">
         <v>0</v>
@@ -5138,22 +5138,22 @@
         <v>0</v>
       </c>
       <c r="K102">
-        <v>173063</v>
+        <v>417258</v>
       </c>
       <c r="L102">
-        <v>27487.9135</v>
+        <v>65712.735</v>
       </c>
       <c r="M102">
-        <v>500</v>
+        <v>14800</v>
       </c>
       <c r="N102">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="O102">
-        <v>159.5</v>
+        <v>157.5</v>
       </c>
       <c r="P102">
-        <v>1600</v>
+        <v>62400</v>
       </c>
     </row>
     <row r="103">
@@ -5167,10 +5167,10 @@
         <v>53.5</v>
       </c>
       <c r="D103">
-        <v>0.25</v>
+        <v>0</v>
       </c>
       <c r="E103">
-        <v>0.4694835680751174</v>
+        <v>0</v>
       </c>
       <c r="F103">
         <v>53.5</v>
@@ -5179,22 +5179,22 @@
         <v>53.75</v>
       </c>
       <c r="H103">
-        <v>53.25</v>
+        <v>53</v>
       </c>
       <c r="I103">
-        <v>0</v>
+        <v>17500</v>
       </c>
       <c r="J103">
-        <v>0</v>
+        <v>936.25</v>
       </c>
       <c r="K103">
-        <v>1702870</v>
+        <v>5797609</v>
       </c>
       <c r="L103">
-        <v>91093.57375</v>
+        <v>309590.9925</v>
       </c>
       <c r="M103">
-        <v>739000</v>
+        <v>199300</v>
       </c>
       <c r="N103">
         <v>53.25</v>
@@ -5203,7 +5203,7 @@
         <v>53.5</v>
       </c>
       <c r="P103">
-        <v>609700</v>
+        <v>145700</v>
       </c>
     </row>
     <row r="104">
@@ -5217,43 +5217,43 @@
         <v>4.44</v>
       </c>
       <c r="D104">
-        <v>0</v>
+        <v>-0.06</v>
       </c>
       <c r="E104">
-        <v>0</v>
+        <v>-1.3333333333333333</v>
       </c>
       <c r="F104">
+        <v>4.48</v>
+      </c>
+      <c r="G104">
+        <v>4.5</v>
+      </c>
+      <c r="H104">
+        <v>4.4</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>8944234</v>
+      </c>
+      <c r="L104">
+        <v>39711.11982</v>
+      </c>
+      <c r="M104">
+        <v>315100</v>
+      </c>
+      <c r="N104">
+        <v>4.42</v>
+      </c>
+      <c r="O104">
         <v>4.44</v>
       </c>
-      <c r="G104">
-        <v>4.48</v>
-      </c>
-      <c r="H104">
-        <v>4.42</v>
-      </c>
-      <c r="I104">
-        <v>0</v>
-      </c>
-      <c r="J104">
-        <v>0</v>
-      </c>
-      <c r="K104">
-        <v>4074800</v>
-      </c>
-      <c r="L104">
-        <v>18138.34</v>
-      </c>
-      <c r="M104">
-        <v>352000</v>
-      </c>
-      <c r="N104">
-        <v>4.44</v>
-      </c>
-      <c r="O104">
-        <v>4.46</v>
-      </c>
       <c r="P104">
-        <v>113500</v>
+        <v>207900</v>
       </c>
     </row>
     <row r="105">
@@ -5267,10 +5267,10 @@
         <v>1.92</v>
       </c>
       <c r="D105">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="E105">
-        <v>2.6737967914438503</v>
+        <v>3.225806451612903</v>
       </c>
       <c r="F105">
         <v>1.88</v>
@@ -5279,7 +5279,7 @@
         <v>1.92</v>
       </c>
       <c r="H105">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="I105">
         <v>0</v>
@@ -5288,13 +5288,13 @@
         <v>0</v>
       </c>
       <c r="K105">
-        <v>226707199</v>
+        <v>249162219</v>
       </c>
       <c r="L105">
-        <v>431382.65508999996</v>
+        <v>473339.7729</v>
       </c>
       <c r="M105">
-        <v>7505100</v>
+        <v>4313100</v>
       </c>
       <c r="N105">
         <v>1.91</v>
@@ -5303,7 +5303,7 @@
         <v>1.92</v>
       </c>
       <c r="P105">
-        <v>8244100</v>
+        <v>655500</v>
       </c>
     </row>
     <row r="106">
@@ -5314,37 +5314,37 @@
         <v>-</v>
       </c>
       <c r="C106">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="D106">
-        <v>-0.1</v>
+        <v>0.1</v>
       </c>
       <c r="E106">
-        <v>-0.684931506849315</v>
+        <v>0.6896551724137931</v>
       </c>
       <c r="F106">
-        <v>14.4</v>
+        <v>14.6</v>
       </c>
       <c r="G106">
         <v>14.6</v>
       </c>
       <c r="H106">
-        <v>14.4</v>
+        <v>14.5</v>
       </c>
       <c r="I106">
-        <v>0</v>
+        <v>95000</v>
       </c>
       <c r="J106">
-        <v>0</v>
+        <v>1385.1</v>
       </c>
       <c r="K106">
-        <v>88451</v>
+        <v>373800</v>
       </c>
       <c r="L106">
-        <v>1281.78</v>
+        <v>5449.58</v>
       </c>
       <c r="M106">
-        <v>8800</v>
+        <v>171300</v>
       </c>
       <c r="N106">
         <v>14.5</v>
@@ -5353,7 +5353,7 @@
         <v>14.6</v>
       </c>
       <c r="P106">
-        <v>232500</v>
+        <v>142700</v>
       </c>
     </row>
     <row r="107">
@@ -5364,19 +5364,19 @@
         <v>-</v>
       </c>
       <c r="C107">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="D107">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E107">
-        <v>0.4132231404958678</v>
+        <v>1.2396694214876034</v>
       </c>
       <c r="F107">
-        <v>24.3</v>
+        <v>24.4</v>
       </c>
       <c r="G107">
-        <v>24.4</v>
+        <v>24.7</v>
       </c>
       <c r="H107">
         <v>24.1</v>
@@ -5388,22 +5388,22 @@
         <v>0</v>
       </c>
       <c r="K107">
-        <v>1274520</v>
+        <v>17117094</v>
       </c>
       <c r="L107">
-        <v>30903.6704</v>
+        <v>418845.7735</v>
       </c>
       <c r="M107">
-        <v>129900</v>
+        <v>443500</v>
       </c>
       <c r="N107">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="O107">
-        <v>24.4</v>
+        <v>24.6</v>
       </c>
       <c r="P107">
-        <v>232900</v>
+        <v>289200</v>
       </c>
     </row>
     <row r="108">
@@ -5414,22 +5414,22 @@
         <v>-</v>
       </c>
       <c r="C108">
-        <v>22.5</v>
+        <v>23.4</v>
       </c>
       <c r="D108">
-        <v>-0.2</v>
+        <v>0.8</v>
       </c>
       <c r="E108">
-        <v>-0.8810572687224669</v>
+        <v>3.5398230088495577</v>
       </c>
       <c r="F108">
-        <v>22.4</v>
+        <v>22.6</v>
       </c>
       <c r="G108">
-        <v>22.7</v>
+        <v>23.6</v>
       </c>
       <c r="H108">
-        <v>22.2</v>
+        <v>22.6</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -5438,22 +5438,22 @@
         <v>0</v>
       </c>
       <c r="K108">
-        <v>3373962</v>
+        <v>17792391</v>
       </c>
       <c r="L108">
-        <v>75963.40740000001</v>
+        <v>410653.2648</v>
       </c>
       <c r="M108">
-        <v>371100</v>
+        <v>371800</v>
       </c>
       <c r="N108">
-        <v>22.5</v>
+        <v>23.3</v>
       </c>
       <c r="O108">
-        <v>22.6</v>
+        <v>23.4</v>
       </c>
       <c r="P108">
-        <v>127500</v>
+        <v>22700</v>
       </c>
     </row>
     <row r="109">
@@ -5464,22 +5464,22 @@
         <v>-</v>
       </c>
       <c r="C109">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="D109">
-        <v>-0.1</v>
+        <v>0.3</v>
       </c>
       <c r="E109">
-        <v>-0.8771929824561403</v>
+        <v>2.7027027027027026</v>
       </c>
       <c r="F109">
-        <v>11.4</v>
+        <v>11.1</v>
       </c>
       <c r="G109">
         <v>11.6</v>
       </c>
       <c r="H109">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -5488,22 +5488,22 @@
         <v>0</v>
       </c>
       <c r="K109">
-        <v>13236816</v>
+        <v>26522526</v>
       </c>
       <c r="L109">
-        <v>150250.6619</v>
+        <v>302055.1235</v>
       </c>
       <c r="M109">
-        <v>847700</v>
+        <v>1124000</v>
       </c>
       <c r="N109">
-        <v>11.2</v>
+        <v>11.4</v>
       </c>
       <c r="O109">
-        <v>11.3</v>
+        <v>11.5</v>
       </c>
       <c r="P109">
-        <v>280100</v>
+        <v>556600</v>
       </c>
     </row>
     <row r="110">
@@ -5514,22 +5514,22 @@
         <v>-</v>
       </c>
       <c r="C110">
-        <v>16.7</v>
+        <v>17.1</v>
       </c>
       <c r="D110">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="E110">
-        <v>1.2121212121212122</v>
+        <v>0</v>
       </c>
       <c r="F110">
-        <v>16.4</v>
+        <v>17.2</v>
       </c>
       <c r="G110">
-        <v>16.7</v>
+        <v>17.6</v>
       </c>
       <c r="H110">
-        <v>16.4</v>
+        <v>17</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -5538,22 +5538,22 @@
         <v>0</v>
       </c>
       <c r="K110">
-        <v>917273</v>
+        <v>6475566</v>
       </c>
       <c r="L110">
-        <v>15234.4586</v>
+        <v>112298.1049</v>
       </c>
       <c r="M110">
-        <v>81100</v>
+        <v>9600</v>
       </c>
       <c r="N110">
-        <v>16.6</v>
+        <v>17.1</v>
       </c>
       <c r="O110">
-        <v>16.7</v>
+        <v>17.2</v>
       </c>
       <c r="P110">
-        <v>128600</v>
+        <v>203200</v>
       </c>
     </row>
     <row r="111">
@@ -5564,22 +5564,22 @@
         <v>-</v>
       </c>
       <c r="C111">
-        <v>4.16</v>
+        <v>4.06</v>
       </c>
       <c r="D111">
-        <v>-0.04</v>
+        <v>-0.06</v>
       </c>
       <c r="E111">
-        <v>-0.9523809523809523</v>
+        <v>-1.4563106796116505</v>
       </c>
       <c r="F111">
-        <v>4.18</v>
+        <v>4.1</v>
       </c>
       <c r="G111">
-        <v>4.18</v>
+        <v>4.12</v>
       </c>
       <c r="H111">
-        <v>4.14</v>
+        <v>4.06</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -5588,22 +5588,22 @@
         <v>0</v>
       </c>
       <c r="K111">
-        <v>3563910</v>
+        <v>18301546</v>
       </c>
       <c r="L111">
-        <v>14837.03822</v>
+        <v>74524.31034</v>
       </c>
       <c r="M111">
-        <v>922200</v>
+        <v>2654200</v>
       </c>
       <c r="N111">
-        <v>4.14</v>
+        <v>4.06</v>
       </c>
       <c r="O111">
-        <v>4.16</v>
+        <v>4.08</v>
       </c>
       <c r="P111">
-        <v>445500</v>
+        <v>499100</v>
       </c>
     </row>
     <row r="112">
@@ -5614,22 +5614,22 @@
         <v>-</v>
       </c>
       <c r="C112">
+        <v>16.1</v>
+      </c>
+      <c r="D112">
+        <v>0</v>
+      </c>
+      <c r="E112">
+        <v>0</v>
+      </c>
+      <c r="F112">
+        <v>16.1</v>
+      </c>
+      <c r="G112">
         <v>16.2</v>
       </c>
-      <c r="D112">
-        <v>0.1</v>
-      </c>
-      <c r="E112">
-        <v>0.6211180124223602</v>
-      </c>
-      <c r="F112">
-        <v>16.2</v>
-      </c>
-      <c r="G112">
-        <v>16.3</v>
-      </c>
       <c r="H112">
-        <v>16</v>
+        <v>15.9</v>
       </c>
       <c r="I112">
         <v>0</v>
@@ -5638,13 +5638,13 @@
         <v>0</v>
       </c>
       <c r="K112">
-        <v>2458468</v>
+        <v>5819119</v>
       </c>
       <c r="L112">
-        <v>39842.401600000005</v>
+        <v>93254.035</v>
       </c>
       <c r="M112">
-        <v>339400</v>
+        <v>71300</v>
       </c>
       <c r="N112">
         <v>16.1</v>
@@ -5653,7 +5653,7 @@
         <v>16.2</v>
       </c>
       <c r="P112">
-        <v>115300</v>
+        <v>308200</v>
       </c>
     </row>
     <row r="113">
@@ -5664,46 +5664,46 @@
         <v>-</v>
       </c>
       <c r="C113">
-        <v>101.5</v>
+        <v>102.5</v>
       </c>
       <c r="D113">
         <v>-0.5</v>
       </c>
       <c r="E113">
-        <v>-0.49019607843137253</v>
+        <v>-0.4854368932038835</v>
       </c>
       <c r="F113">
+        <v>103</v>
+      </c>
+      <c r="G113">
+        <v>103</v>
+      </c>
+      <c r="H113">
         <v>102</v>
       </c>
-      <c r="G113">
+      <c r="I113">
+        <v>0</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>3757061</v>
+      </c>
+      <c r="L113">
+        <v>385313.0485</v>
+      </c>
+      <c r="M113">
+        <v>312300</v>
+      </c>
+      <c r="N113">
         <v>102.5</v>
       </c>
-      <c r="H113">
-        <v>101.5</v>
-      </c>
-      <c r="I113">
-        <v>0</v>
-      </c>
-      <c r="J113">
-        <v>0</v>
-      </c>
-      <c r="K113">
-        <v>806699</v>
-      </c>
-      <c r="L113">
-        <v>82012.9315</v>
-      </c>
-      <c r="M113">
-        <v>368100</v>
-      </c>
-      <c r="N113">
-        <v>101.5</v>
-      </c>
       <c r="O113">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P113">
-        <v>357500</v>
+        <v>1323400</v>
       </c>
     </row>
     <row r="114">
@@ -5714,46 +5714,46 @@
         <v>-</v>
       </c>
       <c r="C114">
+        <v>13.4</v>
+      </c>
+      <c r="D114">
+        <v>-0.2</v>
+      </c>
+      <c r="E114">
+        <v>-1.4705882352941178</v>
+      </c>
+      <c r="F114">
         <v>13.6</v>
       </c>
-      <c r="D114">
-        <v>-0.1</v>
-      </c>
-      <c r="E114">
-        <v>-0.7299270072992701</v>
-      </c>
-      <c r="F114">
-        <v>13.7</v>
-      </c>
       <c r="G114">
-        <v>13.8</v>
+        <v>13.6</v>
       </c>
       <c r="H114">
+        <v>13.3</v>
+      </c>
+      <c r="I114">
+        <v>0</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>1934281</v>
+      </c>
+      <c r="L114">
+        <v>26024.160399999997</v>
+      </c>
+      <c r="M114">
+        <v>275600</v>
+      </c>
+      <c r="N114">
+        <v>13.4</v>
+      </c>
+      <c r="O114">
         <v>13.5</v>
       </c>
-      <c r="I114">
-        <v>0</v>
-      </c>
-      <c r="J114">
-        <v>0</v>
-      </c>
-      <c r="K114">
-        <v>1197110</v>
-      </c>
-      <c r="L114">
-        <v>16235.2397</v>
-      </c>
-      <c r="M114">
-        <v>322400</v>
-      </c>
-      <c r="N114">
-        <v>13.5</v>
-      </c>
-      <c r="O114">
-        <v>13.6</v>
-      </c>
       <c r="P114">
-        <v>347200</v>
+        <v>137500</v>
       </c>
     </row>
     <row r="115">
@@ -5773,10 +5773,10 @@
         <v>0</v>
       </c>
       <c r="F115">
-        <v>8.2</v>
+        <v>8.25</v>
       </c>
       <c r="G115">
-        <v>8.2</v>
+        <v>8.25</v>
       </c>
       <c r="H115">
         <v>8.1</v>
@@ -5788,13 +5788,13 @@
         <v>0</v>
       </c>
       <c r="K115">
-        <v>122799</v>
+        <v>121777</v>
       </c>
       <c r="L115">
-        <v>1001.0569</v>
+        <v>995.21645</v>
       </c>
       <c r="M115">
-        <v>7300</v>
+        <v>12100</v>
       </c>
       <c r="N115">
         <v>8.15</v>
@@ -5803,7 +5803,7 @@
         <v>8.2</v>
       </c>
       <c r="P115">
-        <v>74200</v>
+        <v>28700</v>
       </c>
     </row>
     <row r="116">
@@ -5814,22 +5814,22 @@
         <v>-</v>
       </c>
       <c r="C116">
-        <v>34.5</v>
+        <v>34.25</v>
       </c>
       <c r="D116">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E116">
-        <v>0</v>
+        <v>-1.4388489208633093</v>
       </c>
       <c r="F116">
-        <v>35</v>
+        <v>34.75</v>
       </c>
       <c r="G116">
-        <v>35</v>
+        <v>34.75</v>
       </c>
       <c r="H116">
-        <v>33.75</v>
+        <v>34.25</v>
       </c>
       <c r="I116">
         <v>0</v>
@@ -5838,13 +5838,13 @@
         <v>0</v>
       </c>
       <c r="K116">
-        <v>216028</v>
+        <v>308244</v>
       </c>
       <c r="L116">
-        <v>7386.74775</v>
+        <v>10609.06925</v>
       </c>
       <c r="M116">
-        <v>11000</v>
+        <v>21600</v>
       </c>
       <c r="N116">
         <v>34.25</v>
@@ -5853,7 +5853,7 @@
         <v>34.5</v>
       </c>
       <c r="P116">
-        <v>24200</v>
+        <v>10800</v>
       </c>
     </row>
     <row r="117">
@@ -5864,16 +5864,16 @@
         <v>-</v>
       </c>
       <c r="C117">
-        <v>57.25</v>
+        <v>57</v>
       </c>
       <c r="D117">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E117">
-        <v>-0.8658008658008658</v>
+        <v>-0.4366812227074236</v>
       </c>
       <c r="F117">
-        <v>57.75</v>
+        <v>57.5</v>
       </c>
       <c r="G117">
         <v>58</v>
@@ -5888,13 +5888,13 @@
         <v>0</v>
       </c>
       <c r="K117">
-        <v>7565247</v>
+        <v>9125904</v>
       </c>
       <c r="L117">
-        <v>432750.8315</v>
+        <v>523788.4305</v>
       </c>
       <c r="M117">
-        <v>467600</v>
+        <v>10400</v>
       </c>
       <c r="N117">
         <v>57</v>
@@ -5903,7 +5903,7 @@
         <v>57.25</v>
       </c>
       <c r="P117">
-        <v>722600</v>
+        <v>552800</v>
       </c>
     </row>
     <row r="118">
@@ -5914,46 +5914,46 @@
         <v>-</v>
       </c>
       <c r="C118">
+        <v>1.82</v>
+      </c>
+      <c r="D118">
+        <v>-0.02</v>
+      </c>
+      <c r="E118">
+        <v>-1.0869565217391304</v>
+      </c>
+      <c r="F118">
         <v>1.84</v>
       </c>
-      <c r="D118">
-        <v>0</v>
-      </c>
-      <c r="E118">
-        <v>0</v>
-      </c>
-      <c r="F118">
-        <v>1.85</v>
-      </c>
       <c r="G118">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H118">
+        <v>1.82</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>8860867</v>
+      </c>
+      <c r="L118">
+        <v>16172.160240000001</v>
+      </c>
+      <c r="M118">
+        <v>1316800</v>
+      </c>
+      <c r="N118">
+        <v>1.82</v>
+      </c>
+      <c r="O118">
         <v>1.83</v>
       </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>2120114</v>
-      </c>
-      <c r="L118">
-        <v>3904.23944</v>
-      </c>
-      <c r="M118">
-        <v>810000</v>
-      </c>
-      <c r="N118">
-        <v>1.84</v>
-      </c>
-      <c r="O118">
-        <v>1.85</v>
-      </c>
       <c r="P118">
-        <v>1211000</v>
+        <v>6000</v>
       </c>
     </row>
     <row r="119">
@@ -5964,22 +5964,22 @@
         <v>-</v>
       </c>
       <c r="C119">
-        <v>3.52</v>
+        <v>3.5</v>
       </c>
       <c r="D119">
-        <v>0</v>
+        <v>-0.02</v>
       </c>
       <c r="E119">
-        <v>0</v>
+        <v>-0.5681818181818182</v>
       </c>
       <c r="F119">
         <v>3.52</v>
       </c>
       <c r="G119">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="H119">
-        <v>3.5</v>
+        <v>3.48</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -5988,13 +5988,13 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>2151686</v>
+        <v>9303552</v>
       </c>
       <c r="L119">
-        <v>7572.23112</v>
+        <v>32598.451719999997</v>
       </c>
       <c r="M119">
-        <v>2907100</v>
+        <v>958200</v>
       </c>
       <c r="N119">
         <v>3.5</v>
@@ -6003,7 +6003,7 @@
         <v>3.52</v>
       </c>
       <c r="P119">
-        <v>115000</v>
+        <v>1220600</v>
       </c>
     </row>
     <row r="120">
@@ -6017,16 +6017,16 @@
         <v>42.75</v>
       </c>
       <c r="D120">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E120">
-        <v>0</v>
+        <v>-1.1560693641618498</v>
       </c>
       <c r="F120">
-        <v>42.5</v>
+        <v>43.25</v>
       </c>
       <c r="G120">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="H120">
         <v>42.5</v>
@@ -6038,22 +6038,22 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>1085905</v>
+        <v>1743121</v>
       </c>
       <c r="L120">
-        <v>46402.03925</v>
+        <v>75207.92425</v>
       </c>
       <c r="M120">
-        <v>267900</v>
+        <v>136700</v>
       </c>
       <c r="N120">
-        <v>42.5</v>
+        <v>42.75</v>
       </c>
       <c r="O120">
-        <v>42.75</v>
+        <v>43</v>
       </c>
       <c r="P120">
-        <v>52100</v>
+        <v>152000</v>
       </c>
     </row>
     <row r="121">
@@ -6064,22 +6064,22 @@
         <v>-</v>
       </c>
       <c r="C121">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="D121">
-        <v>-0.01</v>
+        <v>0.01</v>
       </c>
       <c r="E121">
-        <v>-0.8264462809917356</v>
+        <v>0.8620689655172413</v>
       </c>
       <c r="F121">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="G121">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="H121">
-        <v>1.2</v>
+        <v>1.15</v>
       </c>
       <c r="I121">
         <v>0</v>
@@ -6088,22 +6088,22 @@
         <v>0</v>
       </c>
       <c r="K121">
-        <v>1779100</v>
+        <v>2418600</v>
       </c>
       <c r="L121">
-        <v>2153.838</v>
+        <v>2811.27308</v>
       </c>
       <c r="M121">
-        <v>779800</v>
+        <v>213000</v>
       </c>
       <c r="N121">
-        <v>1.2</v>
+        <v>1.16</v>
       </c>
       <c r="O121">
-        <v>1.21</v>
+        <v>1.17</v>
       </c>
       <c r="P121">
-        <v>339700</v>
+        <v>183700</v>
       </c>
     </row>
     <row r="122">
@@ -6123,37 +6123,37 @@
         <v>0.6211180124223602</v>
       </c>
       <c r="F122">
-        <v>8.1</v>
+        <v>8.05</v>
       </c>
       <c r="G122">
         <v>8.15</v>
       </c>
       <c r="H122">
+        <v>8</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>3759691</v>
+      </c>
+      <c r="L122">
+        <v>30312.5005</v>
+      </c>
+      <c r="M122">
+        <v>178500</v>
+      </c>
+      <c r="N122">
         <v>8.05</v>
       </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>1728396</v>
-      </c>
-      <c r="L122">
-        <v>14003.966849999999</v>
-      </c>
-      <c r="M122">
-        <v>458900</v>
-      </c>
-      <c r="N122">
+      <c r="O122">
         <v>8.1</v>
       </c>
-      <c r="O122">
-        <v>8.15</v>
-      </c>
       <c r="P122">
-        <v>449900</v>
+        <v>88100</v>
       </c>
     </row>
     <row r="123">
@@ -6164,22 +6164,22 @@
         <v>-</v>
       </c>
       <c r="C123">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="D123">
-        <v>0.01</v>
+        <v>-0.03</v>
       </c>
       <c r="E123">
-        <v>0.6896551724137931</v>
+        <v>-2.0689655172413794</v>
       </c>
       <c r="F123">
+        <v>1.44</v>
+      </c>
+      <c r="G123">
         <v>1.45</v>
       </c>
-      <c r="G123">
-        <v>1.46</v>
-      </c>
       <c r="H123">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="I123">
         <v>0</v>
@@ -6188,22 +6188,22 @@
         <v>0</v>
       </c>
       <c r="K123">
-        <v>125265315</v>
+        <v>194236716</v>
       </c>
       <c r="L123">
-        <v>181621.13614</v>
+        <v>276844.8389</v>
       </c>
       <c r="M123">
-        <v>9969700</v>
+        <v>17077300</v>
       </c>
       <c r="N123">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="O123">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="P123">
-        <v>66108700</v>
+        <v>21403900</v>
       </c>
     </row>
     <row r="124">
@@ -6214,19 +6214,19 @@
         <v>-</v>
       </c>
       <c r="C124">
-        <v>9.45</v>
+        <v>9.7</v>
       </c>
       <c r="D124">
-        <v>-0.05</v>
+        <v>0.25</v>
       </c>
       <c r="E124">
-        <v>-0.5263157894736842</v>
+        <v>2.6455026455026456</v>
       </c>
       <c r="F124">
         <v>9.5</v>
       </c>
       <c r="G124">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="H124">
         <v>9.45</v>
@@ -6238,22 +6238,22 @@
         <v>0</v>
       </c>
       <c r="K124">
-        <v>405870</v>
+        <v>6681864</v>
       </c>
       <c r="L124">
-        <v>3851.97785</v>
+        <v>64244.430799999995</v>
       </c>
       <c r="M124">
-        <v>969000</v>
+        <v>30400</v>
       </c>
       <c r="N124">
-        <v>9.45</v>
+        <v>9.65</v>
       </c>
       <c r="O124">
-        <v>9.5</v>
+        <v>9.7</v>
       </c>
       <c r="P124">
-        <v>259600</v>
+        <v>23400</v>
       </c>
     </row>
     <row r="125">
@@ -6264,46 +6264,46 @@
         <v>-</v>
       </c>
       <c r="C125">
-        <v>29.25</v>
+        <v>28.75</v>
       </c>
       <c r="D125">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E125">
-        <v>0</v>
+        <v>-0.8620689655172413</v>
       </c>
       <c r="F125">
-        <v>29.25</v>
+        <v>29</v>
       </c>
       <c r="G125">
         <v>29.25</v>
       </c>
       <c r="H125">
+        <v>28.75</v>
+      </c>
+      <c r="I125">
+        <v>0</v>
+      </c>
+      <c r="J125">
+        <v>0</v>
+      </c>
+      <c r="K125">
+        <v>298190</v>
+      </c>
+      <c r="L125">
+        <v>8600.59175</v>
+      </c>
+      <c r="M125">
+        <v>1106000</v>
+      </c>
+      <c r="N125">
+        <v>28.75</v>
+      </c>
+      <c r="O125">
         <v>29</v>
       </c>
-      <c r="I125">
-        <v>0</v>
-      </c>
-      <c r="J125">
-        <v>0</v>
-      </c>
-      <c r="K125">
-        <v>205476</v>
-      </c>
-      <c r="L125">
-        <v>5990.7045</v>
-      </c>
-      <c r="M125">
-        <v>476300</v>
-      </c>
-      <c r="N125">
-        <v>29</v>
-      </c>
-      <c r="O125">
-        <v>29.25</v>
-      </c>
       <c r="P125">
-        <v>739100</v>
+        <v>64100</v>
       </c>
     </row>
     <row r="126">
@@ -6314,22 +6314,22 @@
         <v>-</v>
       </c>
       <c r="C126">
-        <v>5.05</v>
+        <v>4.98</v>
       </c>
       <c r="D126">
-        <v>0.05</v>
+        <v>-0.02</v>
       </c>
       <c r="E126">
-        <v>1</v>
+        <v>-0.4</v>
       </c>
       <c r="F126">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="G126">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="H126">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="I126">
         <v>0</v>
@@ -6338,22 +6338,22 @@
         <v>0</v>
       </c>
       <c r="K126">
-        <v>3269449</v>
+        <v>16941119</v>
       </c>
       <c r="L126">
-        <v>16503.29105</v>
+        <v>83955.83691</v>
       </c>
       <c r="M126">
-        <v>1750200</v>
+        <v>539000</v>
       </c>
       <c r="N126">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="O126">
-        <v>5.05</v>
+        <v>4.98</v>
       </c>
       <c r="P126">
-        <v>1150100</v>
+        <v>552300</v>
       </c>
     </row>
     <row r="127">
@@ -6364,22 +6364,22 @@
         <v>-</v>
       </c>
       <c r="C127">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="D127">
-        <v>-0.04</v>
+        <v>-0.02</v>
       </c>
       <c r="E127">
-        <v>-0.9950248756218906</v>
+        <v>-0.5102040816326531</v>
       </c>
       <c r="F127">
-        <v>4.02</v>
+        <v>3.92</v>
       </c>
       <c r="G127">
-        <v>4.02</v>
+        <v>3.94</v>
       </c>
       <c r="H127">
-        <v>3.94</v>
+        <v>3.86</v>
       </c>
       <c r="I127">
         <v>0</v>
@@ -6388,22 +6388,22 @@
         <v>0</v>
       </c>
       <c r="K127">
-        <v>53274962</v>
+        <v>73616885</v>
       </c>
       <c r="L127">
-        <v>211880.63530000002</v>
+        <v>286207.30916</v>
       </c>
       <c r="M127">
-        <v>2979500</v>
+        <v>6303600</v>
       </c>
       <c r="N127">
-        <v>3.96</v>
+        <v>3.88</v>
       </c>
       <c r="O127">
-        <v>3.98</v>
+        <v>3.9</v>
       </c>
       <c r="P127">
-        <v>2721100</v>
+        <v>1586700</v>
       </c>
     </row>
     <row r="128">
@@ -6417,19 +6417,19 @@
         <v>4.12</v>
       </c>
       <c r="D128">
-        <v>0.04</v>
+        <v>0</v>
       </c>
       <c r="E128">
-        <v>0.9803921568627451</v>
+        <v>0</v>
       </c>
       <c r="F128">
-        <v>4.1</v>
+        <v>4.12</v>
       </c>
       <c r="G128">
         <v>4.14</v>
       </c>
       <c r="H128">
-        <v>4.06</v>
+        <v>4.08</v>
       </c>
       <c r="I128">
         <v>0</v>
@@ -6438,13 +6438,13 @@
         <v>0</v>
       </c>
       <c r="K128">
-        <v>3154627</v>
+        <v>1427266</v>
       </c>
       <c r="L128">
-        <v>12942.35524</v>
+        <v>5862.84376</v>
       </c>
       <c r="M128">
-        <v>257400</v>
+        <v>86100</v>
       </c>
       <c r="N128">
         <v>4.1</v>
@@ -6453,7 +6453,7 @@
         <v>4.12</v>
       </c>
       <c r="P128">
-        <v>83500</v>
+        <v>9300</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/StockQuotation (4).xlsx
+++ b/Excel/StockQuotation (4).xlsx
@@ -402,7 +402,7 @@
         <v/>
       </c>
       <c r="C1" t="str">
-        <v>07/02/23 23:29:58</v>
+        <v>08/02/23 20:05:49</v>
       </c>
     </row>
     <row r="4">
@@ -426,34 +426,34 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>1064</v>
+        <v>1058.58</v>
       </c>
       <c r="B7" t="str">
-        <v>-0.43 (-0.0403%)</v>
+        <v>-5.42 (-0.5093%)</v>
       </c>
       <c r="C7" t="str">
         <v>High</v>
       </c>
       <c r="D7">
-        <v>1069.54</v>
+        <v>1067.48</v>
       </c>
       <c r="E7" t="str">
         <v>Low</v>
       </c>
       <c r="F7">
-        <v>1060.96</v>
+        <v>1056.65</v>
       </c>
       <c r="G7" t="str">
         <v>Volume</v>
       </c>
       <c r="H7">
-        <v>1843006951</v>
+        <v>2175836616</v>
       </c>
       <c r="I7" t="str">
         <v>Value</v>
       </c>
       <c r="J7">
-        <v>38880805074.99</v>
+        <v>36775332545.09</v>
       </c>
     </row>
     <row r="9">
@@ -514,46 +514,46 @@
         <v>-</v>
       </c>
       <c r="C10">
+        <v>3.04</v>
+      </c>
+      <c r="D10">
+        <v>-0.04</v>
+      </c>
+      <c r="E10">
+        <v>-1.2987012987012987</v>
+      </c>
+      <c r="F10">
         <v>3.08</v>
       </c>
-      <c r="D10">
-        <v>-0.02</v>
-      </c>
-      <c r="E10">
-        <v>-0.6451612903225806</v>
-      </c>
-      <c r="F10">
+      <c r="G10">
         <v>3.1</v>
       </c>
-      <c r="G10">
-        <v>3.12</v>
-      </c>
       <c r="H10">
+        <v>3.04</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <v>0</v>
+      </c>
+      <c r="K10">
+        <v>35912008</v>
+      </c>
+      <c r="L10">
+        <v>110055.06809999999</v>
+      </c>
+      <c r="M10">
+        <v>10794000</v>
+      </c>
+      <c r="N10">
+        <v>3.04</v>
+      </c>
+      <c r="O10">
         <v>3.06</v>
       </c>
-      <c r="I10">
-        <v>0</v>
-      </c>
-      <c r="J10">
-        <v>0</v>
-      </c>
-      <c r="K10">
-        <v>47860704</v>
-      </c>
-      <c r="L10">
-        <v>148095.61584</v>
-      </c>
-      <c r="M10">
-        <v>10938600</v>
-      </c>
-      <c r="N10">
-        <v>3.06</v>
-      </c>
-      <c r="O10">
-        <v>3.08</v>
-      </c>
       <c r="P10">
-        <v>307300</v>
+        <v>1584000</v>
       </c>
     </row>
     <row r="11">
@@ -564,19 +564,19 @@
         <v>-</v>
       </c>
       <c r="C11">
+        <v>2.54</v>
+      </c>
+      <c r="D11">
+        <v>-0.02</v>
+      </c>
+      <c r="E11">
+        <v>-0.78125</v>
+      </c>
+      <c r="F11">
+        <v>2.54</v>
+      </c>
+      <c r="G11">
         <v>2.56</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
-      </c>
-      <c r="F11">
-        <v>2.56</v>
-      </c>
-      <c r="G11">
-        <v>2.58</v>
       </c>
       <c r="H11">
         <v>2.54</v>
@@ -588,13 +588,13 @@
         <v>0</v>
       </c>
       <c r="K11">
-        <v>23915176</v>
+        <v>16004646</v>
       </c>
       <c r="L11">
-        <v>61242.8576</v>
+        <v>40730.70048</v>
       </c>
       <c r="M11">
-        <v>4541200</v>
+        <v>3748000</v>
       </c>
       <c r="N11">
         <v>2.54</v>
@@ -603,7 +603,7 @@
         <v>2.56</v>
       </c>
       <c r="P11">
-        <v>456300</v>
+        <v>2629000</v>
       </c>
     </row>
     <row r="12">
@@ -614,22 +614,22 @@
         <v>-</v>
       </c>
       <c r="C12">
+        <v>195.5</v>
+      </c>
+      <c r="D12">
+        <v>-1</v>
+      </c>
+      <c r="E12">
+        <v>-0.5089058524173028</v>
+      </c>
+      <c r="F12">
+        <v>196</v>
+      </c>
+      <c r="G12">
         <v>196.5</v>
       </c>
-      <c r="D12">
-        <v>-0.5</v>
-      </c>
-      <c r="E12">
-        <v>-0.25380710659898476</v>
-      </c>
-      <c r="F12">
-        <v>197</v>
-      </c>
-      <c r="G12">
-        <v>198</v>
-      </c>
       <c r="H12">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I12">
         <v>0</v>
@@ -638,22 +638,22 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>3223977</v>
+        <v>3770659</v>
       </c>
       <c r="L12">
-        <v>633905.6665</v>
+        <v>737590.8815</v>
       </c>
       <c r="M12">
-        <v>581100</v>
+        <v>1010400</v>
       </c>
       <c r="N12">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="O12">
-        <v>196.5</v>
+        <v>195.5</v>
       </c>
       <c r="P12">
-        <v>51200</v>
+        <v>235500</v>
       </c>
     </row>
     <row r="13">
@@ -664,22 +664,22 @@
         <v>-</v>
       </c>
       <c r="C13">
-        <v>32.75</v>
+        <v>31.75</v>
       </c>
       <c r="D13">
-        <v>-0.25</v>
+        <v>-1</v>
       </c>
       <c r="E13">
-        <v>-0.7575757575757576</v>
+        <v>-3.053435114503817</v>
       </c>
       <c r="F13">
         <v>33</v>
       </c>
       <c r="G13">
-        <v>33.25</v>
+        <v>33</v>
       </c>
       <c r="H13">
-        <v>32.5</v>
+        <v>31.5</v>
       </c>
       <c r="I13">
         <v>0</v>
@@ -688,22 +688,22 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>1688685</v>
+        <v>1449205</v>
       </c>
       <c r="L13">
-        <v>55467.10525</v>
+        <v>46651.59125</v>
       </c>
       <c r="M13">
-        <v>5000</v>
+        <v>135600</v>
       </c>
       <c r="N13">
-        <v>32.75</v>
+        <v>31.75</v>
       </c>
       <c r="O13">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="P13">
-        <v>328000</v>
+        <v>35200</v>
       </c>
     </row>
     <row r="14">
@@ -714,46 +714,46 @@
         <v>-</v>
       </c>
       <c r="C14">
-        <v>12.9</v>
+        <v>12.8</v>
       </c>
       <c r="D14">
         <v>-0.1</v>
       </c>
       <c r="E14">
-        <v>-0.7692307692307693</v>
+        <v>-0.7751937984496124</v>
       </c>
       <c r="F14">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="G14">
-        <v>13.1</v>
+        <v>12.9</v>
       </c>
       <c r="H14">
+        <v>12.7</v>
+      </c>
+      <c r="I14">
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <v>268667</v>
+      </c>
+      <c r="L14">
+        <v>3443.391</v>
+      </c>
+      <c r="M14">
+        <v>26100</v>
+      </c>
+      <c r="N14">
+        <v>12.7</v>
+      </c>
+      <c r="O14">
         <v>12.8</v>
       </c>
-      <c r="I14">
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <v>296417</v>
-      </c>
-      <c r="L14">
-        <v>3835.5916</v>
-      </c>
-      <c r="M14">
-        <v>86000</v>
-      </c>
-      <c r="N14">
-        <v>12.8</v>
-      </c>
-      <c r="O14">
-        <v>12.9</v>
-      </c>
       <c r="P14">
-        <v>27100</v>
+        <v>25900</v>
       </c>
     </row>
     <row r="15">
@@ -773,13 +773,13 @@
         <v>0</v>
       </c>
       <c r="F15">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="G15">
-        <v>20.3</v>
+        <v>20.5</v>
       </c>
       <c r="H15">
-        <v>19.9</v>
+        <v>20.1</v>
       </c>
       <c r="I15">
         <v>0</v>
@@ -788,13 +788,13 @@
         <v>0</v>
       </c>
       <c r="K15">
-        <v>6175226</v>
+        <v>7211455</v>
       </c>
       <c r="L15">
-        <v>124102.2675</v>
+        <v>146060.62269999998</v>
       </c>
       <c r="M15">
-        <v>171800</v>
+        <v>470200</v>
       </c>
       <c r="N15">
         <v>20.1</v>
@@ -803,7 +803,7 @@
         <v>20.2</v>
       </c>
       <c r="P15">
-        <v>143600</v>
+        <v>61600</v>
       </c>
     </row>
     <row r="16">
@@ -814,46 +814,46 @@
         <v>-</v>
       </c>
       <c r="C16">
-        <v>73.5</v>
+        <v>74</v>
       </c>
       <c r="D16">
-        <v>-0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E16">
-        <v>-0.3389830508474576</v>
+        <v>0.6802721088435374</v>
       </c>
       <c r="F16">
         <v>73.5</v>
       </c>
       <c r="G16">
-        <v>74</v>
+        <v>74.25</v>
       </c>
       <c r="H16">
         <v>73.25</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>261700</v>
       </c>
       <c r="J16">
-        <v>0</v>
+        <v>19267.6625</v>
       </c>
       <c r="K16">
-        <v>19882884</v>
+        <v>20316385</v>
       </c>
       <c r="L16">
-        <v>1462189.4985</v>
+        <v>1499172.9605</v>
       </c>
       <c r="M16">
-        <v>5942900</v>
+        <v>1223100</v>
       </c>
       <c r="N16">
-        <v>73.5</v>
+        <v>73.75</v>
       </c>
       <c r="O16">
-        <v>73.75</v>
+        <v>74</v>
       </c>
       <c r="P16">
-        <v>439300</v>
+        <v>578900</v>
       </c>
     </row>
     <row r="17">
@@ -867,43 +867,43 @@
         <v>11.9</v>
       </c>
       <c r="D17">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E17">
-        <v>0.847457627118644</v>
+        <v>0</v>
       </c>
       <c r="F17">
         <v>11.9</v>
       </c>
       <c r="G17">
+        <v>12.1</v>
+      </c>
+      <c r="H17">
+        <v>11.8</v>
+      </c>
+      <c r="I17">
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <v>0</v>
+      </c>
+      <c r="K17">
+        <v>23221669</v>
+      </c>
+      <c r="L17">
+        <v>277018.21280000004</v>
+      </c>
+      <c r="M17">
+        <v>675500</v>
+      </c>
+      <c r="N17">
         <v>11.9</v>
       </c>
-      <c r="H17">
-        <v>11.7</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
-      </c>
-      <c r="J17">
-        <v>0</v>
-      </c>
-      <c r="K17">
-        <v>16341272</v>
-      </c>
-      <c r="L17">
-        <v>193278.3275</v>
-      </c>
-      <c r="M17">
-        <v>2417300</v>
-      </c>
-      <c r="N17">
-        <v>11.8</v>
-      </c>
       <c r="O17">
-        <v>11.9</v>
+        <v>12</v>
       </c>
       <c r="P17">
-        <v>754800</v>
+        <v>4210700</v>
       </c>
     </row>
     <row r="18">
@@ -914,46 +914,46 @@
         <v>-</v>
       </c>
       <c r="C18">
-        <v>13.9</v>
+        <v>13.7</v>
       </c>
       <c r="D18">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E18">
-        <v>0.7246376811594203</v>
+        <v>-1.4388489208633093</v>
       </c>
       <c r="F18">
-        <v>13.9</v>
+        <v>14</v>
       </c>
       <c r="G18">
         <v>14</v>
       </c>
       <c r="H18">
+        <v>13.7</v>
+      </c>
+      <c r="I18">
+        <v>0</v>
+      </c>
+      <c r="J18">
+        <v>0</v>
+      </c>
+      <c r="K18">
+        <v>644605</v>
+      </c>
+      <c r="L18">
+        <v>8900.9921</v>
+      </c>
+      <c r="M18">
+        <v>90900</v>
+      </c>
+      <c r="N18">
+        <v>13.7</v>
+      </c>
+      <c r="O18">
         <v>13.8</v>
       </c>
-      <c r="I18">
-        <v>0</v>
-      </c>
-      <c r="J18">
-        <v>0</v>
-      </c>
-      <c r="K18">
-        <v>740963</v>
-      </c>
-      <c r="L18">
-        <v>10289.0565</v>
-      </c>
-      <c r="M18">
-        <v>281600</v>
-      </c>
-      <c r="N18">
-        <v>13.8</v>
-      </c>
-      <c r="O18">
-        <v>13.9</v>
-      </c>
       <c r="P18">
-        <v>133600</v>
+        <v>43300</v>
       </c>
     </row>
     <row r="19">
@@ -967,16 +967,16 @@
         <v>8.5</v>
       </c>
       <c r="D19">
-        <v>-0.15</v>
+        <v>0</v>
       </c>
       <c r="E19">
-        <v>-1.7341040462427746</v>
+        <v>0</v>
       </c>
       <c r="F19">
-        <v>8.65</v>
+        <v>8.5</v>
       </c>
       <c r="G19">
-        <v>8.65</v>
+        <v>8.7</v>
       </c>
       <c r="H19">
         <v>8.5</v>
@@ -988,13 +988,13 @@
         <v>0</v>
       </c>
       <c r="K19">
-        <v>925083</v>
+        <v>2124032</v>
       </c>
       <c r="L19">
-        <v>7915.8463</v>
+        <v>18255.465</v>
       </c>
       <c r="M19">
-        <v>199800</v>
+        <v>153800</v>
       </c>
       <c r="N19">
         <v>8.5</v>
@@ -1003,7 +1003,7 @@
         <v>8.55</v>
       </c>
       <c r="P19">
-        <v>31500</v>
+        <v>10000</v>
       </c>
     </row>
     <row r="20">
@@ -1014,13 +1014,13 @@
         <v>-</v>
       </c>
       <c r="C20">
-        <v>5.85</v>
+        <v>5.75</v>
       </c>
       <c r="D20">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E20">
-        <v>0</v>
+        <v>-1.7094017094017093</v>
       </c>
       <c r="F20">
         <v>5.85</v>
@@ -1029,7 +1029,7 @@
         <v>5.9</v>
       </c>
       <c r="H20">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="I20">
         <v>0</v>
@@ -1038,22 +1038,22 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>19377717</v>
+        <v>70624918</v>
       </c>
       <c r="L20">
-        <v>113441.1258</v>
+        <v>408342.94214999996</v>
       </c>
       <c r="M20">
-        <v>12201600</v>
+        <v>8814600</v>
       </c>
       <c r="N20">
-        <v>5.85</v>
+        <v>5.7</v>
       </c>
       <c r="O20">
-        <v>5.9</v>
+        <v>5.75</v>
       </c>
       <c r="P20">
-        <v>7559300</v>
+        <v>2778700</v>
       </c>
     </row>
     <row r="21">
@@ -1067,43 +1067,43 @@
         <v>34.25</v>
       </c>
       <c r="D21">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E21">
-        <v>-0.7246376811594203</v>
+        <v>0</v>
       </c>
       <c r="F21">
-        <v>34.5</v>
+        <v>34.25</v>
       </c>
       <c r="G21">
         <v>34.5</v>
       </c>
       <c r="H21">
+        <v>33.75</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>740255</v>
+      </c>
+      <c r="L21">
+        <v>25201.725</v>
+      </c>
+      <c r="M21">
+        <v>8500</v>
+      </c>
+      <c r="N21">
         <v>34</v>
       </c>
-      <c r="I21">
-        <v>0</v>
-      </c>
-      <c r="J21">
-        <v>0</v>
-      </c>
-      <c r="K21">
-        <v>773584</v>
-      </c>
-      <c r="L21">
-        <v>26529.6145</v>
-      </c>
-      <c r="M21">
-        <v>45900</v>
-      </c>
-      <c r="N21">
+      <c r="O21">
         <v>34.25</v>
       </c>
-      <c r="O21">
-        <v>34.5</v>
-      </c>
       <c r="P21">
-        <v>320400</v>
+        <v>198700</v>
       </c>
     </row>
     <row r="22">
@@ -1114,46 +1114,46 @@
         <v>-</v>
       </c>
       <c r="C22">
+        <v>15.7</v>
+      </c>
+      <c r="D22">
+        <v>-0.1</v>
+      </c>
+      <c r="E22">
+        <v>-0.6329113924050633</v>
+      </c>
+      <c r="F22">
+        <v>15.9</v>
+      </c>
+      <c r="G22">
+        <v>15.9</v>
+      </c>
+      <c r="H22">
+        <v>15.7</v>
+      </c>
+      <c r="I22">
+        <v>0</v>
+      </c>
+      <c r="J22">
+        <v>0</v>
+      </c>
+      <c r="K22">
+        <v>18466031</v>
+      </c>
+      <c r="L22">
+        <v>291674.11360000004</v>
+      </c>
+      <c r="M22">
+        <v>1515900</v>
+      </c>
+      <c r="N22">
+        <v>15.7</v>
+      </c>
+      <c r="O22">
         <v>15.8</v>
       </c>
-      <c r="D22">
-        <v>-0.2</v>
-      </c>
-      <c r="E22">
-        <v>-1.25</v>
-      </c>
-      <c r="F22">
-        <v>16.1</v>
-      </c>
-      <c r="G22">
-        <v>16.1</v>
-      </c>
-      <c r="H22">
-        <v>15.8</v>
-      </c>
-      <c r="I22">
-        <v>0</v>
-      </c>
-      <c r="J22">
-        <v>0</v>
-      </c>
-      <c r="K22">
-        <v>20470183</v>
-      </c>
-      <c r="L22">
-        <v>325444.6618</v>
-      </c>
-      <c r="M22">
-        <v>3687500</v>
-      </c>
-      <c r="N22">
-        <v>15.8</v>
-      </c>
-      <c r="O22">
-        <v>15.9</v>
-      </c>
       <c r="P22">
-        <v>706100</v>
+        <v>1520800</v>
       </c>
     </row>
     <row r="23">
@@ -1164,46 +1164,46 @@
         <v>-</v>
       </c>
       <c r="C23">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="D23">
-        <v>-0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="E23">
-        <v>-0.8849557522123894</v>
+        <v>-1.7857142857142858</v>
       </c>
       <c r="F23">
         <v>11.3</v>
       </c>
       <c r="G23">
-        <v>11.5</v>
+        <v>11.4</v>
       </c>
       <c r="H23">
-        <v>11.2</v>
+        <v>10.9</v>
       </c>
       <c r="I23">
-        <v>100000</v>
+        <v>9768400</v>
       </c>
       <c r="J23">
-        <v>1134</v>
+        <v>107468.6</v>
       </c>
       <c r="K23">
-        <v>161516144</v>
+        <v>136003874</v>
       </c>
       <c r="L23">
-        <v>1831534.3802</v>
+        <v>1507824.1778</v>
       </c>
       <c r="M23">
-        <v>23883600</v>
+        <v>16196200</v>
       </c>
       <c r="N23">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="O23">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="P23">
-        <v>772100</v>
+        <v>6055600</v>
       </c>
     </row>
     <row r="24">
@@ -1214,37 +1214,37 @@
         <v>-</v>
       </c>
       <c r="C24">
-        <v>160.5</v>
+        <v>160</v>
       </c>
       <c r="D24">
         <v>-0.5</v>
       </c>
       <c r="E24">
-        <v>-0.3105590062111801</v>
+        <v>-0.3115264797507788</v>
       </c>
       <c r="F24">
-        <v>161.5</v>
+        <v>160</v>
       </c>
       <c r="G24">
-        <v>161.5</v>
+        <v>161</v>
       </c>
       <c r="H24">
         <v>160</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>160000</v>
       </c>
       <c r="J24">
-        <v>0</v>
+        <v>25680</v>
       </c>
       <c r="K24">
-        <v>3101777</v>
+        <v>3694629</v>
       </c>
       <c r="L24">
-        <v>497468.5115</v>
+        <v>592696.122</v>
       </c>
       <c r="M24">
-        <v>756800</v>
+        <v>505300</v>
       </c>
       <c r="N24">
         <v>160</v>
@@ -1253,7 +1253,7 @@
         <v>160.5</v>
       </c>
       <c r="P24">
-        <v>235000</v>
+        <v>189400</v>
       </c>
     </row>
     <row r="25">
@@ -1267,19 +1267,19 @@
         <v>35.5</v>
       </c>
       <c r="D25">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="E25">
-        <v>-1.3888888888888888</v>
+        <v>0</v>
       </c>
       <c r="F25">
-        <v>36</v>
+        <v>35.5</v>
       </c>
       <c r="G25">
-        <v>36</v>
+        <v>36.25</v>
       </c>
       <c r="H25">
-        <v>35.25</v>
+        <v>35.5</v>
       </c>
       <c r="I25">
         <v>0</v>
@@ -1288,22 +1288,22 @@
         <v>0</v>
       </c>
       <c r="K25">
-        <v>5801589</v>
+        <v>4793027</v>
       </c>
       <c r="L25">
-        <v>206626.30275</v>
+        <v>171218.572</v>
       </c>
       <c r="M25">
-        <v>767100</v>
+        <v>261300</v>
       </c>
       <c r="N25">
-        <v>35.25</v>
+        <v>35.5</v>
       </c>
       <c r="O25">
-        <v>35.5</v>
+        <v>35.75</v>
       </c>
       <c r="P25">
-        <v>21000</v>
+        <v>399600</v>
       </c>
     </row>
     <row r="26">
@@ -1323,37 +1323,37 @@
         <v>0</v>
       </c>
       <c r="F26">
-        <v>10.1</v>
+        <v>10</v>
       </c>
       <c r="G26">
         <v>10.1</v>
       </c>
       <c r="H26">
+        <v>9.9</v>
+      </c>
+      <c r="I26">
+        <v>0</v>
+      </c>
+      <c r="J26">
+        <v>0</v>
+      </c>
+      <c r="K26">
+        <v>2617235</v>
+      </c>
+      <c r="L26">
+        <v>26131.1178</v>
+      </c>
+      <c r="M26">
+        <v>102800</v>
+      </c>
+      <c r="N26">
+        <v>9.95</v>
+      </c>
+      <c r="O26">
         <v>10</v>
       </c>
-      <c r="I26">
-        <v>0</v>
-      </c>
-      <c r="J26">
-        <v>0</v>
-      </c>
-      <c r="K26">
-        <v>1404493</v>
-      </c>
-      <c r="L26">
-        <v>14074.1795</v>
-      </c>
-      <c r="M26">
-        <v>640200</v>
-      </c>
-      <c r="N26">
-        <v>10</v>
-      </c>
-      <c r="O26">
-        <v>10.1</v>
-      </c>
       <c r="P26">
-        <v>895700</v>
+        <v>137100</v>
       </c>
     </row>
     <row r="27">
@@ -1367,43 +1367,43 @@
         <v>29.5</v>
       </c>
       <c r="D27">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E27">
-        <v>-0.8403361344537815</v>
+        <v>0</v>
       </c>
       <c r="F27">
-        <v>30</v>
+        <v>29.75</v>
       </c>
       <c r="G27">
         <v>30</v>
       </c>
       <c r="H27">
+        <v>29.25</v>
+      </c>
+      <c r="I27">
+        <v>570000</v>
+      </c>
+      <c r="J27">
+        <v>16815</v>
+      </c>
+      <c r="K27">
+        <v>27537710</v>
+      </c>
+      <c r="L27">
+        <v>814225.86</v>
+      </c>
+      <c r="M27">
+        <v>7226400</v>
+      </c>
+      <c r="N27">
+        <v>29.25</v>
+      </c>
+      <c r="O27">
         <v>29.5</v>
       </c>
-      <c r="I27">
-        <v>0</v>
-      </c>
-      <c r="J27">
-        <v>0</v>
-      </c>
-      <c r="K27">
-        <v>21781654</v>
-      </c>
-      <c r="L27">
-        <v>646621.64125</v>
-      </c>
-      <c r="M27">
-        <v>9700400</v>
-      </c>
-      <c r="N27">
-        <v>29.5</v>
-      </c>
-      <c r="O27">
-        <v>29.75</v>
-      </c>
       <c r="P27">
-        <v>1863000</v>
+        <v>2960000</v>
       </c>
     </row>
     <row r="28">
@@ -1414,19 +1414,19 @@
         <v>-</v>
       </c>
       <c r="C28">
+        <v>9.65</v>
+      </c>
+      <c r="D28">
+        <v>0.05</v>
+      </c>
+      <c r="E28">
+        <v>0.5208333333333334</v>
+      </c>
+      <c r="F28">
         <v>9.6</v>
       </c>
-      <c r="D28">
-        <v>-0.15</v>
-      </c>
-      <c r="E28">
-        <v>-1.5384615384615385</v>
-      </c>
-      <c r="F28">
-        <v>9.7</v>
-      </c>
       <c r="G28">
-        <v>9.75</v>
+        <v>9.65</v>
       </c>
       <c r="H28">
         <v>9.55</v>
@@ -1438,13 +1438,13 @@
         <v>0</v>
       </c>
       <c r="K28">
-        <v>58793587</v>
+        <v>37282411</v>
       </c>
       <c r="L28">
-        <v>565334.3098500001</v>
+        <v>358143.69605</v>
       </c>
       <c r="M28">
-        <v>1211000</v>
+        <v>5826400</v>
       </c>
       <c r="N28">
         <v>9.6</v>
@@ -1453,7 +1453,7 @@
         <v>9.65</v>
       </c>
       <c r="P28">
-        <v>3215400</v>
+        <v>1946600</v>
       </c>
     </row>
     <row r="29">
@@ -1464,16 +1464,16 @@
         <v>-</v>
       </c>
       <c r="C29">
+        <v>10.2</v>
+      </c>
+      <c r="D29">
+        <v>-0.1</v>
+      </c>
+      <c r="E29">
+        <v>-0.970873786407767</v>
+      </c>
+      <c r="F29">
         <v>10.3</v>
-      </c>
-      <c r="D29">
-        <v>0</v>
-      </c>
-      <c r="E29">
-        <v>0</v>
-      </c>
-      <c r="F29">
-        <v>10.2</v>
       </c>
       <c r="G29">
         <v>10.4</v>
@@ -1488,13 +1488,13 @@
         <v>0</v>
       </c>
       <c r="K29">
-        <v>321738</v>
+        <v>177824</v>
       </c>
       <c r="L29">
-        <v>3312.4498</v>
+        <v>1825.4173</v>
       </c>
       <c r="M29">
-        <v>918600</v>
+        <v>895700</v>
       </c>
       <c r="N29">
         <v>10.2</v>
@@ -1503,7 +1503,7 @@
         <v>10.3</v>
       </c>
       <c r="P29">
-        <v>62400</v>
+        <v>104200</v>
       </c>
     </row>
     <row r="30">
@@ -1514,46 +1514,46 @@
         <v>-</v>
       </c>
       <c r="C30">
+        <v>40.25</v>
+      </c>
+      <c r="D30">
+        <v>-0.5</v>
+      </c>
+      <c r="E30">
+        <v>-1.2269938650306749</v>
+      </c>
+      <c r="F30">
         <v>40.75</v>
       </c>
-      <c r="D30">
-        <v>1</v>
-      </c>
-      <c r="E30">
-        <v>2.5157232704402515</v>
-      </c>
-      <c r="F30">
+      <c r="G30">
+        <v>41</v>
+      </c>
+      <c r="H30">
         <v>40</v>
       </c>
-      <c r="G30">
-        <v>40.75</v>
-      </c>
-      <c r="H30">
-        <v>39.75</v>
-      </c>
       <c r="I30">
-        <v>0</v>
+        <v>24400</v>
       </c>
       <c r="J30">
-        <v>0</v>
+        <v>982.1</v>
       </c>
       <c r="K30">
-        <v>9101197</v>
+        <v>3631038</v>
       </c>
       <c r="L30">
-        <v>365517.13</v>
+        <v>146463.26475</v>
       </c>
       <c r="M30">
-        <v>464700</v>
+        <v>916000</v>
       </c>
       <c r="N30">
-        <v>40.5</v>
+        <v>40</v>
       </c>
       <c r="O30">
-        <v>40.75</v>
+        <v>40.25</v>
       </c>
       <c r="P30">
-        <v>724300</v>
+        <v>101500</v>
       </c>
     </row>
     <row r="31">
@@ -1564,22 +1564,22 @@
         <v>-</v>
       </c>
       <c r="C31">
+        <v>38.75</v>
+      </c>
+      <c r="D31">
+        <v>0.25</v>
+      </c>
+      <c r="E31">
+        <v>0.6493506493506493</v>
+      </c>
+      <c r="F31">
         <v>38.5</v>
       </c>
-      <c r="D31">
-        <v>0.5</v>
-      </c>
-      <c r="E31">
-        <v>1.3157894736842106</v>
-      </c>
-      <c r="F31">
-        <v>38.25</v>
-      </c>
       <c r="G31">
-        <v>38.75</v>
+        <v>39.5</v>
       </c>
       <c r="H31">
-        <v>37.5</v>
+        <v>38.5</v>
       </c>
       <c r="I31">
         <v>0</v>
@@ -1588,13 +1588,13 @@
         <v>0</v>
       </c>
       <c r="K31">
-        <v>4774943</v>
+        <v>10373715</v>
       </c>
       <c r="L31">
-        <v>182526.64975</v>
+        <v>403408.98225</v>
       </c>
       <c r="M31">
-        <v>374200</v>
+        <v>18100</v>
       </c>
       <c r="N31">
         <v>38.5</v>
@@ -1603,7 +1603,7 @@
         <v>38.75</v>
       </c>
       <c r="P31">
-        <v>403100</v>
+        <v>102600</v>
       </c>
     </row>
     <row r="32">
@@ -1617,16 +1617,16 @@
         <v>291</v>
       </c>
       <c r="D32">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="E32">
-        <v>-0.3424657534246575</v>
+        <v>0</v>
       </c>
       <c r="F32">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="G32">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H32">
         <v>290</v>
@@ -1638,22 +1638,22 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>21207</v>
+        <v>26699</v>
       </c>
       <c r="L32">
-        <v>6181.244</v>
+        <v>7745.723</v>
       </c>
       <c r="M32">
-        <v>5100</v>
+        <v>1100</v>
       </c>
       <c r="N32">
+        <v>290</v>
+      </c>
+      <c r="O32">
         <v>291</v>
       </c>
-      <c r="O32">
-        <v>292</v>
-      </c>
       <c r="P32">
-        <v>4600</v>
+        <v>4900</v>
       </c>
     </row>
     <row r="33">
@@ -1664,46 +1664,46 @@
         <v>-</v>
       </c>
       <c r="C33">
-        <v>30</v>
+        <v>29.75</v>
       </c>
       <c r="D33">
         <v>-0.25</v>
       </c>
       <c r="E33">
-        <v>-0.8264462809917356</v>
+        <v>-0.8333333333333334</v>
       </c>
       <c r="F33">
+        <v>30</v>
+      </c>
+      <c r="G33">
         <v>30.25</v>
       </c>
-      <c r="G33">
-        <v>30.5</v>
-      </c>
       <c r="H33">
+        <v>29.5</v>
+      </c>
+      <c r="I33">
+        <v>944100</v>
+      </c>
+      <c r="J33">
+        <v>28086.975</v>
+      </c>
+      <c r="K33">
+        <v>5184401</v>
+      </c>
+      <c r="L33">
+        <v>154767.9025</v>
+      </c>
+      <c r="M33">
+        <v>390000</v>
+      </c>
+      <c r="N33">
+        <v>29.5</v>
+      </c>
+      <c r="O33">
         <v>29.75</v>
       </c>
-      <c r="I33">
-        <v>107200</v>
-      </c>
-      <c r="J33">
-        <v>3216</v>
-      </c>
-      <c r="K33">
-        <v>5138658</v>
-      </c>
-      <c r="L33">
-        <v>154918.59375</v>
-      </c>
-      <c r="M33">
-        <v>200400</v>
-      </c>
-      <c r="N33">
-        <v>30</v>
-      </c>
-      <c r="O33">
-        <v>30.25</v>
-      </c>
       <c r="P33">
-        <v>928600</v>
+        <v>163900</v>
       </c>
     </row>
     <row r="34">
@@ -1714,22 +1714,22 @@
         <v>-</v>
       </c>
       <c r="C34">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="D34">
         <v>0.1</v>
       </c>
       <c r="E34">
-        <v>0.5882352941176471</v>
+        <v>0.5847953216374269</v>
       </c>
       <c r="F34">
         <v>17.1</v>
       </c>
       <c r="G34">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="H34">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="I34">
         <v>0</v>
@@ -1738,22 +1738,22 @@
         <v>0</v>
       </c>
       <c r="K34">
-        <v>551835</v>
+        <v>1900409</v>
       </c>
       <c r="L34">
-        <v>9361.9499</v>
+        <v>32622.191600000002</v>
       </c>
       <c r="M34">
-        <v>17000</v>
+        <v>86000</v>
       </c>
       <c r="N34">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="O34">
-        <v>17.1</v>
+        <v>17.3</v>
       </c>
       <c r="P34">
-        <v>228900</v>
+        <v>268500</v>
       </c>
     </row>
     <row r="35">
@@ -1764,19 +1764,19 @@
         <v>-</v>
       </c>
       <c r="C35">
-        <v>8.25</v>
+        <v>8.2</v>
       </c>
       <c r="D35">
         <v>-0.05</v>
       </c>
       <c r="E35">
-        <v>-0.6024096385542169</v>
+        <v>-0.6060606060606061</v>
       </c>
       <c r="F35">
         <v>8.3</v>
       </c>
       <c r="G35">
-        <v>8.4</v>
+        <v>8.3</v>
       </c>
       <c r="H35">
         <v>8.2</v>
@@ -1788,22 +1788,22 @@
         <v>0</v>
       </c>
       <c r="K35">
-        <v>52782066</v>
+        <v>23116540</v>
       </c>
       <c r="L35">
-        <v>436595.46095</v>
+        <v>190510.177</v>
       </c>
       <c r="M35">
-        <v>267700</v>
+        <v>6632600</v>
       </c>
       <c r="N35">
+        <v>8.2</v>
+      </c>
+      <c r="O35">
         <v>8.25</v>
       </c>
-      <c r="O35">
-        <v>8.3</v>
-      </c>
       <c r="P35">
-        <v>1769900</v>
+        <v>1478800</v>
       </c>
     </row>
     <row r="36">
@@ -1814,46 +1814,46 @@
         <v>-</v>
       </c>
       <c r="C36">
-        <v>102</v>
+        <v>100.5</v>
       </c>
       <c r="D36">
-        <v>-1</v>
+        <v>-1.5</v>
       </c>
       <c r="E36">
-        <v>-0.970873786407767</v>
+        <v>-1.4705882352941178</v>
       </c>
       <c r="F36">
-        <v>103</v>
+        <v>102.5</v>
       </c>
       <c r="G36">
-        <v>103.5</v>
+        <v>102.5</v>
       </c>
       <c r="H36">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="I36">
-        <v>0</v>
+        <v>88000</v>
       </c>
       <c r="J36">
-        <v>0</v>
+        <v>8844</v>
       </c>
       <c r="K36">
-        <v>1768116</v>
+        <v>1844304</v>
       </c>
       <c r="L36">
-        <v>180572.946</v>
+        <v>186542.3475</v>
       </c>
       <c r="M36">
-        <v>151600</v>
+        <v>269000</v>
       </c>
       <c r="N36">
-        <v>101.5</v>
+        <v>100.5</v>
       </c>
       <c r="O36">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="P36">
-        <v>63900</v>
+        <v>24500</v>
       </c>
     </row>
     <row r="37">
@@ -1864,23 +1864,23 @@
         <v>-</v>
       </c>
       <c r="C37">
+        <v>55.25</v>
+      </c>
+      <c r="D37">
+        <v>1.25</v>
+      </c>
+      <c r="E37">
+        <v>2.314814814814815</v>
+      </c>
+      <c r="F37">
         <v>54</v>
       </c>
-      <c r="D37">
-        <v>0</v>
-      </c>
-      <c r="E37">
-        <v>0</v>
-      </c>
-      <c r="F37">
+      <c r="G37">
+        <v>56</v>
+      </c>
+      <c r="H37">
         <v>53.75</v>
       </c>
-      <c r="G37">
-        <v>54.25</v>
-      </c>
-      <c r="H37">
-        <v>53.25</v>
-      </c>
       <c r="I37">
         <v>0</v>
       </c>
@@ -1888,22 +1888,22 @@
         <v>0</v>
       </c>
       <c r="K37">
-        <v>2843307</v>
+        <v>9212201</v>
       </c>
       <c r="L37">
-        <v>153187.50425</v>
+        <v>507928.67475</v>
       </c>
       <c r="M37">
-        <v>105900</v>
+        <v>373500</v>
       </c>
       <c r="N37">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="O37">
-        <v>54.25</v>
+        <v>55.25</v>
       </c>
       <c r="P37">
-        <v>66500</v>
+        <v>130000</v>
       </c>
     </row>
     <row r="38">
@@ -1914,46 +1914,46 @@
         <v>-</v>
       </c>
       <c r="C38">
+        <v>4.66</v>
+      </c>
+      <c r="D38">
+        <v>-0.02</v>
+      </c>
+      <c r="E38">
+        <v>-0.42735042735042733</v>
+      </c>
+      <c r="F38">
         <v>4.68</v>
       </c>
-      <c r="D38">
-        <v>0.08</v>
-      </c>
-      <c r="E38">
-        <v>1.7391304347826086</v>
-      </c>
-      <c r="F38">
+      <c r="G38">
+        <v>4.7</v>
+      </c>
+      <c r="H38">
+        <v>4.62</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38">
+        <v>0</v>
+      </c>
+      <c r="K38">
+        <v>12625762</v>
+      </c>
+      <c r="L38">
+        <v>58798.19654</v>
+      </c>
+      <c r="M38">
+        <v>227900</v>
+      </c>
+      <c r="N38">
         <v>4.64</v>
       </c>
-      <c r="G38">
-        <v>4.72</v>
-      </c>
-      <c r="H38">
-        <v>4.6</v>
-      </c>
-      <c r="I38">
-        <v>0</v>
-      </c>
-      <c r="J38">
-        <v>0</v>
-      </c>
-      <c r="K38">
-        <v>24336619</v>
-      </c>
-      <c r="L38">
-        <v>113698.60182</v>
-      </c>
-      <c r="M38">
-        <v>1189900</v>
-      </c>
-      <c r="N38">
+      <c r="O38">
         <v>4.66</v>
       </c>
-      <c r="O38">
-        <v>4.68</v>
-      </c>
       <c r="P38">
-        <v>359000</v>
+        <v>62300</v>
       </c>
     </row>
     <row r="39">
@@ -1964,13 +1964,13 @@
         <v>-</v>
       </c>
       <c r="C39">
-        <v>31.75</v>
+        <v>31.5</v>
       </c>
       <c r="D39">
-        <v>-0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E39">
-        <v>-1.550387596899225</v>
+        <v>-0.7874015748031497</v>
       </c>
       <c r="F39">
         <v>32</v>
@@ -1982,28 +1982,28 @@
         <v>31.25</v>
       </c>
       <c r="I39">
-        <v>7133000</v>
+        <v>555400</v>
       </c>
       <c r="J39">
-        <v>228106</v>
+        <v>17495.1</v>
       </c>
       <c r="K39">
-        <v>15549744</v>
+        <v>7042142</v>
       </c>
       <c r="L39">
-        <v>495102.87975</v>
+        <v>222528.6925</v>
       </c>
       <c r="M39">
-        <v>265700</v>
+        <v>1178100</v>
       </c>
       <c r="N39">
-        <v>31.75</v>
+        <v>31.25</v>
       </c>
       <c r="O39">
-        <v>32</v>
+        <v>31.5</v>
       </c>
       <c r="P39">
-        <v>667600</v>
+        <v>141700</v>
       </c>
     </row>
     <row r="40">
@@ -2023,37 +2023,37 @@
         <v>0</v>
       </c>
       <c r="F40">
-        <v>66.5</v>
+        <v>66.75</v>
       </c>
       <c r="G40">
-        <v>67</v>
+        <v>67.25</v>
       </c>
       <c r="H40">
         <v>66.5</v>
       </c>
       <c r="I40">
-        <v>0</v>
+        <v>46000</v>
       </c>
       <c r="J40">
-        <v>0</v>
+        <v>3070.5</v>
       </c>
       <c r="K40">
-        <v>17353807</v>
+        <v>8511118</v>
       </c>
       <c r="L40">
-        <v>1158120.88375</v>
+        <v>569282.9895</v>
       </c>
       <c r="M40">
-        <v>2792200</v>
+        <v>1263500</v>
       </c>
       <c r="N40">
+        <v>66.5</v>
+      </c>
+      <c r="O40">
         <v>66.75</v>
       </c>
-      <c r="O40">
-        <v>67</v>
-      </c>
       <c r="P40">
-        <v>1848100</v>
+        <v>628500</v>
       </c>
     </row>
     <row r="41">
@@ -2064,46 +2064,46 @@
         <v>-</v>
       </c>
       <c r="C41">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="D41">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E41">
-        <v>0</v>
+        <v>-1.271186440677966</v>
       </c>
       <c r="F41">
         <v>23.6</v>
       </c>
       <c r="G41">
-        <v>23.7</v>
+        <v>23.6</v>
       </c>
       <c r="H41">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="I41">
-        <v>0</v>
+        <v>3472000</v>
       </c>
       <c r="J41">
-        <v>0</v>
+        <v>80897.6</v>
       </c>
       <c r="K41">
-        <v>17028962</v>
+        <v>28889712</v>
       </c>
       <c r="L41">
-        <v>401183.07739999995</v>
+        <v>675575.3047999999</v>
       </c>
       <c r="M41">
-        <v>2056100</v>
+        <v>5431700</v>
       </c>
       <c r="N41">
-        <v>23.5</v>
+        <v>23.3</v>
       </c>
       <c r="O41">
-        <v>23.6</v>
+        <v>23.4</v>
       </c>
       <c r="P41">
-        <v>347500</v>
+        <v>1514900</v>
       </c>
     </row>
     <row r="42">
@@ -2114,46 +2114,46 @@
         <v>-</v>
       </c>
       <c r="C42">
+        <v>73.5</v>
+      </c>
+      <c r="D42">
+        <v>0.5</v>
+      </c>
+      <c r="E42">
+        <v>0.684931506849315</v>
+      </c>
+      <c r="F42">
         <v>73</v>
       </c>
-      <c r="D42">
-        <v>0</v>
-      </c>
-      <c r="E42">
-        <v>0</v>
-      </c>
-      <c r="F42">
+      <c r="G42">
+        <v>73.5</v>
+      </c>
+      <c r="H42">
+        <v>73</v>
+      </c>
+      <c r="I42">
+        <v>0</v>
+      </c>
+      <c r="J42">
+        <v>0</v>
+      </c>
+      <c r="K42">
+        <v>4697118</v>
+      </c>
+      <c r="L42">
+        <v>344265.426</v>
+      </c>
+      <c r="M42">
+        <v>1480400</v>
+      </c>
+      <c r="N42">
         <v>73.25</v>
       </c>
-      <c r="G42">
-        <v>73.25</v>
-      </c>
-      <c r="H42">
-        <v>72.5</v>
-      </c>
-      <c r="I42">
-        <v>0</v>
-      </c>
-      <c r="J42">
-        <v>0</v>
-      </c>
-      <c r="K42">
-        <v>6999054</v>
-      </c>
-      <c r="L42">
-        <v>510636.73125</v>
-      </c>
-      <c r="M42">
-        <v>21700</v>
-      </c>
-      <c r="N42">
-        <v>73</v>
-      </c>
       <c r="O42">
-        <v>73.25</v>
+        <v>73.5</v>
       </c>
       <c r="P42">
-        <v>371800</v>
+        <v>450000</v>
       </c>
     </row>
     <row r="43">
@@ -2167,19 +2167,19 @@
         <v>44.25</v>
       </c>
       <c r="D43">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="E43">
-        <v>-0.5617977528089888</v>
+        <v>0</v>
       </c>
       <c r="F43">
-        <v>44.5</v>
+        <v>44.25</v>
       </c>
       <c r="G43">
         <v>44.5</v>
       </c>
       <c r="H43">
-        <v>43.75</v>
+        <v>44</v>
       </c>
       <c r="I43">
         <v>0</v>
@@ -2188,13 +2188,13 @@
         <v>0</v>
       </c>
       <c r="K43">
-        <v>10167453</v>
+        <v>11168771</v>
       </c>
       <c r="L43">
-        <v>448185.82275</v>
+        <v>493385.741</v>
       </c>
       <c r="M43">
-        <v>667100</v>
+        <v>947000</v>
       </c>
       <c r="N43">
         <v>44</v>
@@ -2203,7 +2203,7 @@
         <v>44.25</v>
       </c>
       <c r="P43">
-        <v>1198400</v>
+        <v>1021800</v>
       </c>
     </row>
     <row r="44">
@@ -2214,22 +2214,22 @@
         <v>-</v>
       </c>
       <c r="C44">
-        <v>970</v>
+        <v>930</v>
       </c>
       <c r="D44">
-        <v>20</v>
+        <v>-40</v>
       </c>
       <c r="E44">
-        <v>2.1052631578947367</v>
+        <v>-4.123711340206185</v>
       </c>
       <c r="F44">
-        <v>966</v>
+        <v>976</v>
       </c>
       <c r="G44">
-        <v>996</v>
+        <v>978</v>
       </c>
       <c r="H44">
-        <v>962</v>
+        <v>930</v>
       </c>
       <c r="I44">
         <v>0</v>
@@ -2238,22 +2238,22 @@
         <v>0</v>
       </c>
       <c r="K44">
-        <v>4132116</v>
+        <v>2776683</v>
       </c>
       <c r="L44">
-        <v>4034300.206</v>
+        <v>2626711.194</v>
       </c>
       <c r="M44">
-        <v>29800</v>
+        <v>27350</v>
       </c>
       <c r="N44">
-        <v>970</v>
+        <v>930</v>
       </c>
       <c r="O44">
-        <v>972</v>
+        <v>932</v>
       </c>
       <c r="P44">
-        <v>66800</v>
+        <v>21350</v>
       </c>
     </row>
     <row r="45">
@@ -2264,46 +2264,46 @@
         <v>-</v>
       </c>
       <c r="C45">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="D45">
-        <v>0</v>
+        <v>-0.3</v>
       </c>
       <c r="E45">
-        <v>0</v>
+        <v>-2.3076923076923075</v>
       </c>
       <c r="F45">
         <v>13</v>
       </c>
       <c r="G45">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="H45">
+        <v>12.7</v>
+      </c>
+      <c r="I45">
+        <v>0</v>
+      </c>
+      <c r="J45">
+        <v>0</v>
+      </c>
+      <c r="K45">
+        <v>926947</v>
+      </c>
+      <c r="L45">
+        <v>11869.731800000001</v>
+      </c>
+      <c r="M45">
+        <v>60300</v>
+      </c>
+      <c r="N45">
+        <v>12.7</v>
+      </c>
+      <c r="O45">
         <v>12.8</v>
       </c>
-      <c r="I45">
-        <v>0</v>
-      </c>
-      <c r="J45">
-        <v>0</v>
-      </c>
-      <c r="K45">
-        <v>1248511</v>
-      </c>
-      <c r="L45">
-        <v>16126.752</v>
-      </c>
-      <c r="M45">
-        <v>60000</v>
-      </c>
-      <c r="N45">
-        <v>12.9</v>
-      </c>
-      <c r="O45">
-        <v>13</v>
-      </c>
       <c r="P45">
-        <v>6900</v>
+        <v>99000</v>
       </c>
     </row>
     <row r="46">
@@ -2314,13 +2314,13 @@
         <v>-</v>
       </c>
       <c r="C46">
-        <v>8.25</v>
+        <v>8.2</v>
       </c>
       <c r="D46">
         <v>-0.05</v>
       </c>
       <c r="E46">
-        <v>-0.6024096385542169</v>
+        <v>-0.6060606060606061</v>
       </c>
       <c r="F46">
         <v>8.25</v>
@@ -2329,31 +2329,31 @@
         <v>8.3</v>
       </c>
       <c r="H46">
+        <v>8.2</v>
+      </c>
+      <c r="I46">
+        <v>0</v>
+      </c>
+      <c r="J46">
+        <v>0</v>
+      </c>
+      <c r="K46">
+        <v>62782</v>
+      </c>
+      <c r="L46">
+        <v>518.53745</v>
+      </c>
+      <c r="M46">
+        <v>45000</v>
+      </c>
+      <c r="N46">
+        <v>8.2</v>
+      </c>
+      <c r="O46">
         <v>8.25</v>
       </c>
-      <c r="I46">
-        <v>0</v>
-      </c>
-      <c r="J46">
-        <v>0</v>
-      </c>
-      <c r="K46">
-        <v>137355</v>
-      </c>
-      <c r="L46">
-        <v>1134.4045</v>
-      </c>
-      <c r="M46">
-        <v>11800</v>
-      </c>
-      <c r="N46">
-        <v>8.25</v>
-      </c>
-      <c r="O46">
-        <v>8.3</v>
-      </c>
       <c r="P46">
-        <v>10000</v>
+        <v>18000</v>
       </c>
     </row>
     <row r="47">
@@ -2364,46 +2364,46 @@
         <v>-</v>
       </c>
       <c r="C47">
-        <v>49.75</v>
+        <v>49.5</v>
       </c>
       <c r="D47">
-        <v>0</v>
+        <v>-0.25</v>
       </c>
       <c r="E47">
-        <v>0</v>
+        <v>-0.5025125628140703</v>
       </c>
       <c r="F47">
-        <v>49.75</v>
+        <v>49.25</v>
       </c>
       <c r="G47">
-        <v>50</v>
+        <v>49.5</v>
       </c>
       <c r="H47">
+        <v>48.75</v>
+      </c>
+      <c r="I47">
+        <v>0</v>
+      </c>
+      <c r="J47">
+        <v>0</v>
+      </c>
+      <c r="K47">
+        <v>3575153</v>
+      </c>
+      <c r="L47">
+        <v>175856.39175</v>
+      </c>
+      <c r="M47">
+        <v>708800</v>
+      </c>
+      <c r="N47">
         <v>49.25</v>
       </c>
-      <c r="I47">
-        <v>0</v>
-      </c>
-      <c r="J47">
-        <v>0</v>
-      </c>
-      <c r="K47">
-        <v>3615781</v>
-      </c>
-      <c r="L47">
-        <v>179304.867</v>
-      </c>
-      <c r="M47">
-        <v>419300</v>
-      </c>
-      <c r="N47">
+      <c r="O47">
         <v>49.5</v>
       </c>
-      <c r="O47">
-        <v>49.75</v>
-      </c>
       <c r="P47">
-        <v>54800</v>
+        <v>653000</v>
       </c>
     </row>
     <row r="48">
@@ -2414,46 +2414,46 @@
         <v>-</v>
       </c>
       <c r="C48">
-        <v>90.5</v>
+        <v>89</v>
       </c>
       <c r="D48">
-        <v>1.75</v>
+        <v>-1.5</v>
       </c>
       <c r="E48">
-        <v>1.971830985915493</v>
+        <v>-1.6574585635359116</v>
       </c>
       <c r="F48">
+        <v>90.25</v>
+      </c>
+      <c r="G48">
+        <v>90.75</v>
+      </c>
+      <c r="H48">
+        <v>88.75</v>
+      </c>
+      <c r="I48">
+        <v>32900</v>
+      </c>
+      <c r="J48">
+        <v>3059.7</v>
+      </c>
+      <c r="K48">
+        <v>14025631</v>
+      </c>
+      <c r="L48">
+        <v>1257473.392</v>
+      </c>
+      <c r="M48">
+        <v>260500</v>
+      </c>
+      <c r="N48">
+        <v>89</v>
+      </c>
+      <c r="O48">
         <v>89.25</v>
       </c>
-      <c r="G48">
-        <v>91.25</v>
-      </c>
-      <c r="H48">
-        <v>89</v>
-      </c>
-      <c r="I48">
-        <v>300000</v>
-      </c>
-      <c r="J48">
-        <v>27150</v>
-      </c>
-      <c r="K48">
-        <v>20532822</v>
-      </c>
-      <c r="L48">
-        <v>1857934.2095</v>
-      </c>
-      <c r="M48">
-        <v>129000</v>
-      </c>
-      <c r="N48">
-        <v>90.5</v>
-      </c>
-      <c r="O48">
-        <v>90.75</v>
-      </c>
       <c r="P48">
-        <v>395700</v>
+        <v>112200</v>
       </c>
     </row>
     <row r="49">
@@ -2464,23 +2464,23 @@
         <v>-</v>
       </c>
       <c r="C49">
+        <v>5.35</v>
+      </c>
+      <c r="D49">
+        <v>-0.1</v>
+      </c>
+      <c r="E49">
+        <v>-1.834862385321101</v>
+      </c>
+      <c r="F49">
         <v>5.45</v>
       </c>
-      <c r="D49">
-        <v>0.1</v>
-      </c>
-      <c r="E49">
-        <v>1.8691588785046729</v>
-      </c>
-      <c r="F49">
+      <c r="G49">
+        <v>5.45</v>
+      </c>
+      <c r="H49">
         <v>5.3</v>
       </c>
-      <c r="G49">
-        <v>5.5</v>
-      </c>
-      <c r="H49">
-        <v>5.25</v>
-      </c>
       <c r="I49">
         <v>0</v>
       </c>
@@ -2488,22 +2488,22 @@
         <v>0</v>
       </c>
       <c r="K49">
-        <v>1512018</v>
+        <v>1381715</v>
       </c>
       <c r="L49">
-        <v>8110.20285</v>
+        <v>7442.78855</v>
       </c>
       <c r="M49">
-        <v>48300</v>
+        <v>87600</v>
       </c>
       <c r="N49">
+        <v>5.35</v>
+      </c>
+      <c r="O49">
         <v>5.4</v>
       </c>
-      <c r="O49">
-        <v>5.45</v>
-      </c>
       <c r="P49">
-        <v>79900</v>
+        <v>359200</v>
       </c>
     </row>
     <row r="50">
@@ -2514,13 +2514,13 @@
         <v>-</v>
       </c>
       <c r="C50">
-        <v>172</v>
+        <v>171.5</v>
       </c>
       <c r="D50">
         <v>-0.5</v>
       </c>
       <c r="E50">
-        <v>-0.2898550724637681</v>
+        <v>-0.29069767441860467</v>
       </c>
       <c r="F50">
         <v>172</v>
@@ -2538,22 +2538,22 @@
         <v>0</v>
       </c>
       <c r="K50">
-        <v>944769</v>
+        <v>642855</v>
       </c>
       <c r="L50">
-        <v>162568.3245</v>
+        <v>110252.033</v>
       </c>
       <c r="M50">
-        <v>100</v>
+        <v>10100</v>
       </c>
       <c r="N50">
+        <v>171.5</v>
+      </c>
+      <c r="O50">
         <v>172</v>
       </c>
-      <c r="O50">
-        <v>172.5</v>
-      </c>
       <c r="P50">
-        <v>23000</v>
+        <v>53500</v>
       </c>
     </row>
     <row r="51">
@@ -2564,46 +2564,46 @@
         <v>-</v>
       </c>
       <c r="C51">
-        <v>8.7</v>
+        <v>8.65</v>
       </c>
       <c r="D51">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="E51">
-        <v>0</v>
+        <v>-0.5747126436781609</v>
       </c>
       <c r="F51">
-        <v>8.65</v>
+        <v>8.75</v>
       </c>
       <c r="G51">
         <v>8.75</v>
       </c>
       <c r="H51">
+        <v>8.6</v>
+      </c>
+      <c r="I51">
+        <v>0</v>
+      </c>
+      <c r="J51">
+        <v>0</v>
+      </c>
+      <c r="K51">
+        <v>2501441</v>
+      </c>
+      <c r="L51">
+        <v>21591.43955</v>
+      </c>
+      <c r="M51">
+        <v>33600</v>
+      </c>
+      <c r="N51">
+        <v>8.6</v>
+      </c>
+      <c r="O51">
         <v>8.65</v>
       </c>
-      <c r="I51">
-        <v>0</v>
-      </c>
-      <c r="J51">
-        <v>0</v>
-      </c>
-      <c r="K51">
-        <v>1349939</v>
-      </c>
-      <c r="L51">
-        <v>11741.280050000001</v>
-      </c>
-      <c r="M51">
-        <v>471000</v>
-      </c>
-      <c r="N51">
-        <v>8.65</v>
-      </c>
-      <c r="O51">
-        <v>8.7</v>
-      </c>
       <c r="P51">
-        <v>124800</v>
+        <v>106600</v>
       </c>
     </row>
     <row r="52">
@@ -2617,19 +2617,19 @@
         <v>4.6</v>
       </c>
       <c r="D52">
-        <v>0.16</v>
+        <v>0</v>
       </c>
       <c r="E52">
-        <v>3.6036036036036037</v>
+        <v>0</v>
       </c>
       <c r="F52">
-        <v>4.46</v>
+        <v>4.6</v>
       </c>
       <c r="G52">
-        <v>4.62</v>
+        <v>4.74</v>
       </c>
       <c r="H52">
-        <v>4.46</v>
+        <v>4.54</v>
       </c>
       <c r="I52">
         <v>0</v>
@@ -2638,22 +2638,22 @@
         <v>0</v>
       </c>
       <c r="K52">
-        <v>27268940</v>
+        <v>22945073</v>
       </c>
       <c r="L52">
-        <v>123563.55742</v>
+        <v>106227.2775</v>
       </c>
       <c r="M52">
-        <v>67000</v>
+        <v>183700</v>
       </c>
       <c r="N52">
+        <v>4.58</v>
+      </c>
+      <c r="O52">
         <v>4.6</v>
       </c>
-      <c r="O52">
-        <v>4.62</v>
-      </c>
       <c r="P52">
-        <v>256800</v>
+        <v>174500</v>
       </c>
     </row>
     <row r="53">
@@ -2664,22 +2664,22 @@
         <v>-</v>
       </c>
       <c r="C53">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="D53">
-        <v>-0.6</v>
+        <v>-0.1</v>
       </c>
       <c r="E53">
-        <v>-4.545454545454546</v>
+        <v>-0.7936507936507936</v>
       </c>
       <c r="F53">
-        <v>13.2</v>
+        <v>12.7</v>
       </c>
       <c r="G53">
-        <v>13.3</v>
+        <v>12.7</v>
       </c>
       <c r="H53">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="I53">
         <v>0</v>
@@ -2688,22 +2688,22 @@
         <v>0</v>
       </c>
       <c r="K53">
-        <v>13964192</v>
+        <v>4299756</v>
       </c>
       <c r="L53">
-        <v>178375.5901</v>
+        <v>53855.501299999996</v>
       </c>
       <c r="M53">
-        <v>950600</v>
+        <v>990000</v>
       </c>
       <c r="N53">
-        <v>12.6</v>
+        <v>12.4</v>
       </c>
       <c r="O53">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="P53">
-        <v>16500</v>
+        <v>5000</v>
       </c>
     </row>
     <row r="54">
@@ -2714,13 +2714,13 @@
         <v>-</v>
       </c>
       <c r="C54">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="D54">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E54">
-        <v>0</v>
+        <v>-0.4784688995215311</v>
       </c>
       <c r="F54">
         <v>20.9</v>
@@ -2732,28 +2732,28 @@
         <v>20.7</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>200000</v>
       </c>
       <c r="J54">
-        <v>0</v>
+        <v>4180</v>
       </c>
       <c r="K54">
-        <v>11074770</v>
+        <v>8045090</v>
       </c>
       <c r="L54">
-        <v>230826.29940000002</v>
+        <v>167697.2623</v>
       </c>
       <c r="M54">
-        <v>9800</v>
+        <v>797800</v>
       </c>
       <c r="N54">
-        <v>20.9</v>
+        <v>20.7</v>
       </c>
       <c r="O54">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="P54">
-        <v>851900</v>
+        <v>3900</v>
       </c>
     </row>
     <row r="55">
@@ -2764,46 +2764,46 @@
         <v>-</v>
       </c>
       <c r="C55">
-        <v>69.5</v>
+        <v>69</v>
       </c>
       <c r="D55">
-        <v>0.5</v>
+        <v>-0.5</v>
       </c>
       <c r="E55">
-        <v>0.7246376811594203</v>
+        <v>-0.7194244604316546</v>
       </c>
       <c r="F55">
-        <v>69</v>
+        <v>69.75</v>
       </c>
       <c r="G55">
         <v>69.75</v>
       </c>
       <c r="H55">
+        <v>68.75</v>
+      </c>
+      <c r="I55">
+        <v>13600</v>
+      </c>
+      <c r="J55">
+        <v>938.4</v>
+      </c>
+      <c r="K55">
+        <v>3744640</v>
+      </c>
+      <c r="L55">
+        <v>258684.2265</v>
+      </c>
+      <c r="M55">
+        <v>422400</v>
+      </c>
+      <c r="N55">
+        <v>68.75</v>
+      </c>
+      <c r="O55">
         <v>69</v>
       </c>
-      <c r="I55">
-        <v>0</v>
-      </c>
-      <c r="J55">
-        <v>0</v>
-      </c>
-      <c r="K55">
-        <v>3829162</v>
-      </c>
-      <c r="L55">
-        <v>265731.12725</v>
-      </c>
-      <c r="M55">
-        <v>160600</v>
-      </c>
-      <c r="N55">
-        <v>69.25</v>
-      </c>
-      <c r="O55">
-        <v>69.5</v>
-      </c>
       <c r="P55">
-        <v>41000</v>
+        <v>36500</v>
       </c>
     </row>
     <row r="56">
@@ -2814,46 +2814,46 @@
         <v>-</v>
       </c>
       <c r="C56">
+        <v>53.5</v>
+      </c>
+      <c r="D56">
+        <v>-0.5</v>
+      </c>
+      <c r="E56">
+        <v>-0.9259259259259259</v>
+      </c>
+      <c r="F56">
         <v>54</v>
-      </c>
-      <c r="D56">
-        <v>0.25</v>
-      </c>
-      <c r="E56">
-        <v>0.46511627906976744</v>
-      </c>
-      <c r="F56">
-        <v>53.75</v>
       </c>
       <c r="G56">
         <v>54.25</v>
       </c>
       <c r="H56">
+        <v>53.5</v>
+      </c>
+      <c r="I56">
+        <v>0</v>
+      </c>
+      <c r="J56">
+        <v>0</v>
+      </c>
+      <c r="K56">
+        <v>7868410</v>
+      </c>
+      <c r="L56">
+        <v>423202.82</v>
+      </c>
+      <c r="M56">
+        <v>1821500</v>
+      </c>
+      <c r="N56">
+        <v>53.5</v>
+      </c>
+      <c r="O56">
         <v>53.75</v>
       </c>
-      <c r="I56">
-        <v>0</v>
-      </c>
-      <c r="J56">
-        <v>0</v>
-      </c>
-      <c r="K56">
-        <v>11502957</v>
-      </c>
-      <c r="L56">
-        <v>620947.3135</v>
-      </c>
-      <c r="M56">
-        <v>3345400</v>
-      </c>
-      <c r="N56">
-        <v>53.75</v>
-      </c>
-      <c r="O56">
-        <v>54</v>
-      </c>
       <c r="P56">
-        <v>190800</v>
+        <v>844100</v>
       </c>
     </row>
     <row r="57">
@@ -2864,46 +2864,46 @@
         <v>-</v>
       </c>
       <c r="C57">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="D57">
         <v>-0.04</v>
       </c>
       <c r="E57">
-        <v>-0.8032128514056225</v>
+        <v>-0.8097165991902834</v>
       </c>
       <c r="F57">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="G57">
-        <v>5.05</v>
+        <v>4.98</v>
       </c>
       <c r="H57">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="I57">
-        <v>580000</v>
+        <v>0</v>
       </c>
       <c r="J57">
-        <v>2865.2</v>
+        <v>0</v>
       </c>
       <c r="K57">
-        <v>52248036</v>
+        <v>83042776</v>
       </c>
       <c r="L57">
-        <v>259856.6892</v>
+        <v>409026.96532</v>
       </c>
       <c r="M57">
-        <v>7270900</v>
+        <v>6304200</v>
       </c>
       <c r="N57">
-        <v>4.94</v>
+        <v>4.9</v>
       </c>
       <c r="O57">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
       <c r="P57">
-        <v>43100</v>
+        <v>621200</v>
       </c>
     </row>
     <row r="58">
@@ -2914,22 +2914,22 @@
         <v>-</v>
       </c>
       <c r="C58">
+        <v>61</v>
+      </c>
+      <c r="D58">
+        <v>-3</v>
+      </c>
+      <c r="E58">
+        <v>-4.6875</v>
+      </c>
+      <c r="F58">
+        <v>62.75</v>
+      </c>
+      <c r="G58">
         <v>64</v>
       </c>
-      <c r="D58">
-        <v>0.75</v>
-      </c>
-      <c r="E58">
-        <v>1.1857707509881423</v>
-      </c>
-      <c r="F58">
-        <v>63</v>
-      </c>
-      <c r="G58">
-        <v>65</v>
-      </c>
       <c r="H58">
-        <v>63</v>
+        <v>60.5</v>
       </c>
       <c r="I58">
         <v>0</v>
@@ -2938,22 +2938,22 @@
         <v>0</v>
       </c>
       <c r="K58">
-        <v>14815331</v>
+        <v>20838145</v>
       </c>
       <c r="L58">
-        <v>949666.43975</v>
+        <v>1296498.84575</v>
       </c>
       <c r="M58">
-        <v>274800</v>
+        <v>483300</v>
       </c>
       <c r="N58">
-        <v>64</v>
+        <v>60.75</v>
       </c>
       <c r="O58">
-        <v>64.25</v>
+        <v>61</v>
       </c>
       <c r="P58">
-        <v>258800</v>
+        <v>175200</v>
       </c>
     </row>
     <row r="59">
@@ -2964,13 +2964,13 @@
         <v>-</v>
       </c>
       <c r="C59">
-        <v>14.7</v>
+        <v>14.6</v>
       </c>
       <c r="D59">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="E59">
-        <v>0</v>
+        <v>-0.6802721088435374</v>
       </c>
       <c r="F59">
         <v>14.7</v>
@@ -2979,31 +2979,31 @@
         <v>14.8</v>
       </c>
       <c r="H59">
+        <v>14.4</v>
+      </c>
+      <c r="I59">
+        <v>1076500</v>
+      </c>
+      <c r="J59">
+        <v>15770.725</v>
+      </c>
+      <c r="K59">
+        <v>33282084</v>
+      </c>
+      <c r="L59">
+        <v>485581.9636</v>
+      </c>
+      <c r="M59">
+        <v>1698500</v>
+      </c>
+      <c r="N59">
+        <v>14.5</v>
+      </c>
+      <c r="O59">
         <v>14.6</v>
       </c>
-      <c r="I59">
-        <v>0</v>
-      </c>
-      <c r="J59">
-        <v>0</v>
-      </c>
-      <c r="K59">
-        <v>11804881</v>
-      </c>
-      <c r="L59">
-        <v>173815.2965</v>
-      </c>
-      <c r="M59">
-        <v>2315500</v>
-      </c>
-      <c r="N59">
-        <v>14.7</v>
-      </c>
-      <c r="O59">
-        <v>14.8</v>
-      </c>
       <c r="P59">
-        <v>1376800</v>
+        <v>1132700</v>
       </c>
     </row>
     <row r="60">
@@ -3014,22 +3014,22 @@
         <v>-</v>
       </c>
       <c r="C60">
-        <v>31.5</v>
+        <v>31.25</v>
       </c>
       <c r="D60">
-        <v>0.5</v>
+        <v>-0.25</v>
       </c>
       <c r="E60">
-        <v>1.6129032258064515</v>
+        <v>-0.7936507936507936</v>
       </c>
       <c r="F60">
-        <v>31.5</v>
+        <v>31.75</v>
       </c>
       <c r="G60">
-        <v>32.25</v>
+        <v>31.75</v>
       </c>
       <c r="H60">
-        <v>31.5</v>
+        <v>31</v>
       </c>
       <c r="I60">
         <v>0</v>
@@ -3038,13 +3038,13 @@
         <v>0</v>
       </c>
       <c r="K60">
-        <v>521964</v>
+        <v>251640</v>
       </c>
       <c r="L60">
-        <v>16558.09075</v>
+        <v>7885.956</v>
       </c>
       <c r="M60">
-        <v>17800</v>
+        <v>9800</v>
       </c>
       <c r="N60">
         <v>31.25</v>
@@ -3053,7 +3053,7 @@
         <v>31.5</v>
       </c>
       <c r="P60">
-        <v>6700</v>
+        <v>53100</v>
       </c>
     </row>
     <row r="61">
@@ -3064,22 +3064,22 @@
         <v>-</v>
       </c>
       <c r="C61">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="D61">
-        <v>-0.1</v>
+        <v>-0.3</v>
       </c>
       <c r="E61">
-        <v>-0.8</v>
+        <v>-2.4193548387096775</v>
       </c>
       <c r="F61">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="G61">
-        <v>12.7</v>
+        <v>12.5</v>
       </c>
       <c r="H61">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="I61">
         <v>0</v>
@@ -3088,22 +3088,22 @@
         <v>0</v>
       </c>
       <c r="K61">
-        <v>3613668</v>
+        <v>4461052</v>
       </c>
       <c r="L61">
-        <v>45327.817299999995</v>
+        <v>54519.0479</v>
       </c>
       <c r="M61">
-        <v>656600</v>
+        <v>579500</v>
       </c>
       <c r="N61">
-        <v>12.4</v>
+        <v>12.1</v>
       </c>
       <c r="O61">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="P61">
-        <v>15000</v>
+        <v>90000</v>
       </c>
     </row>
     <row r="62">
@@ -3114,22 +3114,22 @@
         <v>-</v>
       </c>
       <c r="C62">
+        <v>72</v>
+      </c>
+      <c r="D62">
+        <v>-0.5</v>
+      </c>
+      <c r="E62">
+        <v>-0.6896551724137931</v>
+      </c>
+      <c r="F62">
         <v>72.5</v>
       </c>
-      <c r="D62">
-        <v>-0.25</v>
-      </c>
-      <c r="E62">
-        <v>-0.3436426116838488</v>
-      </c>
-      <c r="F62">
+      <c r="G62">
         <v>72.75</v>
       </c>
-      <c r="G62">
-        <v>73</v>
-      </c>
       <c r="H62">
-        <v>72.25</v>
+        <v>71.5</v>
       </c>
       <c r="I62">
         <v>0</v>
@@ -3138,22 +3138,22 @@
         <v>0</v>
       </c>
       <c r="K62">
-        <v>1572591</v>
+        <v>3001482</v>
       </c>
       <c r="L62">
-        <v>114134.26675</v>
+        <v>215776.429</v>
       </c>
       <c r="M62">
-        <v>25400</v>
+        <v>136700</v>
       </c>
       <c r="N62">
-        <v>72.5</v>
+        <v>71.75</v>
       </c>
       <c r="O62">
-        <v>72.75</v>
+        <v>72</v>
       </c>
       <c r="P62">
-        <v>154600</v>
+        <v>63900</v>
       </c>
     </row>
     <row r="63">
@@ -3164,23 +3164,23 @@
         <v>-</v>
       </c>
       <c r="C63">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="D63">
-        <v>-0.02</v>
+        <v>0.06</v>
       </c>
       <c r="E63">
-        <v>-0.6535947712418301</v>
+        <v>1.9736842105263157</v>
       </c>
       <c r="F63">
+        <v>3.08</v>
+      </c>
+      <c r="G63">
+        <v>3.18</v>
+      </c>
+      <c r="H63">
         <v>3.06</v>
       </c>
-      <c r="G63">
-        <v>3.08</v>
-      </c>
-      <c r="H63">
-        <v>3.04</v>
-      </c>
       <c r="I63">
         <v>0</v>
       </c>
@@ -3188,22 +3188,22 @@
         <v>0</v>
       </c>
       <c r="K63">
-        <v>19508263</v>
+        <v>281845700</v>
       </c>
       <c r="L63">
-        <v>59583.11662</v>
+        <v>882113.9228</v>
       </c>
       <c r="M63">
-        <v>10848100</v>
+        <v>7637400</v>
       </c>
       <c r="N63">
-        <v>3.04</v>
+        <v>3.1</v>
       </c>
       <c r="O63">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="P63">
-        <v>1410300</v>
+        <v>1252800</v>
       </c>
     </row>
     <row r="64">
@@ -3214,46 +3214,46 @@
         <v>-</v>
       </c>
       <c r="C64">
+        <v>4.08</v>
+      </c>
+      <c r="D64">
+        <v>-0.04</v>
+      </c>
+      <c r="E64">
+        <v>-0.970873786407767</v>
+      </c>
+      <c r="F64">
         <v>4.12</v>
       </c>
-      <c r="D64">
-        <v>-0.02</v>
-      </c>
-      <c r="E64">
-        <v>-0.4830917874396135</v>
-      </c>
-      <c r="F64">
-        <v>4.2</v>
-      </c>
       <c r="G64">
-        <v>4.22</v>
+        <v>4.12</v>
       </c>
       <c r="H64">
+        <v>4.04</v>
+      </c>
+      <c r="I64">
+        <v>0</v>
+      </c>
+      <c r="J64">
+        <v>0</v>
+      </c>
+      <c r="K64">
+        <v>5315361</v>
+      </c>
+      <c r="L64">
+        <v>21669.274920000003</v>
+      </c>
+      <c r="M64">
+        <v>35700</v>
+      </c>
+      <c r="N64">
         <v>4.06</v>
       </c>
-      <c r="I64">
-        <v>0</v>
-      </c>
-      <c r="J64">
-        <v>0</v>
-      </c>
-      <c r="K64">
-        <v>26726143</v>
-      </c>
-      <c r="L64">
-        <v>110904.4647</v>
-      </c>
-      <c r="M64">
-        <v>186900</v>
-      </c>
-      <c r="N64">
-        <v>4.1</v>
-      </c>
       <c r="O64">
-        <v>4.12</v>
+        <v>4.08</v>
       </c>
       <c r="P64">
-        <v>146000</v>
+        <v>270100</v>
       </c>
     </row>
     <row r="65">
@@ -3264,37 +3264,37 @@
         <v>-</v>
       </c>
       <c r="C65">
+        <v>40.75</v>
+      </c>
+      <c r="D65">
+        <v>0.25</v>
+      </c>
+      <c r="E65">
+        <v>0.6172839506172839</v>
+      </c>
+      <c r="F65">
         <v>40.5</v>
       </c>
-      <c r="D65">
-        <v>-0.5</v>
-      </c>
-      <c r="E65">
-        <v>-1.2195121951219512</v>
-      </c>
-      <c r="F65">
-        <v>40.75</v>
-      </c>
       <c r="G65">
-        <v>41</v>
+        <v>41.5</v>
       </c>
       <c r="H65">
-        <v>40.25</v>
+        <v>40.5</v>
       </c>
       <c r="I65">
-        <v>69700</v>
+        <v>298100</v>
       </c>
       <c r="J65">
-        <v>2822.85</v>
+        <v>12147.575</v>
       </c>
       <c r="K65">
-        <v>11842657</v>
+        <v>13513473</v>
       </c>
       <c r="L65">
-        <v>481125.65975</v>
+        <v>554274.7775</v>
       </c>
       <c r="M65">
-        <v>181400</v>
+        <v>2086200</v>
       </c>
       <c r="N65">
         <v>40.5</v>
@@ -3303,7 +3303,7 @@
         <v>40.75</v>
       </c>
       <c r="P65">
-        <v>641100</v>
+        <v>58500</v>
       </c>
     </row>
     <row r="66">
@@ -3314,46 +3314,46 @@
         <v>-</v>
       </c>
       <c r="C66">
+        <v>20.4</v>
+      </c>
+      <c r="D66">
+        <v>-0.3</v>
+      </c>
+      <c r="E66">
+        <v>-1.4492753623188406</v>
+      </c>
+      <c r="F66">
         <v>20.7</v>
       </c>
-      <c r="D66">
-        <v>-0.2</v>
-      </c>
-      <c r="E66">
-        <v>-0.9569377990430622</v>
-      </c>
-      <c r="F66">
-        <v>20.8</v>
-      </c>
       <c r="G66">
-        <v>21</v>
+        <v>20.7</v>
       </c>
       <c r="H66">
+        <v>19.9</v>
+      </c>
+      <c r="I66">
+        <v>0</v>
+      </c>
+      <c r="J66">
+        <v>0</v>
+      </c>
+      <c r="K66">
+        <v>7581343</v>
+      </c>
+      <c r="L66">
+        <v>153631.8931</v>
+      </c>
+      <c r="M66">
+        <v>479600</v>
+      </c>
+      <c r="N66">
+        <v>20.4</v>
+      </c>
+      <c r="O66">
         <v>20.5</v>
       </c>
-      <c r="I66">
-        <v>0</v>
-      </c>
-      <c r="J66">
-        <v>0</v>
-      </c>
-      <c r="K66">
-        <v>5033514</v>
-      </c>
-      <c r="L66">
-        <v>104421.0835</v>
-      </c>
-      <c r="M66">
-        <v>167300</v>
-      </c>
-      <c r="N66">
-        <v>20.6</v>
-      </c>
-      <c r="O66">
-        <v>20.7</v>
-      </c>
       <c r="P66">
-        <v>10300</v>
+        <v>1200</v>
       </c>
     </row>
     <row r="67">
@@ -3367,13 +3367,13 @@
         <v>143.5</v>
       </c>
       <c r="D67">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="E67">
-        <v>-0.3472222222222222</v>
+        <v>0</v>
       </c>
       <c r="F67">
-        <v>144</v>
+        <v>143.5</v>
       </c>
       <c r="G67">
         <v>144.5</v>
@@ -3382,19 +3382,19 @@
         <v>143.5</v>
       </c>
       <c r="I67">
-        <v>500000</v>
+        <v>268000</v>
       </c>
       <c r="J67">
-        <v>72000</v>
+        <v>38575</v>
       </c>
       <c r="K67">
-        <v>7124224</v>
+        <v>6388329</v>
       </c>
       <c r="L67">
-        <v>1025018.0965</v>
+        <v>918999.6015</v>
       </c>
       <c r="M67">
-        <v>1601200</v>
+        <v>1529100</v>
       </c>
       <c r="N67">
         <v>143.5</v>
@@ -3403,7 +3403,7 @@
         <v>144</v>
       </c>
       <c r="P67">
-        <v>163200</v>
+        <v>117600</v>
       </c>
     </row>
     <row r="68">
@@ -3414,46 +3414,46 @@
         <v>-</v>
       </c>
       <c r="C68">
-        <v>18.3</v>
+        <v>18.1</v>
       </c>
       <c r="D68">
-        <v>-0.3</v>
+        <v>-0.2</v>
       </c>
       <c r="E68">
-        <v>-1.6129032258064515</v>
+        <v>-1.092896174863388</v>
       </c>
       <c r="F68">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="G68">
-        <v>18.7</v>
+        <v>18.4</v>
       </c>
       <c r="H68">
+        <v>18.1</v>
+      </c>
+      <c r="I68">
+        <v>0</v>
+      </c>
+      <c r="J68">
+        <v>0</v>
+      </c>
+      <c r="K68">
+        <v>2402994</v>
+      </c>
+      <c r="L68">
+        <v>43820.721</v>
+      </c>
+      <c r="M68">
+        <v>163700</v>
+      </c>
+      <c r="N68">
+        <v>18.1</v>
+      </c>
+      <c r="O68">
         <v>18.2</v>
       </c>
-      <c r="I68">
-        <v>0</v>
-      </c>
-      <c r="J68">
-        <v>0</v>
-      </c>
-      <c r="K68">
-        <v>2231293</v>
-      </c>
-      <c r="L68">
-        <v>40973.5248</v>
-      </c>
-      <c r="M68">
-        <v>130400</v>
-      </c>
-      <c r="N68">
-        <v>18.3</v>
-      </c>
-      <c r="O68">
-        <v>18.4</v>
-      </c>
       <c r="P68">
-        <v>30900</v>
+        <v>18400</v>
       </c>
     </row>
     <row r="69">
@@ -3464,46 +3464,46 @@
         <v>-</v>
       </c>
       <c r="C69">
+        <v>67</v>
+      </c>
+      <c r="D69">
+        <v>-0.5</v>
+      </c>
+      <c r="E69">
+        <v>-0.7407407407407407</v>
+      </c>
+      <c r="F69">
         <v>67.5</v>
       </c>
-      <c r="D69">
-        <v>-1</v>
-      </c>
-      <c r="E69">
-        <v>-1.4598540145985401</v>
-      </c>
-      <c r="F69">
-        <v>68.5</v>
-      </c>
       <c r="G69">
-        <v>68.5</v>
+        <v>67.75</v>
       </c>
       <c r="H69">
+        <v>67</v>
+      </c>
+      <c r="I69">
+        <v>0</v>
+      </c>
+      <c r="J69">
+        <v>0</v>
+      </c>
+      <c r="K69">
+        <v>6480541</v>
+      </c>
+      <c r="L69">
+        <v>435661.81975</v>
+      </c>
+      <c r="M69">
+        <v>103900</v>
+      </c>
+      <c r="N69">
+        <v>67</v>
+      </c>
+      <c r="O69">
         <v>67.25</v>
       </c>
-      <c r="I69">
-        <v>600000</v>
-      </c>
-      <c r="J69">
-        <v>40500</v>
-      </c>
-      <c r="K69">
-        <v>9986259</v>
-      </c>
-      <c r="L69">
-        <v>675593.27775</v>
-      </c>
-      <c r="M69">
-        <v>688400</v>
-      </c>
-      <c r="N69">
-        <v>67.25</v>
-      </c>
-      <c r="O69">
-        <v>67.5</v>
-      </c>
       <c r="P69">
-        <v>110400</v>
+        <v>227700</v>
       </c>
     </row>
     <row r="70">
@@ -3514,22 +3514,22 @@
         <v>-</v>
       </c>
       <c r="C70">
-        <v>17.2</v>
+        <v>17.1</v>
       </c>
       <c r="D70">
-        <v>-0.2</v>
+        <v>-0.1</v>
       </c>
       <c r="E70">
-        <v>-1.1494252873563218</v>
+        <v>-0.5813953488372093</v>
       </c>
       <c r="F70">
         <v>17.3</v>
       </c>
       <c r="G70">
-        <v>17.4</v>
+        <v>17.3</v>
       </c>
       <c r="H70">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="I70">
         <v>0</v>
@@ -3538,22 +3538,22 @@
         <v>0</v>
       </c>
       <c r="K70">
-        <v>37917040</v>
+        <v>48659237</v>
       </c>
       <c r="L70">
-        <v>654660.8281</v>
+        <v>833459.7826</v>
       </c>
       <c r="M70">
-        <v>6309000</v>
+        <v>9581700</v>
       </c>
       <c r="N70">
-        <v>17.2</v>
+        <v>17</v>
       </c>
       <c r="O70">
-        <v>17.3</v>
+        <v>17.1</v>
       </c>
       <c r="P70">
-        <v>3186300</v>
+        <v>971100</v>
       </c>
     </row>
     <row r="71">
@@ -3567,34 +3567,34 @@
         <v>58</v>
       </c>
       <c r="D71">
-        <v>-0.75</v>
+        <v>0</v>
       </c>
       <c r="E71">
-        <v>-1.2765957446808511</v>
+        <v>0</v>
       </c>
       <c r="F71">
+        <v>57.75</v>
+      </c>
+      <c r="G71">
         <v>58.75</v>
       </c>
-      <c r="G71">
-        <v>59</v>
-      </c>
       <c r="H71">
-        <v>57.5</v>
+        <v>57.75</v>
       </c>
       <c r="I71">
-        <v>4000000</v>
+        <v>2084000</v>
       </c>
       <c r="J71">
-        <v>222500</v>
+        <v>121872</v>
       </c>
       <c r="K71">
-        <v>13144003</v>
+        <v>5206216</v>
       </c>
       <c r="L71">
-        <v>751904.0455</v>
+        <v>303187.6635</v>
       </c>
       <c r="M71">
-        <v>1194900</v>
+        <v>861100</v>
       </c>
       <c r="N71">
         <v>57.75</v>
@@ -3603,7 +3603,7 @@
         <v>58</v>
       </c>
       <c r="P71">
-        <v>78100</v>
+        <v>377600</v>
       </c>
     </row>
     <row r="72">
@@ -3614,19 +3614,19 @@
         <v>-</v>
       </c>
       <c r="C72">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="D72">
         <v>-0.2</v>
       </c>
       <c r="E72">
-        <v>-1.0638297872340425</v>
+        <v>-1.075268817204301</v>
       </c>
       <c r="F72">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="G72">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="H72">
         <v>18.4</v>
@@ -3638,22 +3638,22 @@
         <v>0</v>
       </c>
       <c r="K72">
-        <v>1235687</v>
+        <v>2692783</v>
       </c>
       <c r="L72">
-        <v>23003.4544</v>
+        <v>50277.9519</v>
       </c>
       <c r="M72">
-        <v>122700</v>
+        <v>107600</v>
       </c>
       <c r="N72">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="O72">
-        <v>18.7</v>
+        <v>18.5</v>
       </c>
       <c r="P72">
-        <v>20100</v>
+        <v>79800</v>
       </c>
     </row>
     <row r="73">
@@ -3664,22 +3664,22 @@
         <v>-</v>
       </c>
       <c r="C73">
+        <v>50.75</v>
+      </c>
+      <c r="D73">
+        <v>-0.75</v>
+      </c>
+      <c r="E73">
+        <v>-1.4563106796116505</v>
+      </c>
+      <c r="F73">
         <v>51.5</v>
-      </c>
-      <c r="D73">
-        <v>-0.25</v>
-      </c>
-      <c r="E73">
-        <v>-0.4830917874396135</v>
-      </c>
-      <c r="F73">
-        <v>51.75</v>
       </c>
       <c r="G73">
         <v>52</v>
       </c>
       <c r="H73">
-        <v>50.5</v>
+        <v>50.75</v>
       </c>
       <c r="I73">
         <v>0</v>
@@ -3688,22 +3688,22 @@
         <v>0</v>
       </c>
       <c r="K73">
-        <v>2419856</v>
+        <v>1412541</v>
       </c>
       <c r="L73">
-        <v>124190.05275</v>
+        <v>72185.227</v>
       </c>
       <c r="M73">
-        <v>307500</v>
+        <v>103800</v>
       </c>
       <c r="N73">
-        <v>51.5</v>
+        <v>50.75</v>
       </c>
       <c r="O73">
-        <v>51.75</v>
+        <v>51</v>
       </c>
       <c r="P73">
-        <v>22200</v>
+        <v>16500</v>
       </c>
     </row>
     <row r="74">
@@ -3714,16 +3714,16 @@
         <v>-</v>
       </c>
       <c r="C74">
+        <v>33.5</v>
+      </c>
+      <c r="D74">
+        <v>0.25</v>
+      </c>
+      <c r="E74">
+        <v>0.7518796992481203</v>
+      </c>
+      <c r="F74">
         <v>33.25</v>
-      </c>
-      <c r="D74">
-        <v>-0.25</v>
-      </c>
-      <c r="E74">
-        <v>-0.746268656716418</v>
-      </c>
-      <c r="F74">
-        <v>33.5</v>
       </c>
       <c r="G74">
         <v>33.75</v>
@@ -3732,19 +3732,19 @@
         <v>33</v>
       </c>
       <c r="I74">
-        <v>374700</v>
+        <v>0</v>
       </c>
       <c r="J74">
-        <v>12458.775</v>
+        <v>0</v>
       </c>
       <c r="K74">
-        <v>26462523</v>
+        <v>16398461</v>
       </c>
       <c r="L74">
-        <v>882109.52025</v>
+        <v>548487.3465</v>
       </c>
       <c r="M74">
-        <v>3142800</v>
+        <v>1959200</v>
       </c>
       <c r="N74">
         <v>33.25</v>
@@ -3753,7 +3753,7 @@
         <v>33.5</v>
       </c>
       <c r="P74">
-        <v>2900500</v>
+        <v>139700</v>
       </c>
     </row>
     <row r="75">
@@ -3764,46 +3764,46 @@
         <v>-</v>
       </c>
       <c r="C75">
-        <v>37</v>
+        <v>36.5</v>
       </c>
       <c r="D75">
-        <v>-1.75</v>
+        <v>-0.5</v>
       </c>
       <c r="E75">
-        <v>-4.516129032258065</v>
+        <v>-1.3513513513513513</v>
       </c>
       <c r="F75">
-        <v>38.75</v>
+        <v>37.25</v>
       </c>
       <c r="G75">
-        <v>39</v>
+        <v>37.25</v>
       </c>
       <c r="H75">
+        <v>36.5</v>
+      </c>
+      <c r="I75">
+        <v>5784200</v>
+      </c>
+      <c r="J75">
+        <v>211123.3</v>
+      </c>
+      <c r="K75">
+        <v>16187987</v>
+      </c>
+      <c r="L75">
+        <v>595110.356</v>
+      </c>
+      <c r="M75">
+        <v>1123200</v>
+      </c>
+      <c r="N75">
+        <v>36.5</v>
+      </c>
+      <c r="O75">
         <v>36.75</v>
       </c>
-      <c r="I75">
-        <v>519800</v>
-      </c>
-      <c r="J75">
-        <v>19232.6</v>
-      </c>
-      <c r="K75">
-        <v>35140049</v>
-      </c>
-      <c r="L75">
-        <v>1317204.382</v>
-      </c>
-      <c r="M75">
-        <v>1845900</v>
-      </c>
-      <c r="N75">
-        <v>36.75</v>
-      </c>
-      <c r="O75">
-        <v>37</v>
-      </c>
       <c r="P75">
-        <v>58000</v>
+        <v>183500</v>
       </c>
     </row>
     <row r="76">
@@ -3814,46 +3814,46 @@
         <v>-</v>
       </c>
       <c r="C76">
+        <v>6.35</v>
+      </c>
+      <c r="D76">
+        <v>-0.1</v>
+      </c>
+      <c r="E76">
+        <v>-1.550387596899225</v>
+      </c>
+      <c r="F76">
         <v>6.45</v>
-      </c>
-      <c r="D76">
-        <v>-0.05</v>
-      </c>
-      <c r="E76">
-        <v>-0.7692307692307693</v>
-      </c>
-      <c r="F76">
-        <v>6.5</v>
       </c>
       <c r="G76">
         <v>6.5</v>
       </c>
       <c r="H76">
+        <v>6.3</v>
+      </c>
+      <c r="I76">
+        <v>0</v>
+      </c>
+      <c r="J76">
+        <v>0</v>
+      </c>
+      <c r="K76">
+        <v>13085955</v>
+      </c>
+      <c r="L76">
+        <v>83386.8573</v>
+      </c>
+      <c r="M76">
+        <v>443300</v>
+      </c>
+      <c r="N76">
+        <v>6.35</v>
+      </c>
+      <c r="O76">
         <v>6.4</v>
       </c>
-      <c r="I76">
-        <v>0</v>
-      </c>
-      <c r="J76">
-        <v>0</v>
-      </c>
-      <c r="K76">
-        <v>5084039</v>
-      </c>
-      <c r="L76">
-        <v>32840.1161</v>
-      </c>
-      <c r="M76">
-        <v>1176800</v>
-      </c>
-      <c r="N76">
-        <v>6.4</v>
-      </c>
-      <c r="O76">
-        <v>6.45</v>
-      </c>
       <c r="P76">
-        <v>136400</v>
+        <v>515300</v>
       </c>
     </row>
     <row r="77">
@@ -3864,22 +3864,22 @@
         <v>-</v>
       </c>
       <c r="C77">
-        <v>5.65</v>
+        <v>5.6</v>
       </c>
       <c r="D77">
         <v>-0.05</v>
       </c>
       <c r="E77">
-        <v>-0.8771929824561403</v>
+        <v>-0.8849557522123894</v>
       </c>
       <c r="F77">
-        <v>5.75</v>
+        <v>5.7</v>
       </c>
       <c r="G77">
         <v>5.75</v>
       </c>
       <c r="H77">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="I77">
         <v>0</v>
@@ -3888,22 +3888,22 @@
         <v>0</v>
       </c>
       <c r="K77">
-        <v>4374247</v>
+        <v>2873399</v>
       </c>
       <c r="L77">
-        <v>24894.49825</v>
+        <v>16197.22175</v>
       </c>
       <c r="M77">
-        <v>322000</v>
+        <v>349500</v>
       </c>
       <c r="N77">
-        <v>5.65</v>
+        <v>5.55</v>
       </c>
       <c r="O77">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="P77">
-        <v>10500</v>
+        <v>3400</v>
       </c>
     </row>
     <row r="78">
@@ -3914,22 +3914,22 @@
         <v>-</v>
       </c>
       <c r="C78">
+        <v>5.85</v>
+      </c>
+      <c r="D78">
+        <v>-0.15</v>
+      </c>
+      <c r="E78">
+        <v>-2.5</v>
+      </c>
+      <c r="F78">
         <v>6</v>
       </c>
-      <c r="D78">
-        <v>0</v>
-      </c>
-      <c r="E78">
-        <v>0</v>
-      </c>
-      <c r="F78">
-        <v>6.05</v>
-      </c>
       <c r="G78">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="H78">
-        <v>5.95</v>
+        <v>5.8</v>
       </c>
       <c r="I78">
         <v>0</v>
@@ -3938,22 +3938,22 @@
         <v>0</v>
       </c>
       <c r="K78">
-        <v>1057658</v>
+        <v>2109398</v>
       </c>
       <c r="L78">
-        <v>6319.468</v>
+        <v>12391.20655</v>
       </c>
       <c r="M78">
-        <v>25100</v>
+        <v>120400</v>
       </c>
       <c r="N78">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="O78">
-        <v>6.05</v>
+        <v>5.85</v>
       </c>
       <c r="P78">
-        <v>430700</v>
+        <v>4000</v>
       </c>
     </row>
     <row r="79">
@@ -3964,46 +3964,46 @@
         <v>-</v>
       </c>
       <c r="C79">
+        <v>22.2</v>
+      </c>
+      <c r="D79">
+        <v>-0.1</v>
+      </c>
+      <c r="E79">
+        <v>-0.4484304932735426</v>
+      </c>
+      <c r="F79">
         <v>22.3</v>
       </c>
-      <c r="D79">
-        <v>-0.2</v>
-      </c>
-      <c r="E79">
-        <v>-0.8888888888888888</v>
-      </c>
-      <c r="F79">
-        <v>22.5</v>
-      </c>
       <c r="G79">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="H79">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="I79">
-        <v>87500</v>
+        <v>212000</v>
       </c>
       <c r="J79">
-        <v>1951.25</v>
+        <v>4706.4</v>
       </c>
       <c r="K79">
-        <v>10067522</v>
+        <v>15970538</v>
       </c>
       <c r="L79">
-        <v>225402.4148</v>
+        <v>354820.56639999995</v>
       </c>
       <c r="M79">
-        <v>2745000</v>
+        <v>3590900</v>
       </c>
       <c r="N79">
-        <v>22.3</v>
+        <v>22.1</v>
       </c>
       <c r="O79">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="P79">
-        <v>658200</v>
+        <v>1371000</v>
       </c>
     </row>
     <row r="80">
@@ -4026,10 +4026,10 @@
         <v>11.8</v>
       </c>
       <c r="G80">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="H80">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="I80">
         <v>0</v>
@@ -4038,13 +4038,13 @@
         <v>0</v>
       </c>
       <c r="K80">
-        <v>8430180</v>
+        <v>2906473</v>
       </c>
       <c r="L80">
-        <v>98138.46029999999</v>
+        <v>34136.7525</v>
       </c>
       <c r="M80">
-        <v>115300</v>
+        <v>877600</v>
       </c>
       <c r="N80">
         <v>11.7</v>
@@ -4053,7 +4053,7 @@
         <v>11.8</v>
       </c>
       <c r="P80">
-        <v>439100</v>
+        <v>334500</v>
       </c>
     </row>
     <row r="81">
@@ -4064,37 +4064,37 @@
         <v>-</v>
       </c>
       <c r="C81">
+        <v>28.25</v>
+      </c>
+      <c r="D81">
+        <v>-0.25</v>
+      </c>
+      <c r="E81">
+        <v>-0.8771929824561403</v>
+      </c>
+      <c r="F81">
         <v>28.5</v>
-      </c>
-      <c r="D81">
-        <v>0.25</v>
-      </c>
-      <c r="E81">
-        <v>0.8849557522123894</v>
-      </c>
-      <c r="F81">
-        <v>28.25</v>
       </c>
       <c r="G81">
         <v>28.5</v>
       </c>
       <c r="H81">
-        <v>28</v>
+        <v>28.25</v>
       </c>
       <c r="I81">
-        <v>0</v>
+        <v>804100</v>
       </c>
       <c r="J81">
-        <v>0</v>
+        <v>22715.825</v>
       </c>
       <c r="K81">
-        <v>5471542</v>
+        <v>2828867</v>
       </c>
       <c r="L81">
-        <v>154774.204</v>
+        <v>79952.18825</v>
       </c>
       <c r="M81">
-        <v>760700</v>
+        <v>1505600</v>
       </c>
       <c r="N81">
         <v>28.25</v>
@@ -4103,7 +4103,7 @@
         <v>28.5</v>
       </c>
       <c r="P81">
-        <v>714100</v>
+        <v>753900</v>
       </c>
     </row>
     <row r="82">
@@ -4114,22 +4114,22 @@
         <v>-</v>
       </c>
       <c r="C82">
-        <v>8.9</v>
+        <v>9.15</v>
       </c>
       <c r="D82">
-        <v>-0.1</v>
+        <v>0.25</v>
       </c>
       <c r="E82">
-        <v>-1.1111111111111112</v>
+        <v>2.808988764044944</v>
       </c>
       <c r="F82">
         <v>8.9</v>
       </c>
       <c r="G82">
-        <v>9</v>
+        <v>9.3</v>
       </c>
       <c r="H82">
-        <v>8.7</v>
+        <v>8.85</v>
       </c>
       <c r="I82">
         <v>0</v>
@@ -4138,22 +4138,22 @@
         <v>0</v>
       </c>
       <c r="K82">
-        <v>32374692</v>
+        <v>55391165</v>
       </c>
       <c r="L82">
-        <v>286589.20310000004</v>
+        <v>501629.34745</v>
       </c>
       <c r="M82">
-        <v>9800</v>
+        <v>1040100</v>
       </c>
       <c r="N82">
-        <v>8.9</v>
+        <v>9.15</v>
       </c>
       <c r="O82">
-        <v>8.95</v>
+        <v>9.2</v>
       </c>
       <c r="P82">
-        <v>1105600</v>
+        <v>2017200</v>
       </c>
     </row>
     <row r="83">
@@ -4167,19 +4167,19 @@
         <v>9.65</v>
       </c>
       <c r="D83">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E83">
-        <v>0.5208333333333334</v>
+        <v>0</v>
       </c>
       <c r="F83">
-        <v>9.55</v>
+        <v>9.65</v>
       </c>
       <c r="G83">
         <v>9.7</v>
       </c>
       <c r="H83">
-        <v>9.55</v>
+        <v>9.65</v>
       </c>
       <c r="I83">
         <v>0</v>
@@ -4188,13 +4188,13 @@
         <v>0</v>
       </c>
       <c r="K83">
-        <v>24233</v>
+        <v>67256</v>
       </c>
       <c r="L83">
-        <v>232.7922</v>
+        <v>649.65315</v>
       </c>
       <c r="M83">
-        <v>20600</v>
+        <v>6900</v>
       </c>
       <c r="N83">
         <v>9.6</v>
@@ -4203,7 +4203,7 @@
         <v>9.65</v>
       </c>
       <c r="P83">
-        <v>11700</v>
+        <v>24700</v>
       </c>
     </row>
     <row r="84">
@@ -4214,22 +4214,22 @@
         <v>-</v>
       </c>
       <c r="C84">
+        <v>20.5</v>
+      </c>
+      <c r="D84">
+        <v>0.5</v>
+      </c>
+      <c r="E84">
+        <v>2.5</v>
+      </c>
+      <c r="F84">
         <v>20</v>
       </c>
-      <c r="D84">
-        <v>0.1</v>
-      </c>
-      <c r="E84">
-        <v>0.5025125628140703</v>
-      </c>
-      <c r="F84">
-        <v>19.8</v>
-      </c>
       <c r="G84">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="H84">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="I84">
         <v>0</v>
@@ -4238,22 +4238,22 @@
         <v>0</v>
       </c>
       <c r="K84">
-        <v>1248209</v>
+        <v>2778652</v>
       </c>
       <c r="L84">
-        <v>24861.0687</v>
+        <v>56473.4789</v>
       </c>
       <c r="M84">
-        <v>73000</v>
+        <v>24200</v>
       </c>
       <c r="N84">
-        <v>20</v>
+        <v>20.4</v>
       </c>
       <c r="O84">
-        <v>20.1</v>
+        <v>20.5</v>
       </c>
       <c r="P84">
-        <v>126800</v>
+        <v>42000</v>
       </c>
     </row>
     <row r="85">
@@ -4264,16 +4264,16 @@
         <v>-</v>
       </c>
       <c r="C85">
+        <v>13.3</v>
+      </c>
+      <c r="D85">
+        <v>-0.1</v>
+      </c>
+      <c r="E85">
+        <v>-0.746268656716418</v>
+      </c>
+      <c r="F85">
         <v>13.4</v>
-      </c>
-      <c r="D85">
-        <v>0.1</v>
-      </c>
-      <c r="E85">
-        <v>0.7518796992481203</v>
-      </c>
-      <c r="F85">
-        <v>13.3</v>
       </c>
       <c r="G85">
         <v>13.4</v>
@@ -4288,22 +4288,22 @@
         <v>0</v>
       </c>
       <c r="K85">
-        <v>381025</v>
+        <v>452763</v>
       </c>
       <c r="L85">
-        <v>5083.5905</v>
+        <v>6024.3952</v>
       </c>
       <c r="M85">
-        <v>100100</v>
+        <v>361600</v>
       </c>
       <c r="N85">
+        <v>13.2</v>
+      </c>
+      <c r="O85">
         <v>13.3</v>
       </c>
-      <c r="O85">
-        <v>13.4</v>
-      </c>
       <c r="P85">
-        <v>15200</v>
+        <v>90600</v>
       </c>
     </row>
     <row r="86">
@@ -4317,16 +4317,16 @@
         <v>16.1</v>
       </c>
       <c r="D86">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="E86">
-        <v>-0.6172839506172839</v>
+        <v>0</v>
       </c>
       <c r="F86">
+        <v>16</v>
+      </c>
+      <c r="G86">
         <v>16.2</v>
-      </c>
-      <c r="G86">
-        <v>16.4</v>
       </c>
       <c r="H86">
         <v>16</v>
@@ -4338,13 +4338,13 @@
         <v>0</v>
       </c>
       <c r="K86">
-        <v>4381392</v>
+        <v>3321948</v>
       </c>
       <c r="L86">
-        <v>70741.9954</v>
+        <v>53462.680799999995</v>
       </c>
       <c r="M86">
-        <v>580600</v>
+        <v>47800</v>
       </c>
       <c r="N86">
         <v>16.1</v>
@@ -4353,7 +4353,7 @@
         <v>16.2</v>
       </c>
       <c r="P86">
-        <v>807600</v>
+        <v>513700</v>
       </c>
     </row>
     <row r="87">
@@ -4367,43 +4367,43 @@
         <v>13.3</v>
       </c>
       <c r="D87">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="E87">
-        <v>-1.4814814814814814</v>
+        <v>0</v>
       </c>
       <c r="F87">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="G87">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="H87">
+        <v>13.2</v>
+      </c>
+      <c r="I87">
+        <v>0</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>6115071</v>
+      </c>
+      <c r="L87">
+        <v>81326.6111</v>
+      </c>
+      <c r="M87">
+        <v>2786500</v>
+      </c>
+      <c r="N87">
+        <v>13.2</v>
+      </c>
+      <c r="O87">
         <v>13.3</v>
       </c>
-      <c r="I87">
-        <v>0</v>
-      </c>
-      <c r="J87">
-        <v>0</v>
-      </c>
-      <c r="K87">
-        <v>5654769</v>
-      </c>
-      <c r="L87">
-        <v>75620.2913</v>
-      </c>
-      <c r="M87">
-        <v>2709100</v>
-      </c>
-      <c r="N87">
-        <v>13.3</v>
-      </c>
-      <c r="O87">
-        <v>13.4</v>
-      </c>
       <c r="P87">
-        <v>528200</v>
+        <v>404800</v>
       </c>
     </row>
     <row r="88">
@@ -4414,13 +4414,13 @@
         <v>-</v>
       </c>
       <c r="C88">
-        <v>32.5</v>
+        <v>32.75</v>
       </c>
       <c r="D88">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="E88">
-        <v>-0.7633587786259542</v>
+        <v>0.7692307692307693</v>
       </c>
       <c r="F88">
         <v>32.75</v>
@@ -4438,13 +4438,13 @@
         <v>0</v>
       </c>
       <c r="K88">
-        <v>33729036</v>
+        <v>42273305</v>
       </c>
       <c r="L88">
-        <v>1100507.0125</v>
+        <v>1384108.04175</v>
       </c>
       <c r="M88">
-        <v>13937300</v>
+        <v>10710700</v>
       </c>
       <c r="N88">
         <v>32.5</v>
@@ -4453,7 +4453,7 @@
         <v>32.75</v>
       </c>
       <c r="P88">
-        <v>1785800</v>
+        <v>1246100</v>
       </c>
     </row>
     <row r="89">
@@ -4467,34 +4467,34 @@
         <v>165</v>
       </c>
       <c r="D89">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E89">
-        <v>0.6097560975609756</v>
+        <v>0</v>
       </c>
       <c r="F89">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="G89">
-        <v>165.5</v>
+        <v>167.5</v>
       </c>
       <c r="H89">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="I89">
-        <v>160000</v>
+        <v>11900</v>
       </c>
       <c r="J89">
-        <v>26240</v>
+        <v>1963.5</v>
       </c>
       <c r="K89">
-        <v>15544249</v>
+        <v>9754541</v>
       </c>
       <c r="L89">
-        <v>2560725.5295</v>
+        <v>1619306.919</v>
       </c>
       <c r="M89">
-        <v>810500</v>
+        <v>918900</v>
       </c>
       <c r="N89">
         <v>164.5</v>
@@ -4503,7 +4503,7 @@
         <v>165</v>
       </c>
       <c r="P89">
-        <v>30300</v>
+        <v>8100</v>
       </c>
     </row>
     <row r="90">
@@ -4514,46 +4514,46 @@
         <v>-</v>
       </c>
       <c r="C90">
-        <v>49.75</v>
+        <v>50</v>
       </c>
       <c r="D90">
         <v>0.25</v>
       </c>
       <c r="E90">
-        <v>0.5050505050505051</v>
+        <v>0.5025125628140703</v>
       </c>
       <c r="F90">
-        <v>49.25</v>
+        <v>49.75</v>
       </c>
       <c r="G90">
+        <v>51.25</v>
+      </c>
+      <c r="H90">
+        <v>49.5</v>
+      </c>
+      <c r="I90">
+        <v>0</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>18484688</v>
+      </c>
+      <c r="L90">
+        <v>933610.59825</v>
+      </c>
+      <c r="M90">
+        <v>332600</v>
+      </c>
+      <c r="N90">
         <v>50</v>
       </c>
-      <c r="H90">
-        <v>49.25</v>
-      </c>
-      <c r="I90">
-        <v>0</v>
-      </c>
-      <c r="J90">
-        <v>0</v>
-      </c>
-      <c r="K90">
-        <v>9366275</v>
-      </c>
-      <c r="L90">
-        <v>464101.732</v>
-      </c>
-      <c r="M90">
-        <v>1252000</v>
-      </c>
-      <c r="N90">
-        <v>49.5</v>
-      </c>
       <c r="O90">
-        <v>49.75</v>
+        <v>50.25</v>
       </c>
       <c r="P90">
-        <v>526900</v>
+        <v>2105600</v>
       </c>
     </row>
     <row r="91">
@@ -4564,23 +4564,23 @@
         <v>-</v>
       </c>
       <c r="C91">
+        <v>42.75</v>
+      </c>
+      <c r="D91">
+        <v>0.25</v>
+      </c>
+      <c r="E91">
+        <v>0.5882352941176471</v>
+      </c>
+      <c r="F91">
+        <v>42.75</v>
+      </c>
+      <c r="G91">
+        <v>43</v>
+      </c>
+      <c r="H91">
         <v>42.5</v>
       </c>
-      <c r="D91">
-        <v>-0.25</v>
-      </c>
-      <c r="E91">
-        <v>-0.5847953216374269</v>
-      </c>
-      <c r="F91">
-        <v>42.5</v>
-      </c>
-      <c r="G91">
-        <v>42.75</v>
-      </c>
-      <c r="H91">
-        <v>42.25</v>
-      </c>
       <c r="I91">
         <v>0</v>
       </c>
@@ -4588,13 +4588,13 @@
         <v>0</v>
       </c>
       <c r="K91">
-        <v>2231778</v>
+        <v>1720777</v>
       </c>
       <c r="L91">
-        <v>94917.6095</v>
+        <v>73573.31375</v>
       </c>
       <c r="M91">
-        <v>242100</v>
+        <v>392400</v>
       </c>
       <c r="N91">
         <v>42.5</v>
@@ -4603,7 +4603,7 @@
         <v>42.75</v>
       </c>
       <c r="P91">
-        <v>159700</v>
+        <v>183000</v>
       </c>
     </row>
     <row r="92">
@@ -4614,22 +4614,22 @@
         <v>-</v>
       </c>
       <c r="C92">
+        <v>18.1</v>
+      </c>
+      <c r="D92">
+        <v>0.8</v>
+      </c>
+      <c r="E92">
+        <v>4.624277456647399</v>
+      </c>
+      <c r="F92">
         <v>17.3</v>
       </c>
-      <c r="D92">
-        <v>-0.2</v>
-      </c>
-      <c r="E92">
-        <v>-1.1428571428571428</v>
-      </c>
-      <c r="F92">
-        <v>17.5</v>
-      </c>
       <c r="G92">
-        <v>17.6</v>
+        <v>18.4</v>
       </c>
       <c r="H92">
-        <v>17.2</v>
+        <v>17.3</v>
       </c>
       <c r="I92">
         <v>0</v>
@@ -4638,22 +4638,22 @@
         <v>0</v>
       </c>
       <c r="K92">
-        <v>4053447</v>
+        <v>22441062</v>
       </c>
       <c r="L92">
-        <v>70573.511</v>
+        <v>404501.9105</v>
       </c>
       <c r="M92">
-        <v>339300</v>
+        <v>216400</v>
       </c>
       <c r="N92">
-        <v>17.3</v>
+        <v>18</v>
       </c>
       <c r="O92">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="P92">
-        <v>18000</v>
+        <v>330200</v>
       </c>
     </row>
     <row r="93">
@@ -4664,22 +4664,22 @@
         <v>-</v>
       </c>
       <c r="C93">
+        <v>2.02</v>
+      </c>
+      <c r="D93">
+        <v>-0.02</v>
+      </c>
+      <c r="E93">
+        <v>-0.9803921568627451</v>
+      </c>
+      <c r="F93">
         <v>2.04</v>
-      </c>
-      <c r="D93">
-        <v>0.04</v>
-      </c>
-      <c r="E93">
-        <v>2</v>
-      </c>
-      <c r="F93">
-        <v>2.02</v>
       </c>
       <c r="G93">
         <v>2.04</v>
       </c>
       <c r="H93">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="I93">
         <v>0</v>
@@ -4688,22 +4688,22 @@
         <v>0</v>
       </c>
       <c r="K93">
-        <v>7185045</v>
+        <v>12814282</v>
       </c>
       <c r="L93">
-        <v>14467.114300000001</v>
+        <v>25660.95544</v>
       </c>
       <c r="M93">
-        <v>903500</v>
+        <v>364300</v>
       </c>
       <c r="N93">
         <v>2</v>
       </c>
       <c r="O93">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="P93">
-        <v>531000</v>
+        <v>1194700</v>
       </c>
     </row>
     <row r="94">
@@ -4714,19 +4714,19 @@
         <v>-</v>
       </c>
       <c r="C94">
+        <v>26.25</v>
+      </c>
+      <c r="D94">
+        <v>0.5</v>
+      </c>
+      <c r="E94">
+        <v>1.941747572815534</v>
+      </c>
+      <c r="F94">
         <v>25.75</v>
       </c>
-      <c r="D94">
-        <v>-0.25</v>
-      </c>
-      <c r="E94">
-        <v>-0.9615384615384616</v>
-      </c>
-      <c r="F94">
-        <v>26</v>
-      </c>
       <c r="G94">
-        <v>26.25</v>
+        <v>26.5</v>
       </c>
       <c r="H94">
         <v>25.5</v>
@@ -4738,22 +4738,22 @@
         <v>0</v>
       </c>
       <c r="K94">
-        <v>681003</v>
+        <v>1230305</v>
       </c>
       <c r="L94">
-        <v>17658.303</v>
+        <v>32190.806</v>
       </c>
       <c r="M94">
-        <v>43900</v>
+        <v>16500</v>
       </c>
       <c r="N94">
-        <v>25.75</v>
+        <v>26</v>
       </c>
       <c r="O94">
-        <v>26</v>
+        <v>26.25</v>
       </c>
       <c r="P94">
-        <v>35500</v>
+        <v>188200</v>
       </c>
     </row>
     <row r="95">
@@ -4767,43 +4767,43 @@
         <v>7.05</v>
       </c>
       <c r="D95">
-        <v>-0.2</v>
+        <v>0</v>
       </c>
       <c r="E95">
-        <v>-2.7586206896551726</v>
+        <v>0</v>
       </c>
       <c r="F95">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="G95">
-        <v>7.3</v>
+        <v>7.2</v>
       </c>
       <c r="H95">
+        <v>7.05</v>
+      </c>
+      <c r="I95">
+        <v>0</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>1732533</v>
+      </c>
+      <c r="L95">
+        <v>12272.0548</v>
+      </c>
+      <c r="M95">
+        <v>895300</v>
+      </c>
+      <c r="N95">
         <v>7</v>
       </c>
-      <c r="I95">
-        <v>0</v>
-      </c>
-      <c r="J95">
-        <v>0</v>
-      </c>
-      <c r="K95">
-        <v>2719032</v>
-      </c>
-      <c r="L95">
-        <v>19312.0583</v>
-      </c>
-      <c r="M95">
-        <v>160900</v>
-      </c>
-      <c r="N95">
+      <c r="O95">
         <v>7.05</v>
       </c>
-      <c r="O95">
-        <v>7.1</v>
-      </c>
       <c r="P95">
-        <v>91000</v>
+        <v>32700</v>
       </c>
     </row>
     <row r="96">
@@ -4814,22 +4814,22 @@
         <v>-</v>
       </c>
       <c r="C96">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="D96">
-        <v>3</v>
+        <v>0.5</v>
       </c>
       <c r="E96">
-        <v>6.0606060606060606</v>
+        <v>0.9523809523809523</v>
       </c>
       <c r="F96">
-        <v>50</v>
+        <v>52.75</v>
       </c>
       <c r="G96">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="H96">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I96">
         <v>0</v>
@@ -4838,22 +4838,22 @@
         <v>0</v>
       </c>
       <c r="K96">
-        <v>2552941</v>
+        <v>1154662</v>
       </c>
       <c r="L96">
-        <v>131784.8835</v>
+        <v>59962.5365</v>
       </c>
       <c r="M96">
-        <v>33900</v>
+        <v>800</v>
       </c>
       <c r="N96">
-        <v>51.75</v>
+        <v>52.25</v>
       </c>
       <c r="O96">
-        <v>52.5</v>
+        <v>53</v>
       </c>
       <c r="P96">
-        <v>9300</v>
+        <v>23100</v>
       </c>
     </row>
     <row r="97">
@@ -4864,22 +4864,22 @@
         <v>-</v>
       </c>
       <c r="C97">
+        <v>21.2</v>
+      </c>
+      <c r="D97">
+        <v>-0.3</v>
+      </c>
+      <c r="E97">
+        <v>-1.3953488372093024</v>
+      </c>
+      <c r="F97">
         <v>21.5</v>
       </c>
-      <c r="D97">
-        <v>-0.1</v>
-      </c>
-      <c r="E97">
-        <v>-0.46296296296296297</v>
-      </c>
-      <c r="F97">
+      <c r="G97">
         <v>21.6</v>
       </c>
-      <c r="G97">
-        <v>21.7</v>
-      </c>
       <c r="H97">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="I97">
         <v>0</v>
@@ -4888,22 +4888,22 @@
         <v>0</v>
       </c>
       <c r="K97">
-        <v>438245</v>
+        <v>844079</v>
       </c>
       <c r="L97">
-        <v>9425.7183</v>
+        <v>17973.0022</v>
       </c>
       <c r="M97">
-        <v>129000</v>
+        <v>139400</v>
       </c>
       <c r="N97">
-        <v>21.4</v>
+        <v>21.1</v>
       </c>
       <c r="O97">
-        <v>21.5</v>
+        <v>21.2</v>
       </c>
       <c r="P97">
-        <v>400</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="98">
@@ -4914,13 +4914,13 @@
         <v>-</v>
       </c>
       <c r="C98">
-        <v>55.5</v>
+        <v>55</v>
       </c>
       <c r="D98">
-        <v>-1</v>
+        <v>-0.5</v>
       </c>
       <c r="E98">
-        <v>-1.7699115044247788</v>
+        <v>-0.9009009009009009</v>
       </c>
       <c r="F98">
         <v>56</v>
@@ -4929,31 +4929,31 @@
         <v>56.5</v>
       </c>
       <c r="H98">
+        <v>54.75</v>
+      </c>
+      <c r="I98">
+        <v>0</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>10618744</v>
+      </c>
+      <c r="L98">
+        <v>590772.99275</v>
+      </c>
+      <c r="M98">
+        <v>513300</v>
+      </c>
+      <c r="N98">
         <v>55</v>
       </c>
-      <c r="I98">
-        <v>0</v>
-      </c>
-      <c r="J98">
-        <v>0</v>
-      </c>
-      <c r="K98">
-        <v>10005330</v>
-      </c>
-      <c r="L98">
-        <v>555531.02575</v>
-      </c>
-      <c r="M98">
-        <v>289500</v>
-      </c>
-      <c r="N98">
+      <c r="O98">
         <v>55.25</v>
       </c>
-      <c r="O98">
-        <v>55.5</v>
-      </c>
       <c r="P98">
-        <v>33800</v>
+        <v>34700</v>
       </c>
     </row>
     <row r="99">
@@ -4964,22 +4964,22 @@
         <v>-</v>
       </c>
       <c r="C99">
-        <v>4.64</v>
+        <v>4.54</v>
       </c>
       <c r="D99">
-        <v>0.04</v>
+        <v>-0.1</v>
       </c>
       <c r="E99">
-        <v>0.8695652173913043</v>
+        <v>-2.1551724137931036</v>
       </c>
       <c r="F99">
-        <v>4.62</v>
+        <v>4.66</v>
       </c>
       <c r="G99">
         <v>4.7</v>
       </c>
       <c r="H99">
-        <v>4.62</v>
+        <v>4.52</v>
       </c>
       <c r="I99">
         <v>0</v>
@@ -4988,22 +4988,22 @@
         <v>0</v>
       </c>
       <c r="K99">
-        <v>6508767</v>
+        <v>15341503</v>
       </c>
       <c r="L99">
-        <v>30310.22646</v>
+        <v>70317.48023999999</v>
       </c>
       <c r="M99">
-        <v>228200</v>
+        <v>65100</v>
       </c>
       <c r="N99">
-        <v>4.64</v>
+        <v>4.52</v>
       </c>
       <c r="O99">
-        <v>4.66</v>
+        <v>4.54</v>
       </c>
       <c r="P99">
-        <v>13200</v>
+        <v>281300</v>
       </c>
     </row>
     <row r="100">
@@ -5014,46 +5014,46 @@
         <v>-</v>
       </c>
       <c r="C100">
+        <v>102.5</v>
+      </c>
+      <c r="D100">
+        <v>-1</v>
+      </c>
+      <c r="E100">
+        <v>-0.966183574879227</v>
+      </c>
+      <c r="F100">
+        <v>103</v>
+      </c>
+      <c r="G100">
         <v>103.5</v>
-      </c>
-      <c r="D100">
-        <v>-0.5</v>
-      </c>
-      <c r="E100">
-        <v>-0.4807692307692308</v>
-      </c>
-      <c r="F100">
-        <v>103.5</v>
-      </c>
-      <c r="G100">
-        <v>104</v>
       </c>
       <c r="H100">
         <v>102.5</v>
       </c>
       <c r="I100">
-        <v>30400</v>
+        <v>0</v>
       </c>
       <c r="J100">
-        <v>3146.4</v>
+        <v>0</v>
       </c>
       <c r="K100">
-        <v>7684973</v>
+        <v>6804620</v>
       </c>
       <c r="L100">
-        <v>791786.1195</v>
+        <v>699823.3</v>
       </c>
       <c r="M100">
-        <v>639400</v>
+        <v>1437400</v>
       </c>
       <c r="N100">
+        <v>102.5</v>
+      </c>
+      <c r="O100">
         <v>103</v>
       </c>
-      <c r="O100">
-        <v>103.5</v>
-      </c>
       <c r="P100">
-        <v>169900</v>
+        <v>467500</v>
       </c>
     </row>
     <row r="101">
@@ -5067,43 +5067,43 @@
         <v>338</v>
       </c>
       <c r="D101">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E101">
-        <v>0.5952380952380952</v>
+        <v>0</v>
       </c>
       <c r="F101">
+        <v>338</v>
+      </c>
+      <c r="G101">
+        <v>340</v>
+      </c>
+      <c r="H101">
         <v>337</v>
       </c>
-      <c r="G101">
+      <c r="I101">
+        <v>0</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>2114967</v>
+      </c>
+      <c r="L101">
+        <v>716071.182</v>
+      </c>
+      <c r="M101">
+        <v>34700</v>
+      </c>
+      <c r="N101">
+        <v>338</v>
+      </c>
+      <c r="O101">
         <v>339</v>
       </c>
-      <c r="H101">
-        <v>336</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>0</v>
-      </c>
-      <c r="K101">
-        <v>2304687</v>
-      </c>
-      <c r="L101">
-        <v>778502.554</v>
-      </c>
-      <c r="M101">
-        <v>487000</v>
-      </c>
-      <c r="N101">
-        <v>337</v>
-      </c>
-      <c r="O101">
-        <v>338</v>
-      </c>
       <c r="P101">
-        <v>211800</v>
+        <v>286100</v>
       </c>
     </row>
     <row r="102">
@@ -5114,46 +5114,46 @@
         <v>-</v>
       </c>
       <c r="C102">
-        <v>157.5</v>
+        <v>156.5</v>
       </c>
       <c r="D102">
         <v>-1</v>
       </c>
       <c r="E102">
-        <v>-0.6309148264984227</v>
+        <v>-0.6349206349206349</v>
       </c>
       <c r="F102">
-        <v>158.5</v>
+        <v>158</v>
       </c>
       <c r="G102">
-        <v>158.5</v>
+        <v>158</v>
       </c>
       <c r="H102">
+        <v>156</v>
+      </c>
+      <c r="I102">
+        <v>0</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>372042</v>
+      </c>
+      <c r="L102">
+        <v>58281.191</v>
+      </c>
+      <c r="M102">
+        <v>6000</v>
+      </c>
+      <c r="N102">
+        <v>156.5</v>
+      </c>
+      <c r="O102">
         <v>157</v>
       </c>
-      <c r="I102">
-        <v>0</v>
-      </c>
-      <c r="J102">
-        <v>0</v>
-      </c>
-      <c r="K102">
-        <v>417258</v>
-      </c>
-      <c r="L102">
-        <v>65712.735</v>
-      </c>
-      <c r="M102">
-        <v>14800</v>
-      </c>
-      <c r="N102">
-        <v>157</v>
-      </c>
-      <c r="O102">
-        <v>157.5</v>
-      </c>
       <c r="P102">
-        <v>62400</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="103">
@@ -5164,46 +5164,46 @@
         <v>-</v>
       </c>
       <c r="C103">
-        <v>53.5</v>
+        <v>52.75</v>
       </c>
       <c r="D103">
-        <v>0</v>
+        <v>-0.75</v>
       </c>
       <c r="E103">
-        <v>0</v>
+        <v>-1.4018691588785046</v>
       </c>
       <c r="F103">
         <v>53.5</v>
       </c>
       <c r="G103">
-        <v>53.75</v>
+        <v>53.5</v>
       </c>
       <c r="H103">
-        <v>53</v>
+        <v>52.25</v>
       </c>
       <c r="I103">
-        <v>17500</v>
+        <v>615300</v>
       </c>
       <c r="J103">
-        <v>936.25</v>
+        <v>32457.075</v>
       </c>
       <c r="K103">
-        <v>5797609</v>
+        <v>10412198</v>
       </c>
       <c r="L103">
-        <v>309590.9925</v>
+        <v>549593.22075</v>
       </c>
       <c r="M103">
-        <v>199300</v>
+        <v>88800</v>
       </c>
       <c r="N103">
-        <v>53.25</v>
+        <v>52.5</v>
       </c>
       <c r="O103">
-        <v>53.5</v>
+        <v>52.75</v>
       </c>
       <c r="P103">
-        <v>145700</v>
+        <v>7100</v>
       </c>
     </row>
     <row r="104">
@@ -5214,46 +5214,46 @@
         <v>-</v>
       </c>
       <c r="C104">
+        <v>4.4</v>
+      </c>
+      <c r="D104">
+        <v>-0.04</v>
+      </c>
+      <c r="E104">
+        <v>-0.9009009009009009</v>
+      </c>
+      <c r="F104">
         <v>4.44</v>
       </c>
-      <c r="D104">
-        <v>-0.06</v>
-      </c>
-      <c r="E104">
-        <v>-1.3333333333333333</v>
-      </c>
-      <c r="F104">
-        <v>4.48</v>
-      </c>
       <c r="G104">
-        <v>4.5</v>
+        <v>4.44</v>
       </c>
       <c r="H104">
+        <v>4.38</v>
+      </c>
+      <c r="I104">
+        <v>0</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>6314133</v>
+      </c>
+      <c r="L104">
+        <v>27812.07386</v>
+      </c>
+      <c r="M104">
+        <v>181700</v>
+      </c>
+      <c r="N104">
         <v>4.4</v>
       </c>
-      <c r="I104">
-        <v>0</v>
-      </c>
-      <c r="J104">
-        <v>0</v>
-      </c>
-      <c r="K104">
-        <v>8944234</v>
-      </c>
-      <c r="L104">
-        <v>39711.11982</v>
-      </c>
-      <c r="M104">
-        <v>315100</v>
-      </c>
-      <c r="N104">
+      <c r="O104">
         <v>4.42</v>
       </c>
-      <c r="O104">
-        <v>4.44</v>
-      </c>
       <c r="P104">
-        <v>207900</v>
+        <v>351200</v>
       </c>
     </row>
     <row r="105">
@@ -5264,46 +5264,46 @@
         <v>-</v>
       </c>
       <c r="C105">
+        <v>1.86</v>
+      </c>
+      <c r="D105">
+        <v>-0.06</v>
+      </c>
+      <c r="E105">
+        <v>-3.125</v>
+      </c>
+      <c r="F105">
         <v>1.92</v>
       </c>
-      <c r="D105">
-        <v>0.06</v>
-      </c>
-      <c r="E105">
-        <v>3.225806451612903</v>
-      </c>
-      <c r="F105">
-        <v>1.88</v>
-      </c>
       <c r="G105">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="H105">
+        <v>1.84</v>
+      </c>
+      <c r="I105">
+        <v>0</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>276423490</v>
+      </c>
+      <c r="L105">
+        <v>521791.77239999996</v>
+      </c>
+      <c r="M105">
+        <v>2552200</v>
+      </c>
+      <c r="N105">
+        <v>1.86</v>
+      </c>
+      <c r="O105">
         <v>1.87</v>
       </c>
-      <c r="I105">
-        <v>0</v>
-      </c>
-      <c r="J105">
-        <v>0</v>
-      </c>
-      <c r="K105">
-        <v>249162219</v>
-      </c>
-      <c r="L105">
-        <v>473339.7729</v>
-      </c>
-      <c r="M105">
-        <v>4313100</v>
-      </c>
-      <c r="N105">
-        <v>1.91</v>
-      </c>
-      <c r="O105">
-        <v>1.92</v>
-      </c>
       <c r="P105">
-        <v>655500</v>
+        <v>1639900</v>
       </c>
     </row>
     <row r="106">
@@ -5314,46 +5314,46 @@
         <v>-</v>
       </c>
       <c r="C106">
-        <v>14.6</v>
+        <v>14.5</v>
       </c>
       <c r="D106">
-        <v>0.1</v>
+        <v>-0.1</v>
       </c>
       <c r="E106">
-        <v>0.6896551724137931</v>
+        <v>-0.684931506849315</v>
       </c>
       <c r="F106">
         <v>14.6</v>
       </c>
       <c r="G106">
-        <v>14.6</v>
+        <v>14.7</v>
       </c>
       <c r="H106">
+        <v>14.4</v>
+      </c>
+      <c r="I106">
+        <v>0</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>961868</v>
+      </c>
+      <c r="L106">
+        <v>14016.0407</v>
+      </c>
+      <c r="M106">
+        <v>337200</v>
+      </c>
+      <c r="N106">
+        <v>14.4</v>
+      </c>
+      <c r="O106">
         <v>14.5</v>
       </c>
-      <c r="I106">
-        <v>95000</v>
-      </c>
-      <c r="J106">
-        <v>1385.1</v>
-      </c>
-      <c r="K106">
-        <v>373800</v>
-      </c>
-      <c r="L106">
-        <v>5449.58</v>
-      </c>
-      <c r="M106">
-        <v>171300</v>
-      </c>
-      <c r="N106">
-        <v>14.5</v>
-      </c>
-      <c r="O106">
-        <v>14.6</v>
-      </c>
       <c r="P106">
-        <v>142700</v>
+        <v>46700</v>
       </c>
     </row>
     <row r="107">
@@ -5367,20 +5367,20 @@
         <v>24.5</v>
       </c>
       <c r="D107">
-        <v>0.3</v>
+        <v>0</v>
       </c>
       <c r="E107">
-        <v>1.2396694214876034</v>
+        <v>0</v>
       </c>
       <c r="F107">
+        <v>24.6</v>
+      </c>
+      <c r="G107">
+        <v>24.8</v>
+      </c>
+      <c r="H107">
         <v>24.4</v>
       </c>
-      <c r="G107">
-        <v>24.7</v>
-      </c>
-      <c r="H107">
-        <v>24.1</v>
-      </c>
       <c r="I107">
         <v>0</v>
       </c>
@@ -5388,13 +5388,13 @@
         <v>0</v>
       </c>
       <c r="K107">
-        <v>17117094</v>
+        <v>10111603</v>
       </c>
       <c r="L107">
-        <v>418845.7735</v>
+        <v>248609.5797</v>
       </c>
       <c r="M107">
-        <v>443500</v>
+        <v>279800</v>
       </c>
       <c r="N107">
         <v>24.5</v>
@@ -5403,7 +5403,7 @@
         <v>24.6</v>
       </c>
       <c r="P107">
-        <v>289200</v>
+        <v>173100</v>
       </c>
     </row>
     <row r="108">
@@ -5414,22 +5414,22 @@
         <v>-</v>
       </c>
       <c r="C108">
+        <v>24.5</v>
+      </c>
+      <c r="D108">
+        <v>1.1</v>
+      </c>
+      <c r="E108">
+        <v>4.700854700854701</v>
+      </c>
+      <c r="F108">
         <v>23.4</v>
       </c>
-      <c r="D108">
-        <v>0.8</v>
-      </c>
-      <c r="E108">
-        <v>3.5398230088495577</v>
-      </c>
-      <c r="F108">
-        <v>22.6</v>
-      </c>
       <c r="G108">
-        <v>23.6</v>
+        <v>24.7</v>
       </c>
       <c r="H108">
-        <v>22.6</v>
+        <v>23.2</v>
       </c>
       <c r="I108">
         <v>0</v>
@@ -5438,22 +5438,22 @@
         <v>0</v>
       </c>
       <c r="K108">
-        <v>17792391</v>
+        <v>19405610</v>
       </c>
       <c r="L108">
-        <v>410653.2648</v>
+        <v>466050.1147</v>
       </c>
       <c r="M108">
-        <v>371800</v>
+        <v>614800</v>
       </c>
       <c r="N108">
-        <v>23.3</v>
+        <v>24.5</v>
       </c>
       <c r="O108">
-        <v>23.4</v>
+        <v>24.6</v>
       </c>
       <c r="P108">
-        <v>22700</v>
+        <v>237600</v>
       </c>
     </row>
     <row r="109">
@@ -5464,22 +5464,22 @@
         <v>-</v>
       </c>
       <c r="C109">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="D109">
         <v>0.3</v>
       </c>
       <c r="E109">
-        <v>2.7027027027027026</v>
+        <v>2.6315789473684212</v>
       </c>
       <c r="F109">
-        <v>11.1</v>
+        <v>11.4</v>
       </c>
       <c r="G109">
-        <v>11.6</v>
+        <v>12</v>
       </c>
       <c r="H109">
-        <v>11</v>
+        <v>11.4</v>
       </c>
       <c r="I109">
         <v>0</v>
@@ -5488,22 +5488,22 @@
         <v>0</v>
       </c>
       <c r="K109">
-        <v>26522526</v>
+        <v>37754818</v>
       </c>
       <c r="L109">
-        <v>302055.1235</v>
+        <v>442598.1054</v>
       </c>
       <c r="M109">
-        <v>1124000</v>
+        <v>1258600</v>
       </c>
       <c r="N109">
-        <v>11.4</v>
+        <v>11.7</v>
       </c>
       <c r="O109">
-        <v>11.5</v>
+        <v>11.8</v>
       </c>
       <c r="P109">
-        <v>556600</v>
+        <v>1145400</v>
       </c>
     </row>
     <row r="110">
@@ -5514,22 +5514,22 @@
         <v>-</v>
       </c>
       <c r="C110">
+        <v>16.3</v>
+      </c>
+      <c r="D110">
+        <v>-0.8</v>
+      </c>
+      <c r="E110">
+        <v>-4.678362573099415</v>
+      </c>
+      <c r="F110">
         <v>17.1</v>
       </c>
-      <c r="D110">
-        <v>0</v>
-      </c>
-      <c r="E110">
-        <v>0</v>
-      </c>
-      <c r="F110">
+      <c r="G110">
         <v>17.2</v>
       </c>
-      <c r="G110">
-        <v>17.6</v>
-      </c>
       <c r="H110">
-        <v>17</v>
+        <v>16.3</v>
       </c>
       <c r="I110">
         <v>0</v>
@@ -5538,22 +5538,22 @@
         <v>0</v>
       </c>
       <c r="K110">
-        <v>6475566</v>
+        <v>3347661</v>
       </c>
       <c r="L110">
-        <v>112298.1049</v>
+        <v>56075.0762</v>
       </c>
       <c r="M110">
-        <v>9600</v>
+        <v>278600</v>
       </c>
       <c r="N110">
-        <v>17.1</v>
+        <v>16.3</v>
       </c>
       <c r="O110">
-        <v>17.2</v>
+        <v>16.4</v>
       </c>
       <c r="P110">
-        <v>203200</v>
+        <v>16100</v>
       </c>
     </row>
     <row r="111">
@@ -5564,22 +5564,22 @@
         <v>-</v>
       </c>
       <c r="C111">
+        <v>4.04</v>
+      </c>
+      <c r="D111">
+        <v>-0.02</v>
+      </c>
+      <c r="E111">
+        <v>-0.49261083743842365</v>
+      </c>
+      <c r="F111">
         <v>4.06</v>
       </c>
-      <c r="D111">
-        <v>-0.06</v>
-      </c>
-      <c r="E111">
-        <v>-1.4563106796116505</v>
-      </c>
-      <c r="F111">
+      <c r="G111">
         <v>4.1</v>
       </c>
-      <c r="G111">
-        <v>4.12</v>
-      </c>
       <c r="H111">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="I111">
         <v>0</v>
@@ -5588,22 +5588,22 @@
         <v>0</v>
       </c>
       <c r="K111">
-        <v>18301546</v>
+        <v>35674628</v>
       </c>
       <c r="L111">
-        <v>74524.31034</v>
+        <v>144373.1414</v>
       </c>
       <c r="M111">
-        <v>2654200</v>
+        <v>1820600</v>
       </c>
       <c r="N111">
-        <v>4.06</v>
+        <v>4.02</v>
       </c>
       <c r="O111">
-        <v>4.08</v>
+        <v>4.04</v>
       </c>
       <c r="P111">
-        <v>499100</v>
+        <v>118300</v>
       </c>
     </row>
     <row r="112">
@@ -5614,46 +5614,46 @@
         <v>-</v>
       </c>
       <c r="C112">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="D112">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="E112">
-        <v>0</v>
+        <v>0.6211180124223602</v>
       </c>
       <c r="F112">
         <v>16.1</v>
       </c>
       <c r="G112">
+        <v>16.6</v>
+      </c>
+      <c r="H112">
+        <v>16</v>
+      </c>
+      <c r="I112">
+        <v>0</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>11447811</v>
+      </c>
+      <c r="L112">
+        <v>186660.108</v>
+      </c>
+      <c r="M112">
+        <v>233300</v>
+      </c>
+      <c r="N112">
         <v>16.2</v>
       </c>
-      <c r="H112">
-        <v>15.9</v>
-      </c>
-      <c r="I112">
-        <v>0</v>
-      </c>
-      <c r="J112">
-        <v>0</v>
-      </c>
-      <c r="K112">
-        <v>5819119</v>
-      </c>
-      <c r="L112">
-        <v>93254.035</v>
-      </c>
-      <c r="M112">
-        <v>71300</v>
-      </c>
-      <c r="N112">
-        <v>16.1</v>
-      </c>
       <c r="O112">
-        <v>16.2</v>
+        <v>16.3</v>
       </c>
       <c r="P112">
-        <v>308200</v>
+        <v>56300</v>
       </c>
     </row>
     <row r="113">
@@ -5667,13 +5667,13 @@
         <v>102.5</v>
       </c>
       <c r="D113">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="E113">
-        <v>-0.4854368932038835</v>
+        <v>0</v>
       </c>
       <c r="F113">
-        <v>103</v>
+        <v>102.5</v>
       </c>
       <c r="G113">
         <v>103</v>
@@ -5688,13 +5688,13 @@
         <v>0</v>
       </c>
       <c r="K113">
-        <v>3757061</v>
+        <v>3130384</v>
       </c>
       <c r="L113">
-        <v>385313.0485</v>
+        <v>320852.1005</v>
       </c>
       <c r="M113">
-        <v>312300</v>
+        <v>38100</v>
       </c>
       <c r="N113">
         <v>102.5</v>
@@ -5703,7 +5703,7 @@
         <v>103</v>
       </c>
       <c r="P113">
-        <v>1323400</v>
+        <v>1244600</v>
       </c>
     </row>
     <row r="114">
@@ -5714,22 +5714,22 @@
         <v>-</v>
       </c>
       <c r="C114">
-        <v>13.4</v>
+        <v>13.2</v>
       </c>
       <c r="D114">
         <v>-0.2</v>
       </c>
       <c r="E114">
-        <v>-1.4705882352941178</v>
+        <v>-1.492537313432836</v>
       </c>
       <c r="F114">
-        <v>13.6</v>
+        <v>13.4</v>
       </c>
       <c r="G114">
-        <v>13.6</v>
+        <v>13.5</v>
       </c>
       <c r="H114">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="I114">
         <v>0</v>
@@ -5738,22 +5738,22 @@
         <v>0</v>
       </c>
       <c r="K114">
-        <v>1934281</v>
+        <v>2950828</v>
       </c>
       <c r="L114">
-        <v>26024.160399999997</v>
+        <v>39079.1244</v>
       </c>
       <c r="M114">
-        <v>275600</v>
+        <v>314800</v>
       </c>
       <c r="N114">
-        <v>13.4</v>
+        <v>13.1</v>
       </c>
       <c r="O114">
-        <v>13.5</v>
+        <v>13.2</v>
       </c>
       <c r="P114">
-        <v>137500</v>
+        <v>182000</v>
       </c>
     </row>
     <row r="115">
@@ -5764,46 +5764,46 @@
         <v>-</v>
       </c>
       <c r="C115">
+        <v>8.1</v>
+      </c>
+      <c r="D115">
+        <v>-0.05</v>
+      </c>
+      <c r="E115">
+        <v>-0.6134969325153374</v>
+      </c>
+      <c r="F115">
         <v>8.15</v>
       </c>
-      <c r="D115">
-        <v>0</v>
-      </c>
-      <c r="E115">
-        <v>0</v>
-      </c>
-      <c r="F115">
-        <v>8.25</v>
-      </c>
       <c r="G115">
-        <v>8.25</v>
+        <v>8.15</v>
       </c>
       <c r="H115">
+        <v>8.05</v>
+      </c>
+      <c r="I115">
+        <v>0</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>219041</v>
+      </c>
+      <c r="L115">
+        <v>1775.27415</v>
+      </c>
+      <c r="M115">
+        <v>35900</v>
+      </c>
+      <c r="N115">
         <v>8.1</v>
       </c>
-      <c r="I115">
-        <v>0</v>
-      </c>
-      <c r="J115">
-        <v>0</v>
-      </c>
-      <c r="K115">
-        <v>121777</v>
-      </c>
-      <c r="L115">
-        <v>995.21645</v>
-      </c>
-      <c r="M115">
-        <v>12100</v>
-      </c>
-      <c r="N115">
+      <c r="O115">
         <v>8.15</v>
       </c>
-      <c r="O115">
-        <v>8.2</v>
-      </c>
       <c r="P115">
-        <v>28700</v>
+        <v>48900</v>
       </c>
     </row>
     <row r="116">
@@ -5817,43 +5817,43 @@
         <v>34.25</v>
       </c>
       <c r="D116">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="E116">
-        <v>-1.4388489208633093</v>
+        <v>0</v>
       </c>
       <c r="F116">
-        <v>34.75</v>
+        <v>34.5</v>
       </c>
       <c r="G116">
-        <v>34.75</v>
+        <v>34.5</v>
       </c>
       <c r="H116">
+        <v>34</v>
+      </c>
+      <c r="I116">
+        <v>0</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>236361</v>
+      </c>
+      <c r="L116">
+        <v>8094.6095</v>
+      </c>
+      <c r="M116">
+        <v>314200</v>
+      </c>
+      <c r="N116">
+        <v>34</v>
+      </c>
+      <c r="O116">
         <v>34.25</v>
       </c>
-      <c r="I116">
-        <v>0</v>
-      </c>
-      <c r="J116">
-        <v>0</v>
-      </c>
-      <c r="K116">
-        <v>308244</v>
-      </c>
-      <c r="L116">
-        <v>10609.06925</v>
-      </c>
-      <c r="M116">
-        <v>21600</v>
-      </c>
-      <c r="N116">
-        <v>34.25</v>
-      </c>
-      <c r="O116">
-        <v>34.5</v>
-      </c>
       <c r="P116">
-        <v>10800</v>
+        <v>9100</v>
       </c>
     </row>
     <row r="117">
@@ -5864,37 +5864,37 @@
         <v>-</v>
       </c>
       <c r="C117">
-        <v>57</v>
+        <v>57.25</v>
       </c>
       <c r="D117">
-        <v>-0.25</v>
+        <v>0.25</v>
       </c>
       <c r="E117">
-        <v>-0.4366812227074236</v>
+        <v>0.43859649122807015</v>
       </c>
       <c r="F117">
         <v>57.5</v>
       </c>
       <c r="G117">
-        <v>58</v>
+        <v>58.5</v>
       </c>
       <c r="H117">
-        <v>56.75</v>
+        <v>57</v>
       </c>
       <c r="I117">
-        <v>0</v>
+        <v>775200</v>
       </c>
       <c r="J117">
-        <v>0</v>
+        <v>44550.37</v>
       </c>
       <c r="K117">
-        <v>9125904</v>
+        <v>12358616</v>
       </c>
       <c r="L117">
-        <v>523788.4305</v>
+        <v>712620.5205</v>
       </c>
       <c r="M117">
-        <v>10400</v>
+        <v>1227200</v>
       </c>
       <c r="N117">
         <v>57</v>
@@ -5903,7 +5903,7 @@
         <v>57.25</v>
       </c>
       <c r="P117">
-        <v>552800</v>
+        <v>36900</v>
       </c>
     </row>
     <row r="118">
@@ -5914,46 +5914,46 @@
         <v>-</v>
       </c>
       <c r="C118">
+        <v>1.84</v>
+      </c>
+      <c r="D118">
+        <v>0.02</v>
+      </c>
+      <c r="E118">
+        <v>1.098901098901099</v>
+      </c>
+      <c r="F118">
         <v>1.82</v>
       </c>
-      <c r="D118">
-        <v>-0.02</v>
-      </c>
-      <c r="E118">
-        <v>-1.0869565217391304</v>
-      </c>
-      <c r="F118">
+      <c r="G118">
+        <v>1.85</v>
+      </c>
+      <c r="H118">
+        <v>1.81</v>
+      </c>
+      <c r="I118">
+        <v>0</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>13538520</v>
+      </c>
+      <c r="L118">
+        <v>24811.78485</v>
+      </c>
+      <c r="M118">
+        <v>640100</v>
+      </c>
+      <c r="N118">
+        <v>1.83</v>
+      </c>
+      <c r="O118">
         <v>1.84</v>
       </c>
-      <c r="G118">
-        <v>1.84</v>
-      </c>
-      <c r="H118">
-        <v>1.82</v>
-      </c>
-      <c r="I118">
-        <v>0</v>
-      </c>
-      <c r="J118">
-        <v>0</v>
-      </c>
-      <c r="K118">
-        <v>8860867</v>
-      </c>
-      <c r="L118">
-        <v>16172.160240000001</v>
-      </c>
-      <c r="M118">
-        <v>1316800</v>
-      </c>
-      <c r="N118">
-        <v>1.82</v>
-      </c>
-      <c r="O118">
-        <v>1.83</v>
-      </c>
       <c r="P118">
-        <v>6000</v>
+        <v>1137700</v>
       </c>
     </row>
     <row r="119">
@@ -5961,25 +5961,25 @@
         <v>TPIPP</v>
       </c>
       <c r="B119" t="str">
-        <v>-</v>
+        <v>XD</v>
       </c>
       <c r="C119">
-        <v>3.5</v>
+        <v>3.42</v>
       </c>
       <c r="D119">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="E119">
-        <v>-0.5681818181818182</v>
+        <v>-2.2857142857142856</v>
       </c>
       <c r="F119">
-        <v>3.52</v>
+        <v>3.4</v>
       </c>
       <c r="G119">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="H119">
-        <v>3.48</v>
+        <v>3.4</v>
       </c>
       <c r="I119">
         <v>0</v>
@@ -5988,22 +5988,22 @@
         <v>0</v>
       </c>
       <c r="K119">
-        <v>9303552</v>
+        <v>5336479</v>
       </c>
       <c r="L119">
-        <v>32598.451719999997</v>
+        <v>18194.42448</v>
       </c>
       <c r="M119">
-        <v>958200</v>
+        <v>1884500</v>
       </c>
       <c r="N119">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="O119">
-        <v>3.52</v>
+        <v>3.42</v>
       </c>
       <c r="P119">
-        <v>1220600</v>
+        <v>758400</v>
       </c>
     </row>
     <row r="120">
@@ -6014,19 +6014,19 @@
         <v>-</v>
       </c>
       <c r="C120">
+        <v>42.5</v>
+      </c>
+      <c r="D120">
+        <v>-0.25</v>
+      </c>
+      <c r="E120">
+        <v>-0.5847953216374269</v>
+      </c>
+      <c r="F120">
         <v>42.75</v>
       </c>
-      <c r="D120">
-        <v>-0.5</v>
-      </c>
-      <c r="E120">
-        <v>-1.1560693641618498</v>
-      </c>
-      <c r="F120">
-        <v>43.25</v>
-      </c>
       <c r="G120">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="H120">
         <v>42.5</v>
@@ -6038,22 +6038,22 @@
         <v>0</v>
       </c>
       <c r="K120">
-        <v>1743121</v>
+        <v>1223928</v>
       </c>
       <c r="L120">
-        <v>75207.92425</v>
+        <v>52245.6045</v>
       </c>
       <c r="M120">
-        <v>136700</v>
+        <v>123500</v>
       </c>
       <c r="N120">
+        <v>42.5</v>
+      </c>
+      <c r="O120">
         <v>42.75</v>
       </c>
-      <c r="O120">
-        <v>43</v>
-      </c>
       <c r="P120">
-        <v>152000</v>
+        <v>128600</v>
       </c>
     </row>
     <row r="121">
@@ -6064,46 +6064,46 @@
         <v>-</v>
       </c>
       <c r="C121">
+        <v>1.16</v>
+      </c>
+      <c r="D121">
+        <v>-0.01</v>
+      </c>
+      <c r="E121">
+        <v>-0.8547008547008547</v>
+      </c>
+      <c r="F121">
         <v>1.17</v>
       </c>
-      <c r="D121">
-        <v>0.01</v>
-      </c>
-      <c r="E121">
-        <v>0.8620689655172413</v>
-      </c>
-      <c r="F121">
+      <c r="G121">
+        <v>1.17</v>
+      </c>
+      <c r="H121">
+        <v>1.14</v>
+      </c>
+      <c r="I121">
+        <v>0</v>
+      </c>
+      <c r="J121">
+        <v>0</v>
+      </c>
+      <c r="K121">
+        <v>5021700</v>
+      </c>
+      <c r="L121">
+        <v>5813.152</v>
+      </c>
+      <c r="M121">
+        <v>674300</v>
+      </c>
+      <c r="N121">
+        <v>1.14</v>
+      </c>
+      <c r="O121">
         <v>1.16</v>
       </c>
-      <c r="G121">
-        <v>1.18</v>
-      </c>
-      <c r="H121">
-        <v>1.15</v>
-      </c>
-      <c r="I121">
-        <v>0</v>
-      </c>
-      <c r="J121">
-        <v>0</v>
-      </c>
-      <c r="K121">
-        <v>2418600</v>
-      </c>
-      <c r="L121">
-        <v>2811.27308</v>
-      </c>
-      <c r="M121">
-        <v>213000</v>
-      </c>
-      <c r="N121">
-        <v>1.16</v>
-      </c>
-      <c r="O121">
-        <v>1.17</v>
-      </c>
       <c r="P121">
-        <v>183700</v>
+        <v>54100</v>
       </c>
     </row>
     <row r="122">
@@ -6114,46 +6114,46 @@
         <v>-</v>
       </c>
       <c r="C122">
+        <v>8</v>
+      </c>
+      <c r="D122">
+        <v>-0.1</v>
+      </c>
+      <c r="E122">
+        <v>-1.2345679012345678</v>
+      </c>
+      <c r="F122">
         <v>8.1</v>
       </c>
-      <c r="D122">
-        <v>0.05</v>
-      </c>
-      <c r="E122">
-        <v>0.6211180124223602</v>
-      </c>
-      <c r="F122">
+      <c r="G122">
+        <v>8.1</v>
+      </c>
+      <c r="H122">
+        <v>7.95</v>
+      </c>
+      <c r="I122">
+        <v>0</v>
+      </c>
+      <c r="J122">
+        <v>0</v>
+      </c>
+      <c r="K122">
+        <v>4719758</v>
+      </c>
+      <c r="L122">
+        <v>37730.91895000001</v>
+      </c>
+      <c r="M122">
+        <v>5300</v>
+      </c>
+      <c r="N122">
+        <v>8</v>
+      </c>
+      <c r="O122">
         <v>8.05</v>
       </c>
-      <c r="G122">
-        <v>8.15</v>
-      </c>
-      <c r="H122">
-        <v>8</v>
-      </c>
-      <c r="I122">
-        <v>0</v>
-      </c>
-      <c r="J122">
-        <v>0</v>
-      </c>
-      <c r="K122">
-        <v>3759691</v>
-      </c>
-      <c r="L122">
-        <v>30312.5005</v>
-      </c>
-      <c r="M122">
-        <v>178500</v>
-      </c>
-      <c r="N122">
-        <v>8.05</v>
-      </c>
-      <c r="O122">
-        <v>8.1</v>
-      </c>
       <c r="P122">
-        <v>88100</v>
+        <v>86100</v>
       </c>
     </row>
     <row r="123">
@@ -6164,22 +6164,22 @@
         <v>-</v>
       </c>
       <c r="C123">
+        <v>1.41</v>
+      </c>
+      <c r="D123">
+        <v>-0.01</v>
+      </c>
+      <c r="E123">
+        <v>-0.704225352112676</v>
+      </c>
+      <c r="F123">
         <v>1.42</v>
       </c>
-      <c r="D123">
-        <v>-0.03</v>
-      </c>
-      <c r="E123">
-        <v>-2.0689655172413794</v>
-      </c>
-      <c r="F123">
-        <v>1.44</v>
-      </c>
       <c r="G123">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="H123">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="I123">
         <v>0</v>
@@ -6188,22 +6188,22 @@
         <v>0</v>
       </c>
       <c r="K123">
-        <v>194236716</v>
+        <v>176495947</v>
       </c>
       <c r="L123">
-        <v>276844.8389</v>
+        <v>248569.87536</v>
       </c>
       <c r="M123">
-        <v>17077300</v>
+        <v>32377900</v>
       </c>
       <c r="N123">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="O123">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="P123">
-        <v>21403900</v>
+        <v>27769300</v>
       </c>
     </row>
     <row r="124">
@@ -6214,22 +6214,22 @@
         <v>-</v>
       </c>
       <c r="C124">
-        <v>9.7</v>
+        <v>9.65</v>
       </c>
       <c r="D124">
-        <v>0.25</v>
+        <v>-0.05</v>
       </c>
       <c r="E124">
-        <v>2.6455026455026456</v>
+        <v>-0.5154639175257731</v>
       </c>
       <c r="F124">
-        <v>9.5</v>
+        <v>9.75</v>
       </c>
       <c r="G124">
         <v>9.75</v>
       </c>
       <c r="H124">
-        <v>9.45</v>
+        <v>9.6</v>
       </c>
       <c r="I124">
         <v>0</v>
@@ -6238,22 +6238,22 @@
         <v>0</v>
       </c>
       <c r="K124">
-        <v>6681864</v>
+        <v>1667995</v>
       </c>
       <c r="L124">
-        <v>64244.430799999995</v>
+        <v>16086.04405</v>
       </c>
       <c r="M124">
-        <v>30400</v>
+        <v>444500</v>
       </c>
       <c r="N124">
+        <v>9.6</v>
+      </c>
+      <c r="O124">
         <v>9.65</v>
       </c>
-      <c r="O124">
-        <v>9.7</v>
-      </c>
       <c r="P124">
-        <v>23400</v>
+        <v>56300</v>
       </c>
     </row>
     <row r="125">
@@ -6264,19 +6264,19 @@
         <v>-</v>
       </c>
       <c r="C125">
+        <v>29</v>
+      </c>
+      <c r="D125">
+        <v>0.25</v>
+      </c>
+      <c r="E125">
+        <v>0.8695652173913043</v>
+      </c>
+      <c r="F125">
         <v>28.75</v>
       </c>
-      <c r="D125">
-        <v>-0.25</v>
-      </c>
-      <c r="E125">
-        <v>-0.8620689655172413</v>
-      </c>
-      <c r="F125">
+      <c r="G125">
         <v>29</v>
-      </c>
-      <c r="G125">
-        <v>29.25</v>
       </c>
       <c r="H125">
         <v>28.75</v>
@@ -6288,13 +6288,13 @@
         <v>0</v>
       </c>
       <c r="K125">
-        <v>298190</v>
+        <v>184860</v>
       </c>
       <c r="L125">
-        <v>8600.59175</v>
+        <v>5339.53575</v>
       </c>
       <c r="M125">
-        <v>1106000</v>
+        <v>868700</v>
       </c>
       <c r="N125">
         <v>28.75</v>
@@ -6303,7 +6303,7 @@
         <v>29</v>
       </c>
       <c r="P125">
-        <v>64100</v>
+        <v>256300</v>
       </c>
     </row>
     <row r="126">
@@ -6314,46 +6314,46 @@
         <v>-</v>
       </c>
       <c r="C126">
-        <v>4.98</v>
+        <v>4.92</v>
       </c>
       <c r="D126">
-        <v>-0.02</v>
+        <v>-0.06</v>
       </c>
       <c r="E126">
-        <v>-0.4</v>
+        <v>-1.2048192771084338</v>
       </c>
       <c r="F126">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="G126">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="H126">
+        <v>4.86</v>
+      </c>
+      <c r="I126">
+        <v>0</v>
+      </c>
+      <c r="J126">
+        <v>0</v>
+      </c>
+      <c r="K126">
+        <v>35875930</v>
+      </c>
+      <c r="L126">
+        <v>176936.46269999997</v>
+      </c>
+      <c r="M126">
+        <v>602700</v>
+      </c>
+      <c r="N126">
+        <v>4.9</v>
+      </c>
+      <c r="O126">
         <v>4.92</v>
       </c>
-      <c r="I126">
-        <v>0</v>
-      </c>
-      <c r="J126">
-        <v>0</v>
-      </c>
-      <c r="K126">
-        <v>16941119</v>
-      </c>
-      <c r="L126">
-        <v>83955.83691</v>
-      </c>
-      <c r="M126">
-        <v>539000</v>
-      </c>
-      <c r="N126">
-        <v>4.96</v>
-      </c>
-      <c r="O126">
-        <v>4.98</v>
-      </c>
       <c r="P126">
-        <v>552300</v>
+        <v>408000</v>
       </c>
     </row>
     <row r="127">
@@ -6367,10 +6367,10 @@
         <v>3.9</v>
       </c>
       <c r="D127">
-        <v>-0.02</v>
+        <v>0</v>
       </c>
       <c r="E127">
-        <v>-0.5102040816326531</v>
+        <v>0</v>
       </c>
       <c r="F127">
         <v>3.92</v>
@@ -6388,22 +6388,22 @@
         <v>0</v>
       </c>
       <c r="K127">
-        <v>73616885</v>
+        <v>69634122</v>
       </c>
       <c r="L127">
-        <v>286207.30916</v>
+        <v>271734.08660000004</v>
       </c>
       <c r="M127">
-        <v>6303600</v>
+        <v>46300</v>
       </c>
       <c r="N127">
-        <v>3.88</v>
+        <v>3.9</v>
       </c>
       <c r="O127">
-        <v>3.9</v>
+        <v>3.92</v>
       </c>
       <c r="P127">
-        <v>1586700</v>
+        <v>7688900</v>
       </c>
     </row>
     <row r="128">
@@ -6414,46 +6414,46 @@
         <v>-</v>
       </c>
       <c r="C128">
+        <v>4.08</v>
+      </c>
+      <c r="D128">
+        <v>-0.04</v>
+      </c>
+      <c r="E128">
+        <v>-0.970873786407767</v>
+      </c>
+      <c r="F128">
+        <v>4.1</v>
+      </c>
+      <c r="G128">
         <v>4.12</v>
       </c>
-      <c r="D128">
-        <v>0</v>
-      </c>
-      <c r="E128">
-        <v>0</v>
-      </c>
-      <c r="F128">
-        <v>4.12</v>
-      </c>
-      <c r="G128">
-        <v>4.14</v>
-      </c>
       <c r="H128">
+        <v>4.06</v>
+      </c>
+      <c r="I128">
+        <v>0</v>
+      </c>
+      <c r="J128">
+        <v>0</v>
+      </c>
+      <c r="K128">
+        <v>2547336</v>
+      </c>
+      <c r="L128">
+        <v>10409.716</v>
+      </c>
+      <c r="M128">
+        <v>941700</v>
+      </c>
+      <c r="N128">
+        <v>4.06</v>
+      </c>
+      <c r="O128">
         <v>4.08</v>
       </c>
-      <c r="I128">
-        <v>0</v>
-      </c>
-      <c r="J128">
-        <v>0</v>
-      </c>
-      <c r="K128">
-        <v>1427266</v>
-      </c>
-      <c r="L128">
-        <v>5862.84376</v>
-      </c>
-      <c r="M128">
-        <v>86100</v>
-      </c>
-      <c r="N128">
-        <v>4.1</v>
-      </c>
-      <c r="O128">
-        <v>4.12</v>
-      </c>
       <c r="P128">
-        <v>9300</v>
+        <v>36700</v>
       </c>
     </row>
   </sheetData>
